--- a/www/flightdata/xlsx/eoss-334.xlsx
+++ b/www/flightdata/xlsx/eoss-334.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="489">
   <si>
     <t>flight</t>
   </si>
@@ -36,6 +36,18 @@
     <t>h2fill</t>
   </si>
   <si>
+    <t>maxaltitude</t>
+  </si>
+  <si>
+    <t>numpoints</t>
+  </si>
+  <si>
+    <t>flighttime</t>
+  </si>
+  <si>
+    <t>flighttime_secs</t>
+  </si>
+  <si>
     <t>weights.client</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
   </si>
   <si>
     <t>285</t>
+  </si>
+  <si>
+    <t>1hrs 59mins 28secs</t>
   </si>
   <si>
     <t>7.46</t>
@@ -1829,10 +1844,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1872,46 +1887,70 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>86211</v>
+      </c>
+      <c r="H2">
+        <v>211</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>7168</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1926,102 +1965,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>44940.34004650463</v>
@@ -2039,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K2">
         <v>344</v>
@@ -2069,7 +2108,7 @@
         <v>1.5</v>
       </c>
       <c r="V2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="X2">
         <v>1.5</v>
@@ -2080,10 +2119,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2">
         <v>44940.34033475695</v>
@@ -2101,13 +2140,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2131,7 +2170,7 @@
         <v>13</v>
       </c>
       <c r="V3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W3">
         <v>11.5</v>
@@ -2154,10 +2193,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>44940.34067034722</v>
@@ -2175,13 +2214,13 @@
         <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K4">
         <v>130</v>
@@ -2205,7 +2244,7 @@
         <v>20.93846154</v>
       </c>
       <c r="V4" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W4">
         <v>0.12213</v>
@@ -2234,10 +2273,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2">
         <v>44940.34101709491</v>
@@ -2255,13 +2294,13 @@
         <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K5">
         <v>136</v>
@@ -2285,7 +2324,7 @@
         <v>19.41666667</v>
       </c>
       <c r="V5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W5">
         <v>-0.06340800000000001</v>
@@ -2314,10 +2353,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>44940.34130826389</v>
@@ -2335,13 +2374,13 @@
         <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K6">
         <v>132</v>
@@ -2365,7 +2404,7 @@
         <v>22</v>
       </c>
       <c r="V6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W6">
         <v>2.583333</v>
@@ -2394,10 +2433,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2">
         <v>44940.34164278935</v>
@@ -2415,13 +2454,13 @@
         <v>132</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K7">
         <v>138</v>
@@ -2445,7 +2484,7 @@
         <v>16.92682927</v>
       </c>
       <c r="V7" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W7">
         <v>-0.123736</v>
@@ -2474,10 +2513,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>44940.34199069445</v>
@@ -2495,13 +2534,13 @@
         <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K8">
         <v>120</v>
@@ -2525,7 +2564,7 @@
         <v>24.375</v>
       </c>
       <c r="V8" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W8">
         <v>0.15517</v>
@@ -2554,10 +2593,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>44940.34228068287</v>
@@ -2575,13 +2614,13 @@
         <v>181</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J9" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K9">
         <v>118</v>
@@ -2605,7 +2644,7 @@
         <v>22</v>
       </c>
       <c r="V9" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W9">
         <v>-2.375</v>
@@ -2634,10 +2673,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>44940.34261623843</v>
@@ -2655,13 +2694,13 @@
         <v>222</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K10">
         <v>135</v>
@@ -2685,7 +2724,7 @@
         <v>13.82926829</v>
       </c>
       <c r="V10" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W10">
         <v>-0.199286</v>
@@ -2714,10 +2753,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>44940.3429653125</v>
@@ -2735,13 +2774,13 @@
         <v>245</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J11" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K11">
         <v>96</v>
@@ -2765,7 +2804,7 @@
         <v>18.73913043</v>
       </c>
       <c r="V11" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W11">
         <v>0.213472</v>
@@ -2794,10 +2833,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>44940.3432546412</v>
@@ -2815,13 +2854,13 @@
         <v>271</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K12">
         <v>106</v>
@@ -2845,7 +2884,7 @@
         <v>22.42307692</v>
       </c>
       <c r="V12" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W12">
         <v>0.14169</v>
@@ -2874,10 +2913,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2">
         <v>44940.34359054398</v>
@@ -2895,13 +2934,13 @@
         <v>311</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J13" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K13">
         <v>106</v>
@@ -2925,7 +2964,7 @@
         <v>24.275</v>
       </c>
       <c r="V13" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W13">
         <v>0.046298</v>
@@ -2954,10 +2993,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>44940.34393738426</v>
@@ -2975,13 +3014,13 @@
         <v>335</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K14">
         <v>82</v>
@@ -3005,7 +3044,7 @@
         <v>18.08333333</v>
       </c>
       <c r="V14" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W14">
         <v>-0.257986</v>
@@ -3034,10 +3073,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>44940.34422796296</v>
@@ -3055,13 +3094,13 @@
         <v>337</v>
       </c>
       <c r="H15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J15" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K15">
         <v>86</v>
@@ -3085,7 +3124,7 @@
         <v>21.5</v>
       </c>
       <c r="V15" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W15">
         <v>1.708333</v>
@@ -3114,10 +3153,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>44940.34456484954</v>
@@ -3135,13 +3174,13 @@
         <v>401</v>
       </c>
       <c r="H16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J16" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K16">
         <v>83</v>
@@ -3165,7 +3204,7 @@
         <v>20.703125</v>
       </c>
       <c r="V16" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W16">
         <v>-0.012451</v>
@@ -3194,10 +3233,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2">
         <v>44940.34491047454</v>
@@ -3215,13 +3254,13 @@
         <v>425</v>
       </c>
       <c r="H17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J17" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K17">
         <v>81</v>
@@ -3245,7 +3284,7 @@
         <v>23.79166667</v>
       </c>
       <c r="V17" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W17">
         <v>0.128689</v>
@@ -3274,10 +3313,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2">
         <v>44940.3452025</v>
@@ -3295,13 +3334,13 @@
         <v>427</v>
       </c>
       <c r="H18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K18">
         <v>77</v>
@@ -3325,7 +3364,7 @@
         <v>28</v>
       </c>
       <c r="V18" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W18">
         <v>2.104167</v>
@@ -3354,10 +3393,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>44940.34553807871</v>
@@ -3375,13 +3414,13 @@
         <v>466</v>
       </c>
       <c r="H19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I19" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K19">
         <v>78</v>
@@ -3405,7 +3444,7 @@
         <v>22.66666667</v>
       </c>
       <c r="V19" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W19">
         <v>-0.136752</v>
@@ -3434,10 +3473,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2">
         <v>44940.34588461806</v>
@@ -3455,13 +3494,13 @@
         <v>515</v>
       </c>
       <c r="H20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I20" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J20" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K20">
         <v>85</v>
@@ -3485,7 +3524,7 @@
         <v>23.18367347</v>
       </c>
       <c r="V20" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W20">
         <v>0.010551</v>
@@ -3514,10 +3553,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>44940.3461744213</v>
@@ -3535,13 +3574,13 @@
         <v>517</v>
       </c>
       <c r="H21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I21" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K21">
         <v>79</v>
@@ -3565,7 +3604,7 @@
         <v>23</v>
       </c>
       <c r="V21" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W21">
         <v>-0.091837</v>
@@ -3594,10 +3633,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>44940.34651012732</v>
@@ -3615,13 +3654,13 @@
         <v>558</v>
       </c>
       <c r="H22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K22">
         <v>84</v>
@@ -3645,7 +3684,7 @@
         <v>20.7804878</v>
       </c>
       <c r="V22" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W22">
         <v>-0.054134</v>
@@ -3674,10 +3713,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>44940.34685759259</v>
@@ -3695,13 +3734,13 @@
         <v>605</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I23" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J23" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K23">
         <v>91</v>
@@ -3725,7 +3764,7 @@
         <v>20.06382979</v>
       </c>
       <c r="V23" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W23">
         <v>-0.015248</v>
@@ -3754,10 +3793,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>44940.34714877315</v>
@@ -3775,13 +3814,13 @@
         <v>607</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K24">
         <v>92</v>
@@ -3805,7 +3844,7 @@
         <v>19</v>
       </c>
       <c r="V24" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W24">
         <v>-0.531915</v>
@@ -3834,10 +3873,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>44940.34748677084</v>
@@ -3855,13 +3894,13 @@
         <v>647</v>
       </c>
       <c r="H25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I25" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K25">
         <v>86</v>
@@ -3885,7 +3924,7 @@
         <v>23.05</v>
       </c>
       <c r="V25" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W25">
         <v>0.10125</v>
@@ -3914,10 +3953,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>44940.34783131944</v>
@@ -3935,13 +3974,13 @@
         <v>671</v>
       </c>
       <c r="H26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I26" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J26" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K26">
         <v>98</v>
@@ -3965,7 +4004,7 @@
         <v>22.125</v>
       </c>
       <c r="V26" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W26">
         <v>-0.038542</v>
@@ -3994,10 +4033,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>44940.34812273148</v>
@@ -4015,13 +4054,13 @@
         <v>673</v>
       </c>
       <c r="H27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4045,7 +4084,7 @@
         <v>18.5</v>
       </c>
       <c r="V27" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W27">
         <v>-1.8125</v>
@@ -4074,10 +4113,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2">
         <v>44940.34845848379</v>
@@ -4095,13 +4134,13 @@
         <v>738</v>
       </c>
       <c r="H28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I28" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K28">
         <v>89</v>
@@ -4125,7 +4164,7 @@
         <v>18.44615385</v>
       </c>
       <c r="V28" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W28">
         <v>-0.000828</v>
@@ -4154,10 +4193,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2">
         <v>44940.34880458334</v>
@@ -4175,13 +4214,13 @@
         <v>762</v>
       </c>
       <c r="H29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J29" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K29">
         <v>81</v>
@@ -4205,7 +4244,7 @@
         <v>19.95833333</v>
       </c>
       <c r="V29" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W29">
         <v>0.06300699999999999</v>
@@ -4234,10 +4273,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>44940.349095625</v>
@@ -4255,13 +4294,13 @@
         <v>763</v>
       </c>
       <c r="H30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J30" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K30">
         <v>85</v>
@@ -4285,7 +4324,7 @@
         <v>19</v>
       </c>
       <c r="V30" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W30">
         <v>-0.958333</v>
@@ -4314,10 +4353,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>44940.3494306713</v>
@@ -4335,13 +4374,13 @@
         <v>828</v>
       </c>
       <c r="H31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J31" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K31">
         <v>75</v>
@@ -4365,7 +4404,7 @@
         <v>22.52307692</v>
       </c>
       <c r="V31" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W31">
         <v>0.054201</v>
@@ -4394,10 +4433,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>44940.34977787037</v>
@@ -4415,13 +4454,13 @@
         <v>851</v>
       </c>
       <c r="H32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K32">
         <v>79</v>
@@ -4445,7 +4484,7 @@
         <v>16.2173913</v>
       </c>
       <c r="V32" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W32">
         <v>-0.27416</v>
@@ -4474,10 +4513,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2">
         <v>44940.35006822916</v>
@@ -4495,13 +4534,13 @@
         <v>853</v>
       </c>
       <c r="H33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I33" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K33">
         <v>77</v>
@@ -4525,7 +4564,7 @@
         <v>8</v>
       </c>
       <c r="V33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W33">
         <v>-4.108696</v>
@@ -4554,10 +4593,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2">
         <v>44940.35040363426</v>
@@ -4575,13 +4614,13 @@
         <v>893</v>
       </c>
       <c r="H34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J34" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K34">
         <v>67</v>
@@ -4605,7 +4644,7 @@
         <v>14.725</v>
       </c>
       <c r="V34" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W34">
         <v>0.168125</v>
@@ -4634,10 +4673,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2">
         <v>44940.35075162037</v>
@@ -4655,13 +4694,13 @@
         <v>942</v>
       </c>
       <c r="H35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K35">
         <v>61</v>
@@ -4685,7 +4724,7 @@
         <v>21.02040816</v>
       </c>
       <c r="V35" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W35">
         <v>0.128478</v>
@@ -4714,10 +4753,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>44940.35104189815</v>
@@ -4735,13 +4774,13 @@
         <v>944</v>
       </c>
       <c r="H36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J36" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K36">
         <v>63</v>
@@ -4765,7 +4804,7 @@
         <v>26</v>
       </c>
       <c r="V36" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W36">
         <v>2.489796</v>
@@ -4794,10 +4833,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>44940.35137795139</v>
@@ -4815,13 +4854,13 @@
         <v>985</v>
       </c>
       <c r="H37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J37" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K37">
         <v>60</v>
@@ -4845,7 +4884,7 @@
         <v>24.65853659</v>
       </c>
       <c r="V37" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W37">
         <v>-0.032719</v>
@@ -4874,10 +4913,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>44940.35172524305</v>
@@ -4895,13 +4934,13 @@
         <v>1008</v>
       </c>
       <c r="H38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I38" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J38" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K38">
         <v>58</v>
@@ -4925,7 +4964,7 @@
         <v>23.95652174</v>
       </c>
       <c r="V38" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W38">
         <v>-0.030522</v>
@@ -4954,10 +4993,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
         <v>44940.35201546297</v>
@@ -4975,13 +5014,13 @@
         <v>1009</v>
       </c>
       <c r="H39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I39" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J39" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K39">
         <v>57</v>
@@ -5005,7 +5044,7 @@
         <v>29</v>
       </c>
       <c r="V39" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W39">
         <v>5.043478</v>
@@ -5034,10 +5073,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>44940.35235122685</v>
@@ -5055,13 +5094,13 @@
         <v>1075</v>
       </c>
       <c r="H40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I40" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J40" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K40">
         <v>56</v>
@@ -5085,7 +5124,7 @@
         <v>25.25757576</v>
       </c>
       <c r="V40" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W40">
         <v>-0.056703</v>
@@ -5114,10 +5153,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>44940.35269846065</v>
@@ -5135,13 +5174,13 @@
         <v>1098</v>
       </c>
       <c r="H41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I41" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J41" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K41">
         <v>58</v>
@@ -5165,7 +5204,7 @@
         <v>23.56521739</v>
       </c>
       <c r="V41" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W41">
         <v>-0.07358099999999999</v>
@@ -5194,10 +5233,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>44940.35298905092</v>
@@ -5215,13 +5254,13 @@
         <v>1100</v>
       </c>
       <c r="H42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I42" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J42" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K42">
         <v>59</v>
@@ -5245,7 +5284,7 @@
         <v>30.5</v>
       </c>
       <c r="V42" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W42">
         <v>3.467391</v>
@@ -5274,10 +5313,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>44940.35332460648</v>
@@ -5295,13 +5334,13 @@
         <v>1141</v>
       </c>
       <c r="H43" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I43" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J43" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K43">
         <v>59</v>
@@ -5325,7 +5364,7 @@
         <v>25.09756098</v>
       </c>
       <c r="V43" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W43">
         <v>-0.131767</v>
@@ -5354,10 +5393,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" s="2">
         <v>44940.35367141203</v>
@@ -5375,13 +5414,13 @@
         <v>1190</v>
       </c>
       <c r="H44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I44" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J44" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K44">
         <v>65</v>
@@ -5405,7 +5444,7 @@
         <v>22.73469388</v>
       </c>
       <c r="V44" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W44">
         <v>-0.048222</v>
@@ -5434,10 +5473,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2">
         <v>44940.35396269676</v>
@@ -5455,13 +5494,13 @@
         <v>1191</v>
       </c>
       <c r="H45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I45" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J45" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K45">
         <v>66</v>
@@ -5485,7 +5524,7 @@
         <v>24</v>
       </c>
       <c r="V45" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W45">
         <v>1.265306</v>
@@ -5514,10 +5553,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>44940.35429768518</v>
@@ -5535,13 +5574,13 @@
         <v>1232</v>
       </c>
       <c r="H46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I46" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J46" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K46">
         <v>59</v>
@@ -5565,7 +5604,7 @@
         <v>24</v>
       </c>
       <c r="V46" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -5594,10 +5633,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
         <v>44940.35464509259</v>
@@ -5615,13 +5654,13 @@
         <v>1255</v>
       </c>
       <c r="H47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I47" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J47" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K47">
         <v>60</v>
@@ -5645,7 +5684,7 @@
         <v>26.91304348</v>
       </c>
       <c r="V47" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W47">
         <v>0.126654</v>
@@ -5674,10 +5713,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C48" s="2">
         <v>44940.35493649306</v>
@@ -5695,13 +5734,13 @@
         <v>1257</v>
       </c>
       <c r="H48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J48" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K48">
         <v>61</v>
@@ -5725,7 +5764,7 @@
         <v>25.5</v>
       </c>
       <c r="V48" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W48">
         <v>-0.706522</v>
@@ -5754,10 +5793,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2">
         <v>44940.35527100694</v>
@@ -5775,13 +5814,13 @@
         <v>1323</v>
       </c>
       <c r="H49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I49" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J49" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K49">
         <v>49</v>
@@ -5805,7 +5844,7 @@
         <v>26.6969697</v>
       </c>
       <c r="V49" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W49">
         <v>0.018136</v>
@@ -5834,10 +5873,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>44940.35561853009</v>
@@ -5855,13 +5894,13 @@
         <v>1346</v>
       </c>
       <c r="H50" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I50" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J50" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K50">
         <v>56</v>
@@ -5885,7 +5924,7 @@
         <v>27.30434783</v>
       </c>
       <c r="V50" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W50">
         <v>0.026408</v>
@@ -5914,10 +5953,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2">
         <v>44940.35590945602</v>
@@ -5935,13 +5974,13 @@
         <v>1348</v>
       </c>
       <c r="H51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I51" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J51" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K51">
         <v>57</v>
@@ -5965,7 +6004,7 @@
         <v>18.5</v>
       </c>
       <c r="V51" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W51">
         <v>-4.402174</v>
@@ -5994,10 +6033,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>44940.35624493055</v>
@@ -6015,13 +6054,13 @@
         <v>1414</v>
       </c>
       <c r="H52" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I52" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J52" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K52">
         <v>53</v>
@@ -6045,7 +6084,7 @@
         <v>24.36363636</v>
       </c>
       <c r="V52" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W52">
         <v>0.08884300000000001</v>
@@ -6074,10 +6113,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2">
         <v>44940.3565925</v>
@@ -6095,13 +6134,13 @@
         <v>1437</v>
       </c>
       <c r="H53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I53" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J53" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K53">
         <v>56</v>
@@ -6125,7 +6164,7 @@
         <v>27.17391304</v>
       </c>
       <c r="V53" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W53">
         <v>0.122186</v>
@@ -6154,10 +6193,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>44940.35688671297</v>
@@ -6175,13 +6214,13 @@
         <v>1439</v>
       </c>
       <c r="H54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I54" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J54" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K54">
         <v>54</v>
@@ -6205,7 +6244,7 @@
         <v>21</v>
       </c>
       <c r="V54" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W54">
         <v>-3.086957</v>
@@ -6234,10 +6273,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C55" s="2">
         <v>44940.35721751158</v>
@@ -6255,13 +6294,13 @@
         <v>1479</v>
       </c>
       <c r="H55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I55" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J55" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K55">
         <v>58</v>
@@ -6285,7 +6324,7 @@
         <v>27.475</v>
       </c>
       <c r="V55" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W55">
         <v>0.161875</v>
@@ -6314,10 +6353,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>44940.3575658912</v>
@@ -6335,13 +6374,13 @@
         <v>1526</v>
       </c>
       <c r="H56" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I56" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J56" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K56">
         <v>64</v>
@@ -6365,7 +6404,7 @@
         <v>26.38297872</v>
       </c>
       <c r="V56" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W56">
         <v>-0.023234</v>
@@ -6394,10 +6433,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C57" s="2">
         <v>44940.35785689815</v>
@@ -6415,13 +6454,13 @@
         <v>1528</v>
       </c>
       <c r="H57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I57" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K57">
         <v>65</v>
@@ -6445,7 +6484,7 @@
         <v>26.5</v>
       </c>
       <c r="V57" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W57">
         <v>0.058511</v>
@@ -6474,10 +6513,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2">
         <v>44940.35819158565</v>
@@ -6495,13 +6534,13 @@
         <v>1569</v>
       </c>
       <c r="H58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J58" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K58">
         <v>64</v>
@@ -6525,7 +6564,7 @@
         <v>24.87804878</v>
       </c>
       <c r="V58" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W58">
         <v>-0.03956</v>
@@ -6554,10 +6593,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2">
         <v>44940.35853839121</v>
@@ -6575,13 +6614,13 @@
         <v>1592</v>
       </c>
       <c r="H59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I59" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J59" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K59">
         <v>61</v>
@@ -6605,7 +6644,7 @@
         <v>24.69565217</v>
       </c>
       <c r="V59" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W59">
         <v>-0.00793</v>
@@ -6634,10 +6673,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2">
         <v>44940.35883177083</v>
@@ -6655,13 +6694,13 @@
         <v>1594</v>
       </c>
       <c r="H60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J60" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K60">
         <v>60</v>
@@ -6685,7 +6724,7 @@
         <v>22</v>
       </c>
       <c r="V60" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W60">
         <v>-1.347826</v>
@@ -6714,10 +6753,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
         <v>44940.35916414352</v>
@@ -6735,13 +6774,13 @@
         <v>1658</v>
       </c>
       <c r="H61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I61" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J61" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K61">
         <v>71</v>
@@ -6765,7 +6804,7 @@
         <v>23.328125</v>
       </c>
       <c r="V61" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W61">
         <v>0.020752</v>
@@ -6794,10 +6833,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
         <v>44940.35951258102</v>
@@ -6815,13 +6854,13 @@
         <v>1682</v>
       </c>
       <c r="H62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I62" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J62" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K62">
         <v>72</v>
@@ -6845,7 +6884,7 @@
         <v>24.75</v>
       </c>
       <c r="V62" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W62">
         <v>0.059245</v>
@@ -6874,10 +6913,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>44940.35980234954</v>
@@ -6895,13 +6934,13 @@
         <v>1684</v>
       </c>
       <c r="H63" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J63" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K63">
         <v>75</v>
@@ -6925,7 +6964,7 @@
         <v>22.5</v>
       </c>
       <c r="V63" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W63">
         <v>-1.125</v>
@@ -6954,10 +6993,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
         <v>44940.36013804398</v>
@@ -6975,13 +7014,13 @@
         <v>1750</v>
       </c>
       <c r="H64" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I64" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J64" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K64">
         <v>77</v>
@@ -7005,7 +7044,7 @@
         <v>26.98484848</v>
       </c>
       <c r="V64" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W64">
         <v>0.067952</v>
@@ -7034,10 +7073,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C65" s="2">
         <v>44940.36048796296</v>
@@ -7055,13 +7094,13 @@
         <v>1774</v>
       </c>
       <c r="H65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I65" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J65" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K65">
         <v>72</v>
@@ -7085,7 +7124,7 @@
         <v>23.125</v>
       </c>
       <c r="V65" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W65">
         <v>-0.160827</v>
@@ -7114,10 +7153,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2">
         <v>44940.36076875</v>
@@ -7135,13 +7174,13 @@
         <v>1775</v>
       </c>
       <c r="H66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I66" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J66" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K66">
         <v>71</v>
@@ -7165,7 +7204,7 @@
         <v>24</v>
       </c>
       <c r="V66" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W66">
         <v>0.875</v>
@@ -7194,10 +7233,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2">
         <v>44940.36110262731</v>
@@ -7215,13 +7254,13 @@
         <v>1815</v>
       </c>
       <c r="H67" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I67" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J67" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K67">
         <v>58</v>
@@ -7245,7 +7284,7 @@
         <v>26.35</v>
       </c>
       <c r="V67" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W67">
         <v>0.05875</v>
@@ -7274,10 +7313,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2">
         <v>44940.36144950231</v>
@@ -7295,13 +7334,13 @@
         <v>1864</v>
       </c>
       <c r="H68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I68" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J68" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K68">
         <v>85</v>
@@ -7325,7 +7364,7 @@
         <v>24.48979592</v>
       </c>
       <c r="V68" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W68">
         <v>-0.037963</v>
@@ -7354,10 +7393,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2">
         <v>44940.36174215277</v>
@@ -7375,13 +7414,13 @@
         <v>1865</v>
       </c>
       <c r="H69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I69" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J69" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K69">
         <v>85</v>
@@ -7405,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="V69" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="W69">
         <v>2.510204</v>
@@ -7434,10 +7473,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C70" s="2">
         <v>44940.3620759375</v>
@@ -7455,13 +7494,13 @@
         <v>1906</v>
       </c>
       <c r="H70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I70" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J70" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K70">
         <v>92</v>
@@ -7485,7 +7524,7 @@
         <v>21.90243902</v>
       </c>
       <c r="V70" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W70">
         <v>-0.124331</v>
@@ -7514,10 +7553,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C71" s="2">
         <v>44940.36242248843</v>
@@ -7535,13 +7574,13 @@
         <v>1930</v>
       </c>
       <c r="H71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I71" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J71" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K71">
         <v>87</v>
@@ -7565,7 +7604,7 @@
         <v>16.66666667</v>
       </c>
       <c r="V71" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W71">
         <v>-0.218157</v>
@@ -7594,10 +7633,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C72" s="2">
         <v>44940.36271908565</v>
@@ -7615,13 +7654,13 @@
         <v>1932</v>
       </c>
       <c r="H72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I72" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J72" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K72">
         <v>86</v>
@@ -7645,7 +7684,7 @@
         <v>17</v>
       </c>
       <c r="V72" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W72">
         <v>0.166667</v>
@@ -7674,10 +7713,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C73" s="2">
         <v>44940.36304903936</v>
@@ -7695,13 +7734,13 @@
         <v>1998</v>
       </c>
       <c r="H73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I73" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J73" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K73">
         <v>71</v>
@@ -7725,7 +7764,7 @@
         <v>16.8030303</v>
       </c>
       <c r="V73" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W73">
         <v>-0.002984</v>
@@ -7754,10 +7793,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C74" s="2">
         <v>44940.36339696759</v>
@@ -7775,13 +7814,13 @@
         <v>2022</v>
       </c>
       <c r="H74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I74" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J74" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K74">
         <v>81</v>
@@ -7805,7 +7844,7 @@
         <v>17.91666667</v>
       </c>
       <c r="V74" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W74">
         <v>0.046402</v>
@@ -7834,10 +7873,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2">
         <v>44940.36368710648</v>
@@ -7855,13 +7894,13 @@
         <v>2024</v>
       </c>
       <c r="H75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I75" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J75" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K75">
         <v>84</v>
@@ -7885,7 +7924,7 @@
         <v>16</v>
       </c>
       <c r="V75" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W75">
         <v>-0.958333</v>
@@ -7914,10 +7953,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C76" s="2">
         <v>44940.36402215277</v>
@@ -7935,13 +7974,13 @@
         <v>2065</v>
       </c>
       <c r="H76" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I76" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J76" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K76">
         <v>109</v>
@@ -7965,7 +8004,7 @@
         <v>23.12195122</v>
       </c>
       <c r="V76" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W76">
         <v>0.173706</v>
@@ -7994,10 +8033,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C77" s="2">
         <v>44940.36436971065</v>
@@ -8015,13 +8054,13 @@
         <v>2113</v>
       </c>
       <c r="H77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I77" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J77" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K77">
         <v>81</v>
@@ -8045,7 +8084,7 @@
         <v>20.79166667</v>
       </c>
       <c r="V77" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W77">
         <v>-0.048548</v>
@@ -8074,10 +8113,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C78" s="2">
         <v>44940.36466076389</v>
@@ -8095,13 +8134,13 @@
         <v>2115</v>
       </c>
       <c r="H78" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I78" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J78" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K78">
         <v>81</v>
@@ -8125,7 +8164,7 @@
         <v>20</v>
       </c>
       <c r="V78" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W78">
         <v>-0.395833</v>
@@ -8154,10 +8193,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C79" s="2">
         <v>44940.36499581019</v>
@@ -8175,13 +8214,13 @@
         <v>2156</v>
       </c>
       <c r="H79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I79" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J79" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K79">
         <v>90</v>
@@ -8205,7 +8244,7 @@
         <v>17.97560976</v>
       </c>
       <c r="V79" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W79">
         <v>-0.049375</v>
@@ -8234,10 +8273,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C80" s="2">
         <v>44940.36534358796</v>
@@ -8255,13 +8294,13 @@
         <v>2180</v>
       </c>
       <c r="H80" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J80" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K80">
         <v>105</v>
@@ -8285,7 +8324,7 @@
         <v>20.5</v>
       </c>
       <c r="V80" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W80">
         <v>0.105183</v>
@@ -8314,10 +8353,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C81" s="2">
         <v>44940.36563915509</v>
@@ -8335,13 +8374,13 @@
         <v>2182</v>
       </c>
       <c r="H81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I81" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J81" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K81">
         <v>99</v>
@@ -8365,7 +8404,7 @@
         <v>21</v>
       </c>
       <c r="V81" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W81">
         <v>0.25</v>
@@ -8394,10 +8433,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C82" s="2">
         <v>44940.36597112269</v>
@@ -8415,13 +8454,13 @@
         <v>2247</v>
       </c>
       <c r="H82" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J82" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K82">
         <v>119</v>
@@ -8445,7 +8484,7 @@
         <v>24.24615385</v>
       </c>
       <c r="V82" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W82">
         <v>0.049941</v>
@@ -8474,10 +8513,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C83" s="2">
         <v>44940.3663169213</v>
@@ -8495,13 +8534,13 @@
         <v>2271</v>
       </c>
       <c r="H83" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I83" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J83" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K83">
         <v>79</v>
@@ -8525,7 +8564,7 @@
         <v>19.70833333</v>
       </c>
       <c r="V83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W83">
         <v>-0.189076</v>
@@ -8554,10 +8593,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C84" s="2">
         <v>44940.36660665509</v>
@@ -8575,13 +8614,13 @@
         <v>2273</v>
       </c>
       <c r="H84" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I84" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J84" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K84">
         <v>73</v>
@@ -8605,7 +8644,7 @@
         <v>16.5</v>
       </c>
       <c r="V84" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W84">
         <v>-1.604167</v>
@@ -8634,10 +8673,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C85" s="2">
         <v>44940.36694467592</v>
@@ -8655,13 +8694,13 @@
         <v>2339</v>
       </c>
       <c r="H85" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I85" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J85" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K85">
         <v>59</v>
@@ -8685,7 +8724,7 @@
         <v>19.36363636</v>
       </c>
       <c r="V85" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W85">
         <v>0.043388</v>
@@ -8714,10 +8753,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C86" s="2">
         <v>44940.36729467593</v>
@@ -8735,13 +8774,13 @@
         <v>2362</v>
       </c>
       <c r="H86" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I86" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J86" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K86">
         <v>75</v>
@@ -8765,7 +8804,7 @@
         <v>15.86956522</v>
       </c>
       <c r="V86" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W86">
         <v>-0.151916</v>
@@ -8794,10 +8833,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C87" s="2">
         <v>44940.36757986111</v>
@@ -8815,13 +8854,13 @@
         <v>2364</v>
       </c>
       <c r="H87" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I87" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J87" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K87">
         <v>71</v>
@@ -8845,7 +8884,7 @@
         <v>16.5</v>
       </c>
       <c r="V87" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W87">
         <v>0.315217</v>
@@ -8874,10 +8913,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2">
         <v>44940.36791641204</v>
@@ -8895,13 +8934,13 @@
         <v>2405</v>
       </c>
       <c r="H88" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I88" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J88" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K88">
         <v>80</v>
@@ -8925,7 +8964,7 @@
         <v>15.56097561</v>
       </c>
       <c r="V88" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W88">
         <v>-0.022903</v>
@@ -8954,10 +8993,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C89" s="2">
         <v>44940.36826293982</v>
@@ -8975,13 +9014,13 @@
         <v>2453</v>
       </c>
       <c r="H89" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I89" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J89" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K89">
         <v>77</v>
@@ -9005,7 +9044,7 @@
         <v>16.3125</v>
       </c>
       <c r="V89" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W89">
         <v>0.015657</v>
@@ -9034,10 +9073,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C90" s="2">
         <v>44940.36855534722</v>
@@ -9055,13 +9094,13 @@
         <v>2455</v>
       </c>
       <c r="H90" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I90" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J90" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K90">
         <v>78</v>
@@ -9085,7 +9124,7 @@
         <v>16.5</v>
       </c>
       <c r="V90" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W90">
         <v>0.09375</v>
@@ -9114,10 +9153,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C91" s="2">
         <v>44940.36888913195</v>
@@ -9135,13 +9174,13 @@
         <v>2496</v>
       </c>
       <c r="H91" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I91" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J91" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K91">
         <v>90</v>
@@ -9165,7 +9204,7 @@
         <v>16.58536585</v>
       </c>
       <c r="V91" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W91">
         <v>0.002082</v>
@@ -9194,10 +9233,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C92" s="2">
         <v>44940.36923621528</v>
@@ -9215,13 +9254,13 @@
         <v>2520</v>
       </c>
       <c r="H92" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I92" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J92" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K92">
         <v>102</v>
@@ -9245,7 +9284,7 @@
         <v>17.79166667</v>
       </c>
       <c r="V92" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W92">
         <v>0.050263</v>
@@ -9274,10 +9313,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C93" s="2">
         <v>44940.36952689815</v>
@@ -9295,13 +9334,13 @@
         <v>2521</v>
       </c>
       <c r="H93" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I93" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J93" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K93">
         <v>106</v>
@@ -9325,7 +9364,7 @@
         <v>14</v>
       </c>
       <c r="V93" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W93">
         <v>-3.791667</v>
@@ -9354,10 +9393,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C94" s="2">
         <v>44940.36986238426</v>
@@ -9375,13 +9414,13 @@
         <v>2586</v>
       </c>
       <c r="H94" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I94" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J94" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K94">
         <v>121</v>
@@ -9405,7 +9444,7 @@
         <v>20.95384615</v>
       </c>
       <c r="V94" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W94">
         <v>0.106982</v>
@@ -9434,10 +9473,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C95" s="2">
         <v>44940.37021008102</v>
@@ -9455,13 +9494,13 @@
         <v>2610</v>
       </c>
       <c r="H95" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I95" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J95" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K95">
         <v>139</v>
@@ -9485,7 +9524,7 @@
         <v>20.54166667</v>
       </c>
       <c r="V95" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W95">
         <v>-0.017174</v>
@@ -9514,10 +9553,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C96" s="2">
         <v>44940.37050086806</v>
@@ -9535,13 +9574,13 @@
         <v>2611</v>
       </c>
       <c r="H96" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I96" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J96" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K96">
         <v>140</v>
@@ -9565,7 +9604,7 @@
         <v>15</v>
       </c>
       <c r="V96" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W96">
         <v>-5.541667</v>
@@ -9594,10 +9633,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C97" s="2">
         <v>44940.37083533565</v>
@@ -9615,13 +9654,13 @@
         <v>2677</v>
       </c>
       <c r="H97" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I97" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J97" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K97">
         <v>124</v>
@@ -9645,7 +9684,7 @@
         <v>21.1969697</v>
       </c>
       <c r="V97" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W97">
         <v>0.093893</v>
@@ -9674,10 +9713,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C98" s="2">
         <v>44940.3711837963</v>
@@ -9695,13 +9734,13 @@
         <v>2700</v>
       </c>
       <c r="H98" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I98" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J98" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K98">
         <v>127</v>
@@ -9725,7 +9764,7 @@
         <v>20.43478261</v>
       </c>
       <c r="V98" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W98">
         <v>-0.033139</v>
@@ -9754,10 +9793,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C99" s="2">
         <v>44940.371474375</v>
@@ -9775,13 +9814,13 @@
         <v>2702</v>
       </c>
       <c r="H99" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I99" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J99" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K99">
         <v>129</v>
@@ -9805,7 +9844,7 @@
         <v>16.5</v>
       </c>
       <c r="V99" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W99">
         <v>-1.967391</v>
@@ -9834,10 +9873,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C100" s="2">
         <v>44940.37180888889</v>
@@ -9855,13 +9894,13 @@
         <v>2744</v>
       </c>
       <c r="H100" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I100" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J100" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K100">
         <v>122</v>
@@ -9885,7 +9924,7 @@
         <v>16.47619048</v>
       </c>
       <c r="V100" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W100">
         <v>-0.000567</v>
@@ -9914,10 +9953,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C101" s="2">
         <v>44940.37215681713</v>
@@ -9935,13 +9974,13 @@
         <v>2767</v>
       </c>
       <c r="H101" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I101" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J101" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K101">
         <v>117</v>
@@ -9965,7 +10004,7 @@
         <v>17</v>
       </c>
       <c r="V101" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W101">
         <v>0.022774</v>
@@ -9994,10 +10033,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C102" s="2">
         <v>44940.37244690972</v>
@@ -10015,13 +10054,13 @@
         <v>2793</v>
       </c>
       <c r="H102" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I102" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J102" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K102">
         <v>120</v>
@@ -10045,7 +10084,7 @@
         <v>18.15384615</v>
       </c>
       <c r="V102" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W102">
         <v>0.044379</v>
@@ -10074,10 +10113,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C103" s="2">
         <v>44940.37278292824</v>
@@ -10095,13 +10134,13 @@
         <v>2834</v>
       </c>
       <c r="H103" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I103" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J103" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K103">
         <v>156</v>
@@ -10125,7 +10164,7 @@
         <v>17.31707317</v>
       </c>
       <c r="V103" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W103">
         <v>-0.020409</v>
@@ -10154,10 +10193,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C104" s="2">
         <v>44940.37312947917</v>
@@ -10175,13 +10214,13 @@
         <v>2858</v>
       </c>
       <c r="H104" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I104" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J104" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K104">
         <v>120</v>
@@ -10205,7 +10244,7 @@
         <v>16.625</v>
       </c>
       <c r="V104" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W104">
         <v>-0.028836</v>
@@ -10234,10 +10273,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C105" s="2">
         <v>44940.37342081019</v>
@@ -10255,13 +10294,13 @@
         <v>2860</v>
       </c>
       <c r="H105" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I105" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J105" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K105">
         <v>113</v>
@@ -10285,7 +10324,7 @@
         <v>19</v>
       </c>
       <c r="V105" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W105">
         <v>1.1875</v>
@@ -10314,10 +10353,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C106" s="2">
         <v>44940.37375604167</v>
@@ -10335,13 +10374,13 @@
         <v>2925</v>
       </c>
       <c r="H106" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I106" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J106" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K106">
         <v>169</v>
@@ -10365,7 +10404,7 @@
         <v>15.50769231</v>
       </c>
       <c r="V106" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W106">
         <v>-0.053728</v>
@@ -10394,10 +10433,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C107" s="2">
         <v>44940.37410366898</v>
@@ -10415,13 +10454,13 @@
         <v>2949</v>
       </c>
       <c r="H107" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I107" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J107" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K107">
         <v>128</v>
@@ -10445,7 +10484,7 @@
         <v>17.125</v>
       </c>
       <c r="V107" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W107">
         <v>0.067388</v>
@@ -10474,10 +10513,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C108" s="2">
         <v>44940.37439447916</v>
@@ -10495,13 +10534,13 @@
         <v>2950</v>
       </c>
       <c r="H108" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I108" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J108" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K108">
         <v>125</v>
@@ -10525,7 +10564,7 @@
         <v>15</v>
       </c>
       <c r="V108" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W108">
         <v>-2.125</v>
@@ -10554,10 +10593,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C109" s="2">
         <v>44940.37472954861</v>
@@ -10575,13 +10614,13 @@
         <v>2991</v>
       </c>
       <c r="H109" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I109" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J109" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K109">
         <v>87</v>
@@ -10605,7 +10644,7 @@
         <v>16.24390244</v>
       </c>
       <c r="V109" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W109">
         <v>0.030339</v>
@@ -10634,10 +10673,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C110" s="2">
         <v>44940.3750762037</v>
@@ -10655,13 +10694,13 @@
         <v>3039</v>
       </c>
       <c r="H110" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I110" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J110" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K110">
         <v>155</v>
@@ -10685,7 +10724,7 @@
         <v>16.625</v>
       </c>
       <c r="V110" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W110">
         <v>0.007939999999999999</v>
@@ -10714,10 +10753,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C111" s="2">
         <v>44940.37536677083</v>
@@ -10735,13 +10774,13 @@
         <v>3040</v>
       </c>
       <c r="H111" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I111" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J111" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K111">
         <v>154</v>
@@ -10765,7 +10804,7 @@
         <v>17</v>
       </c>
       <c r="V111" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W111">
         <v>0.375</v>
@@ -10794,10 +10833,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C112" s="2">
         <v>44940.37570267361</v>
@@ -10815,13 +10854,13 @@
         <v>3081</v>
       </c>
       <c r="H112" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I112" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J112" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K112">
         <v>185</v>
@@ -10845,7 +10884,7 @@
         <v>16.12195122</v>
       </c>
       <c r="V112" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W112">
         <v>-0.021416</v>
@@ -10874,10 +10913,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C113" s="2">
         <v>44940.37605122685</v>
@@ -10895,13 +10934,13 @@
         <v>3105</v>
       </c>
       <c r="H113" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I113" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J113" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K113">
         <v>244</v>
@@ -10925,7 +10964,7 @@
         <v>14.125</v>
       </c>
       <c r="V113" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W113">
         <v>-0.083206</v>
@@ -10954,10 +10993,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C114" s="2">
         <v>44940.37634334491</v>
@@ -10975,13 +11014,13 @@
         <v>3107</v>
       </c>
       <c r="H114" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I114" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J114" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K114">
         <v>236</v>
@@ -11005,7 +11044,7 @@
         <v>6.5</v>
       </c>
       <c r="V114" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W114">
         <v>-3.8125</v>
@@ -11034,10 +11073,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C115" s="2">
         <v>44940.37667689815</v>
@@ -11055,13 +11094,13 @@
         <v>3171</v>
       </c>
       <c r="H115" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I115" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J115" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K115">
         <v>216</v>
@@ -11085,7 +11124,7 @@
         <v>16.859375</v>
       </c>
       <c r="V115" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W115">
         <v>0.161865</v>
@@ -11114,10 +11153,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C116" s="2">
         <v>44940.37702810185</v>
@@ -11135,13 +11174,13 @@
         <v>3195</v>
       </c>
       <c r="H116" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I116" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J116" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K116">
         <v>110</v>
@@ -11165,7 +11204,7 @@
         <v>17.58333333</v>
       </c>
       <c r="V116" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W116">
         <v>0.030165</v>
@@ -11194,10 +11233,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C117" s="2">
         <v>44940.37731377315</v>
@@ -11215,13 +11254,13 @@
         <v>3196</v>
       </c>
       <c r="H117" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I117" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J117" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K117">
         <v>107</v>
@@ -11245,7 +11284,7 @@
         <v>17</v>
       </c>
       <c r="V117" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W117">
         <v>-0.583333</v>
@@ -11274,10 +11313,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C118" s="2">
         <v>44940.37764974537</v>
@@ -11295,13 +11334,13 @@
         <v>3260</v>
       </c>
       <c r="H118" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I118" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J118" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K118">
         <v>184</v>
@@ -11325,7 +11364,7 @@
         <v>18.640625</v>
       </c>
       <c r="V118" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W118">
         <v>0.025635</v>
@@ -11354,10 +11393,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C119" s="2">
         <v>44940.37799662037</v>
@@ -11375,13 +11414,13 @@
         <v>3284</v>
       </c>
       <c r="H119" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I119" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J119" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K119">
         <v>173</v>
@@ -11405,7 +11444,7 @@
         <v>17.04166667</v>
       </c>
       <c r="V119" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W119">
         <v>-0.066623</v>
@@ -11434,10 +11473,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C120" s="2">
         <v>44940.37828671296</v>
@@ -11455,13 +11494,13 @@
         <v>3286</v>
       </c>
       <c r="H120" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I120" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J120" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K120">
         <v>177</v>
@@ -11485,7 +11524,7 @@
         <v>15</v>
       </c>
       <c r="V120" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W120">
         <v>-1.020833</v>
@@ -11514,10 +11553,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C121" s="2">
         <v>44940.37862175926</v>
@@ -11535,13 +11574,13 @@
         <v>3350</v>
       </c>
       <c r="H121" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I121" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J121" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K121">
         <v>198</v>
@@ -11565,7 +11604,7 @@
         <v>16.6875</v>
       </c>
       <c r="V121" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W121">
         <v>0.026367</v>
@@ -11594,10 +11633,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C122" s="2">
         <v>44940.37897061343</v>
@@ -11615,13 +11654,13 @@
         <v>3372</v>
       </c>
       <c r="H122" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I122" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J122" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K122">
         <v>172</v>
@@ -11645,7 +11684,7 @@
         <v>16.68181818</v>
       </c>
       <c r="V122" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W122">
         <v>-0.000258</v>
@@ -11674,10 +11713,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C123" s="2">
         <v>44940.37926053241</v>
@@ -11695,13 +11734,13 @@
         <v>3374</v>
       </c>
       <c r="H123" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I123" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J123" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K123">
         <v>166</v>
@@ -11725,7 +11764,7 @@
         <v>17</v>
       </c>
       <c r="V123" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W123">
         <v>0.159091</v>
@@ -11754,10 +11793,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C124" s="2">
         <v>44940.37959600695</v>
@@ -11775,13 +11814,13 @@
         <v>3414</v>
       </c>
       <c r="H124" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I124" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J124" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K124">
         <v>182</v>
@@ -11805,7 +11844,7 @@
         <v>17.225</v>
       </c>
       <c r="V124" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W124">
         <v>0.005625</v>
@@ -11834,10 +11873,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C125" s="2">
         <v>44940.37994346065</v>
@@ -11855,13 +11894,13 @@
         <v>3461</v>
       </c>
       <c r="H125" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I125" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J125" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K125">
         <v>177</v>
@@ -11885,7 +11924,7 @@
         <v>16.0212766</v>
       </c>
       <c r="V125" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W125">
         <v>-0.025611</v>
@@ -11914,10 +11953,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C126" s="2">
         <v>44940.38023311343</v>
@@ -11935,13 +11974,13 @@
         <v>3463</v>
       </c>
       <c r="H126" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I126" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J126" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K126">
         <v>171</v>
@@ -11965,7 +12004,7 @@
         <v>15.5</v>
       </c>
       <c r="V126" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W126">
         <v>-0.260638</v>
@@ -11994,10 +12033,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C127" s="2">
         <v>44940.38056954861</v>
@@ -12015,13 +12054,13 @@
         <v>3504</v>
       </c>
       <c r="H127" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I127" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J127" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K127">
         <v>179</v>
@@ -12045,7 +12084,7 @@
         <v>17.36585366</v>
       </c>
       <c r="V127" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W127">
         <v>0.045509</v>
@@ -12074,10 +12113,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C128" s="2">
         <v>44940.38091631945</v>
@@ -12095,13 +12134,13 @@
         <v>3527</v>
       </c>
       <c r="H128" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I128" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J128" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K128">
         <v>176</v>
@@ -12125,7 +12164,7 @@
         <v>17.17391304</v>
       </c>
       <c r="V128" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W128">
         <v>-0.008345</v>
@@ -12154,10 +12193,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C129" s="2">
         <v>44940.38120711806</v>
@@ -12175,13 +12214,13 @@
         <v>3529</v>
       </c>
       <c r="H129" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I129" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J129" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K129">
         <v>173</v>
@@ -12205,7 +12244,7 @@
         <v>16</v>
       </c>
       <c r="V129" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W129">
         <v>-0.586957</v>
@@ -12234,10 +12273,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C130" s="2">
         <v>44940.38155128472</v>
@@ -12255,13 +12294,13 @@
         <v>3594</v>
       </c>
       <c r="H130" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I130" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J130" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K130">
         <v>173</v>
@@ -12285,7 +12324,7 @@
         <v>17.66153846</v>
       </c>
       <c r="V130" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W130">
         <v>0.025562</v>
@@ -12314,10 +12353,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C131" s="2">
         <v>44940.38189346065</v>
@@ -12335,13 +12374,13 @@
         <v>3617</v>
       </c>
       <c r="H131" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I131" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J131" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K131">
         <v>168</v>
@@ -12365,7 +12404,7 @@
         <v>16.91304348</v>
       </c>
       <c r="V131" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W131">
         <v>-0.032543</v>
@@ -12394,10 +12433,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C132" s="2">
         <v>44940.38251856482</v>
@@ -12415,13 +12454,13 @@
         <v>3683</v>
       </c>
       <c r="H132" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I132" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J132" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K132">
         <v>174</v>
@@ -12445,7 +12484,7 @@
         <v>16.92424242</v>
       </c>
       <c r="V132" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W132">
         <v>0.00017</v>
@@ -12474,10 +12513,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C133" s="2">
         <v>44940.382865625</v>
@@ -12495,13 +12534,13 @@
         <v>3706</v>
       </c>
       <c r="H133" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I133" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J133" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K133">
         <v>146</v>
@@ -12525,7 +12564,7 @@
         <v>17.7826087</v>
       </c>
       <c r="V133" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W133">
         <v>0.03732</v>
@@ -12554,10 +12593,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C134" s="2">
         <v>44940.3831566088</v>
@@ -12575,13 +12614,13 @@
         <v>3708</v>
       </c>
       <c r="H134" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I134" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J134" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="K134">
         <v>152</v>
@@ -12605,7 +12644,7 @@
         <v>15</v>
       </c>
       <c r="V134" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W134">
         <v>-1.391304</v>
@@ -12634,10 +12673,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C135" s="2">
         <v>44940.38349574074</v>
@@ -12655,13 +12694,13 @@
         <v>3749</v>
       </c>
       <c r="H135" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I135" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J135" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K135">
         <v>182</v>
@@ -12685,7 +12724,7 @@
         <v>18.07317073</v>
       </c>
       <c r="V135" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W135">
         <v>0.07495499999999999</v>
@@ -12714,10 +12753,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C136" s="2">
         <v>44940.38384002315</v>
@@ -12735,13 +12774,13 @@
         <v>3796</v>
       </c>
       <c r="H136" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I136" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J136" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K136">
         <v>183</v>
@@ -12765,7 +12804,7 @@
         <v>17.78723404</v>
       </c>
       <c r="V136" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W136">
         <v>-0.006084</v>
@@ -12794,10 +12833,10 @@
     </row>
     <row r="137" spans="1:30">
       <c r="A137" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C137" s="2">
         <v>44940.38413138889</v>
@@ -12815,13 +12854,13 @@
         <v>3798</v>
       </c>
       <c r="H137" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J137" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K137">
         <v>180</v>
@@ -12845,7 +12884,7 @@
         <v>19</v>
       </c>
       <c r="V137" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W137">
         <v>0.606383</v>
@@ -12874,10 +12913,10 @@
     </row>
     <row r="138" spans="1:30">
       <c r="A138" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C138" s="2">
         <v>44940.38446775463</v>
@@ -12895,13 +12934,13 @@
         <v>3839</v>
       </c>
       <c r="H138" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I138" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J138" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="K138">
         <v>182</v>
@@ -12925,7 +12964,7 @@
         <v>17.48780488</v>
       </c>
       <c r="V138" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W138">
         <v>-0.036883</v>
@@ -12954,10 +12993,10 @@
     </row>
     <row r="139" spans="1:30">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C139" s="2">
         <v>44940.38481304398</v>
@@ -12975,13 +13014,13 @@
         <v>3862</v>
       </c>
       <c r="H139" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I139" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J139" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K139">
         <v>179</v>
@@ -13005,7 +13044,7 @@
         <v>16.56521739</v>
       </c>
       <c r="V139" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W139">
         <v>-0.040112</v>
@@ -13034,10 +13073,10 @@
     </row>
     <row r="140" spans="1:30">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C140" s="2">
         <v>44940.38510621528</v>
@@ -13055,13 +13094,13 @@
         <v>3864</v>
       </c>
       <c r="H140" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I140" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J140" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K140">
         <v>182</v>
@@ -13085,7 +13124,7 @@
         <v>15</v>
       </c>
       <c r="V140" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W140">
         <v>-0.782609</v>
@@ -13114,10 +13153,10 @@
     </row>
     <row r="141" spans="1:30">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C141" s="2">
         <v>44940.38544024306</v>
@@ -13135,13 +13174,13 @@
         <v>3928</v>
       </c>
       <c r="H141" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I141" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J141" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K141">
         <v>179</v>
@@ -13165,7 +13204,7 @@
         <v>16.09375</v>
       </c>
       <c r="V141" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W141">
         <v>0.01709</v>
@@ -13194,10 +13233,10 @@
     </row>
     <row r="142" spans="1:30">
       <c r="A142" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C142" s="2">
         <v>44940.38578652778</v>
@@ -13215,13 +13254,13 @@
         <v>3951</v>
       </c>
       <c r="H142" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I142" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J142" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K142">
         <v>177</v>
@@ -13245,7 +13284,7 @@
         <v>15.56521739</v>
       </c>
       <c r="V142" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W142">
         <v>-0.02298</v>
@@ -13274,10 +13313,10 @@
     </row>
     <row r="143" spans="1:30">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C143" s="2">
         <v>44940.38607760417</v>
@@ -13295,13 +13334,13 @@
         <v>3953</v>
       </c>
       <c r="H143" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I143" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J143" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K143">
         <v>177</v>
@@ -13325,7 +13364,7 @@
         <v>16.5</v>
       </c>
       <c r="V143" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W143">
         <v>0.467391</v>
@@ -13354,10 +13393,10 @@
     </row>
     <row r="144" spans="1:30">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C144" s="2">
         <v>44940.386411875</v>
@@ -13375,13 +13414,13 @@
         <v>4017</v>
       </c>
       <c r="H144" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I144" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J144" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="K144">
         <v>177</v>
@@ -13405,7 +13444,7 @@
         <v>16.515625</v>
       </c>
       <c r="V144" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="W144">
         <v>0.000244</v>
@@ -13444,102 +13483,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>44940.38676024305</v>
@@ -13557,13 +13596,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K2">
         <v>177</v>
@@ -13587,7 +13626,7 @@
         <v>-51.73913043</v>
       </c>
       <c r="V2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="X2">
         <v>-51.73913</v>
@@ -13598,10 +13637,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2">
         <v>44940.38705238426</v>
@@ -13619,13 +13658,13 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J3" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="K3">
         <v>165</v>
@@ -13649,7 +13688,7 @@
         <v>-92</v>
       </c>
       <c r="V3" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W3">
         <v>-20.130435</v>
@@ -13672,10 +13711,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>44940.40132559028</v>
@@ -13693,13 +13732,13 @@
         <v>1270</v>
       </c>
       <c r="H4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -13723,7 +13762,7 @@
         <v>-41.10646688</v>
       </c>
       <c r="V4" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W4">
         <v>0.040137</v>
@@ -13752,10 +13791,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2">
         <v>44940.40167709491</v>
@@ -13773,13 +13812,13 @@
         <v>1293</v>
       </c>
       <c r="H5" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I5" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J5" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="K5">
         <v>66</v>
@@ -13803,7 +13842,7 @@
         <v>-20.56521739</v>
       </c>
       <c r="V5" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W5">
         <v>0.8930979999999999</v>
@@ -13832,10 +13871,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>44940.40227767361</v>
@@ -13853,13 +13892,13 @@
         <v>1315</v>
       </c>
       <c r="H6" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I6" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="K6">
         <v>68</v>
@@ -13883,7 +13922,7 @@
         <v>-22.22727273</v>
       </c>
       <c r="V6" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W6">
         <v>-0.075548</v>
@@ -13912,10 +13951,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2">
         <v>44940.40261505787</v>
@@ -13933,13 +13972,13 @@
         <v>1380</v>
       </c>
       <c r="H7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I7" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="K7">
         <v>70</v>
@@ -13963,7 +14002,7 @@
         <v>-20.2</v>
       </c>
       <c r="V7" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W7">
         <v>0.031189</v>
@@ -13992,10 +14031,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>44940.40297104167</v>
@@ -14013,13 +14052,13 @@
         <v>1404</v>
       </c>
       <c r="H8" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J8" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K8">
         <v>66</v>
@@ -14043,7 +14082,7 @@
         <v>-16.20833333</v>
       </c>
       <c r="V8" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W8">
         <v>0.166319</v>
@@ -14072,10 +14111,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>44940.40324975694</v>
@@ -14093,13 +14132,13 @@
         <v>1405</v>
       </c>
       <c r="H9" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I9" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="J9" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K9">
         <v>60</v>
@@ -14123,7 +14162,7 @@
         <v>-29</v>
       </c>
       <c r="V9" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W9">
         <v>-12.791667</v>
@@ -14152,10 +14191,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>44940.40358505787</v>
@@ -14173,13 +14212,13 @@
         <v>1446</v>
       </c>
       <c r="H10" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I10" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J10" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="K10">
         <v>67</v>
@@ -14203,7 +14242,7 @@
         <v>-21.87804878</v>
       </c>
       <c r="V10" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W10">
         <v>0.173706</v>
@@ -14232,10 +14271,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>44940.40393440973</v>
@@ -14253,13 +14292,13 @@
         <v>1495</v>
       </c>
       <c r="H11" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I11" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J11" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K11">
         <v>61</v>
@@ -14283,7 +14322,7 @@
         <v>-20.30612245</v>
       </c>
       <c r="V11" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W11">
         <v>0.03208</v>
@@ -14312,10 +14351,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>44940.40422270833</v>
@@ -14333,13 +14372,13 @@
         <v>1496</v>
       </c>
       <c r="H12" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I12" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J12" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K12">
         <v>65</v>
@@ -14363,7 +14402,7 @@
         <v>-19</v>
       </c>
       <c r="V12" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W12">
         <v>1.306122</v>
@@ -14392,10 +14431,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2">
         <v>44940.40455836806</v>
@@ -14413,13 +14452,13 @@
         <v>1537</v>
       </c>
       <c r="H13" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I13" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J13" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K13">
         <v>64</v>
@@ -14443,7 +14482,7 @@
         <v>-19.70731707</v>
       </c>
       <c r="V13" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W13">
         <v>-0.017252</v>
@@ -14472,10 +14511,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>44940.40490565972</v>
@@ -14493,13 +14532,13 @@
         <v>1560</v>
       </c>
       <c r="H14" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I14" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J14" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K14">
         <v>65</v>
@@ -14523,7 +14562,7 @@
         <v>-19.26086957</v>
       </c>
       <c r="V14" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W14">
         <v>0.019411</v>
@@ -14552,10 +14591,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>44940.40519541666</v>
@@ -14573,13 +14612,13 @@
         <v>1562</v>
       </c>
       <c r="H15" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I15" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="J15" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="K15">
         <v>62</v>
@@ -14603,7 +14642,7 @@
         <v>-18.5</v>
       </c>
       <c r="V15" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W15">
         <v>0.380435</v>
@@ -14632,10 +14671,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>44940.40553086805</v>
@@ -14653,13 +14692,13 @@
         <v>1626</v>
       </c>
       <c r="H16" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I16" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J16" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K16">
         <v>61</v>
@@ -14683,7 +14722,7 @@
         <v>-18.71875</v>
       </c>
       <c r="V16" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W16">
         <v>-0.003418</v>
@@ -14712,10 +14751,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2">
         <v>44940.40587858796</v>
@@ -14733,13 +14772,13 @@
         <v>1650</v>
       </c>
       <c r="H17" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I17" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="J17" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K17">
         <v>70</v>
@@ -14763,7 +14802,7 @@
         <v>-17.33333333</v>
       </c>
       <c r="V17" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W17">
         <v>0.057726</v>
@@ -14792,10 +14831,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2">
         <v>44940.40616829861</v>
@@ -14813,13 +14852,13 @@
         <v>1651</v>
       </c>
       <c r="H18" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I18" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J18" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K18">
         <v>67</v>
@@ -14843,7 +14882,7 @@
         <v>-16</v>
       </c>
       <c r="V18" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W18">
         <v>1.333333</v>
@@ -14872,10 +14911,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>44940.40650520833</v>
@@ -14893,13 +14932,13 @@
         <v>1716</v>
       </c>
       <c r="H19" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I19" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="J19" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K19">
         <v>83</v>
@@ -14923,7 +14962,7 @@
         <v>-16.44615385</v>
       </c>
       <c r="V19" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W19">
         <v>-0.006864</v>
@@ -14952,10 +14991,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2">
         <v>44940.4068628588</v>
@@ -14973,13 +15012,13 @@
         <v>1740</v>
       </c>
       <c r="H20" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I20" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J20" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K20">
         <v>79</v>
@@ -15003,7 +15042,7 @@
         <v>-15.75</v>
       </c>
       <c r="V20" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W20">
         <v>0.029006</v>
@@ -15032,10 +15071,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>44940.40714446759</v>
@@ -15053,13 +15092,13 @@
         <v>1741</v>
       </c>
       <c r="H21" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I21" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J21" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K21">
         <v>83</v>
@@ -15083,7 +15122,7 @@
         <v>-16</v>
       </c>
       <c r="V21" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W21">
         <v>-0.25</v>
@@ -15112,10 +15151,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>44940.40747799769</v>
@@ -15133,13 +15172,13 @@
         <v>1782</v>
       </c>
       <c r="H22" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I22" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J22" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K22">
         <v>88</v>
@@ -15163,7 +15202,7 @@
         <v>-14.63414634</v>
       </c>
       <c r="V22" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W22">
         <v>0.033314</v>
@@ -15192,10 +15231,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>44940.40782540509</v>
@@ -15213,13 +15252,13 @@
         <v>1829</v>
       </c>
       <c r="H23" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I23" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J23" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K23">
         <v>76</v>
@@ -15243,7 +15282,7 @@
         <v>-15.23404255</v>
       </c>
       <c r="V23" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W23">
         <v>-0.012764</v>
@@ -15272,10 +15311,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>44940.4081149537</v>
@@ -15293,13 +15332,13 @@
         <v>1831</v>
       </c>
       <c r="H24" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I24" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J24" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="K24">
         <v>77</v>
@@ -15323,7 +15362,7 @@
         <v>-17.5</v>
       </c>
       <c r="V24" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W24">
         <v>-1.132979</v>
@@ -15352,10 +15391,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>44940.40845047454</v>
@@ -15373,13 +15412,13 @@
         <v>1871</v>
       </c>
       <c r="H25" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I25" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J25" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K25">
         <v>92</v>
@@ -15403,7 +15442,7 @@
         <v>-15.625</v>
       </c>
       <c r="V25" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W25">
         <v>0.046875</v>
@@ -15432,10 +15471,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>44940.4087983912</v>
@@ -15453,13 +15492,13 @@
         <v>1895</v>
       </c>
       <c r="H26" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I26" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J26" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K26">
         <v>82</v>
@@ -15483,7 +15522,7 @@
         <v>-16.375</v>
       </c>
       <c r="V26" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W26">
         <v>-0.03125</v>
@@ -15512,10 +15551,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>44940.40942376157</v>
@@ -15533,13 +15572,13 @@
         <v>1960</v>
       </c>
       <c r="H27" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I27" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="J27" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K27">
         <v>91</v>
@@ -15563,7 +15602,7 @@
         <v>-14.61538462</v>
       </c>
       <c r="V27" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W27">
         <v>0.027071</v>
@@ -15592,10 +15631,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2">
         <v>44940.40977202546</v>
@@ -15613,13 +15652,13 @@
         <v>1982</v>
       </c>
       <c r="H28" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I28" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J28" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K28">
         <v>75</v>
@@ -15643,7 +15682,7 @@
         <v>-14.09090909</v>
       </c>
       <c r="V28" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W28">
         <v>0.02384</v>
@@ -15672,10 +15711,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2">
         <v>44940.41006155092</v>
@@ -15693,13 +15732,13 @@
         <v>1985</v>
       </c>
       <c r="H29" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I29" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="J29" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K29">
         <v>78</v>
@@ -15723,7 +15762,7 @@
         <v>-14.33333333</v>
       </c>
       <c r="V29" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W29">
         <v>-0.080808</v>
@@ -15752,10 +15791,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>44940.41039842593</v>
@@ -15773,13 +15812,13 @@
         <v>2049</v>
       </c>
       <c r="H30" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I30" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="J30" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K30">
         <v>59</v>
@@ -15803,7 +15842,7 @@
         <v>-13.53125</v>
       </c>
       <c r="V30" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W30">
         <v>0.012533</v>
@@ -15832,10 +15871,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>44940.41074732639</v>
@@ -15853,13 +15892,13 @@
         <v>2072</v>
       </c>
       <c r="H31" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I31" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J31" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K31">
         <v>73</v>
@@ -15883,7 +15922,7 @@
         <v>-13.91304348</v>
       </c>
       <c r="V31" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W31">
         <v>-0.0166</v>
@@ -15912,10 +15951,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>44940.41103886574</v>
@@ -15933,13 +15972,13 @@
         <v>2074</v>
       </c>
       <c r="H32" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I32" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J32" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="K32">
         <v>69</v>
@@ -15963,7 +16002,7 @@
         <v>-11</v>
       </c>
       <c r="V32" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W32">
         <v>1.456522</v>
@@ -15992,10 +16031,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2">
         <v>44940.41137101852</v>
@@ -16013,13 +16052,13 @@
         <v>2139</v>
       </c>
       <c r="H33" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I33" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J33" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K33">
         <v>60</v>
@@ -16043,7 +16082,7 @@
         <v>-12.98461538</v>
       </c>
       <c r="V33" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W33">
         <v>-0.030533</v>
@@ -16072,10 +16111,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2">
         <v>44940.41171789352</v>
@@ -16093,13 +16132,13 @@
         <v>2162</v>
       </c>
       <c r="H34" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I34" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J34" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K34">
         <v>74</v>
@@ -16123,7 +16162,7 @@
         <v>-13.34782609</v>
       </c>
       <c r="V34" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W34">
         <v>-0.015792</v>
@@ -16152,10 +16191,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2">
         <v>44940.41200840277</v>
@@ -16173,13 +16212,13 @@
         <v>2164</v>
       </c>
       <c r="H35" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I35" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J35" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K35">
         <v>69</v>
@@ -16203,7 +16242,7 @@
         <v>-13</v>
       </c>
       <c r="V35" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W35">
         <v>0.173913</v>
@@ -16232,10 +16271,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>44940.41234394676</v>
@@ -16253,13 +16292,13 @@
         <v>2204</v>
       </c>
       <c r="H36" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I36" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J36" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K36">
         <v>56</v>
@@ -16283,7 +16322,7 @@
         <v>-13.125</v>
       </c>
       <c r="V36" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W36">
         <v>-0.003125</v>
@@ -16312,10 +16351,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>44940.41269121528</v>
@@ -16333,13 +16372,13 @@
         <v>2252</v>
       </c>
       <c r="H37" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I37" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J37" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K37">
         <v>65</v>
@@ -16363,7 +16402,7 @@
         <v>-13.9375</v>
       </c>
       <c r="V37" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W37">
         <v>-0.016927</v>
@@ -16392,10 +16431,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>44940.41298534722</v>
@@ -16413,13 +16452,13 @@
         <v>2254</v>
       </c>
       <c r="H38" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I38" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J38" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="K38">
         <v>66</v>
@@ -16443,7 +16482,7 @@
         <v>-14</v>
       </c>
       <c r="V38" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W38">
         <v>-0.03125</v>
@@ -16472,10 +16511,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
         <v>44940.41332467592</v>
@@ -16493,13 +16532,13 @@
         <v>2294</v>
       </c>
       <c r="H39" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I39" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J39" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K39">
         <v>80</v>
@@ -16523,7 +16562,7 @@
         <v>-13.25</v>
       </c>
       <c r="V39" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W39">
         <v>0.01875</v>
@@ -16552,10 +16591,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>44940.41366487269</v>
@@ -16573,13 +16612,13 @@
         <v>2317</v>
       </c>
       <c r="H40" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I40" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J40" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K40">
         <v>83</v>
@@ -16603,7 +16642,7 @@
         <v>-12.86956522</v>
       </c>
       <c r="V40" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W40">
         <v>0.016541</v>
@@ -16632,10 +16671,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>44940.41395497685</v>
@@ -16653,13 +16692,13 @@
         <v>2319</v>
       </c>
       <c r="H41" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I41" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J41" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K41">
         <v>78</v>
@@ -16683,7 +16722,7 @@
         <v>-13</v>
       </c>
       <c r="V41" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W41">
         <v>-0.065217</v>
@@ -16712,10 +16751,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>44940.41429173611</v>
@@ -16733,13 +16772,13 @@
         <v>2382</v>
       </c>
       <c r="H42" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I42" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J42" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K42">
         <v>106</v>
@@ -16763,7 +16802,7 @@
         <v>-13.49206349</v>
       </c>
       <c r="V42" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W42">
         <v>-0.007811</v>
@@ -16792,10 +16831,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>44940.41463856481</v>
@@ -16813,13 +16852,13 @@
         <v>2405</v>
       </c>
       <c r="H43" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I43" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J43" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K43">
         <v>110</v>
@@ -16843,7 +16882,7 @@
         <v>-12.69565217</v>
       </c>
       <c r="V43" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W43">
         <v>0.034627</v>
@@ -16872,10 +16911,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" s="2">
         <v>44940.41492850694</v>
@@ -16893,13 +16932,13 @@
         <v>2407</v>
       </c>
       <c r="H44" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I44" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J44" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K44">
         <v>108</v>
@@ -16923,7 +16962,7 @@
         <v>-12</v>
       </c>
       <c r="V44" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W44">
         <v>0.347826</v>
@@ -16952,10 +16991,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2">
         <v>44940.41526369213</v>
@@ -16973,13 +17012,13 @@
         <v>2470</v>
       </c>
       <c r="H45" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I45" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J45" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K45">
         <v>94</v>
@@ -17003,7 +17042,7 @@
         <v>-13.17460317</v>
       </c>
       <c r="V45" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W45">
         <v>-0.018644</v>
@@ -17032,10 +17071,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>44940.41561819444</v>
@@ -17053,13 +17092,13 @@
         <v>2494</v>
       </c>
       <c r="H46" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I46" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J46" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K46">
         <v>110</v>
@@ -17083,7 +17122,7 @@
         <v>-13.25</v>
       </c>
       <c r="V46" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W46">
         <v>-0.003142</v>
@@ -17112,10 +17151,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
         <v>44940.41590708333</v>
@@ -17133,13 +17172,13 @@
         <v>2495</v>
       </c>
       <c r="H47" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I47" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J47" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K47">
         <v>106</v>
@@ -17163,7 +17202,7 @@
         <v>-15</v>
       </c>
       <c r="V47" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W47">
         <v>-1.75</v>
@@ -17192,10 +17231,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C48" s="2">
         <v>44940.41623784722</v>
@@ -17213,13 +17252,13 @@
         <v>2560</v>
       </c>
       <c r="H48" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I48" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J48" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K48">
         <v>108</v>
@@ -17243,7 +17282,7 @@
         <v>-13.78461538</v>
       </c>
       <c r="V48" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W48">
         <v>0.018698</v>
@@ -17272,10 +17311,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2">
         <v>44940.41658493056</v>
@@ -17293,13 +17332,13 @@
         <v>2582</v>
       </c>
       <c r="H49" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I49" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J49" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K49">
         <v>75</v>
@@ -17323,7 +17362,7 @@
         <v>-13.68181818</v>
       </c>
       <c r="V49" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W49">
         <v>0.004673</v>
@@ -17352,10 +17391,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>44940.41687560186</v>
@@ -17373,13 +17412,13 @@
         <v>2584</v>
       </c>
       <c r="H50" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I50" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J50" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K50">
         <v>79</v>
@@ -17403,7 +17442,7 @@
         <v>-14.5</v>
       </c>
       <c r="V50" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W50">
         <v>-0.409091</v>
@@ -17432,10 +17471,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2">
         <v>44940.41721150463</v>
@@ -17453,13 +17492,13 @@
         <v>2624</v>
       </c>
       <c r="H51" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I51" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="J51" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K51">
         <v>81</v>
@@ -17483,7 +17522,7 @@
         <v>-13.05</v>
       </c>
       <c r="V51" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W51">
         <v>0.03625</v>
@@ -17512,10 +17551,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>44940.41755880787</v>
@@ -17533,13 +17572,13 @@
         <v>2670</v>
       </c>
       <c r="H52" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I52" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J52" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K52">
         <v>83</v>
@@ -17563,7 +17602,7 @@
         <v>-12.41304348</v>
       </c>
       <c r="V52" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W52">
         <v>0.013847</v>
@@ -17592,10 +17631,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2">
         <v>44940.41785347222</v>
@@ -17613,13 +17652,13 @@
         <v>2672</v>
       </c>
       <c r="H53" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I53" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J53" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K53">
         <v>83</v>
@@ -17643,7 +17682,7 @@
         <v>-12.5</v>
       </c>
       <c r="V53" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W53">
         <v>-0.043478</v>
@@ -17672,10 +17711,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>44940.41818424768</v>
@@ -17693,13 +17732,13 @@
         <v>2711</v>
       </c>
       <c r="H54" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I54" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J54" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="K54">
         <v>99</v>
@@ -17723,7 +17762,7 @@
         <v>-12.23076923</v>
       </c>
       <c r="V54" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W54">
         <v>0.006903</v>
@@ -17752,10 +17791,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C55" s="2">
         <v>44940.41853172454</v>
@@ -17773,13 +17812,13 @@
         <v>2734</v>
       </c>
       <c r="H55" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I55" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J55" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K55">
         <v>83</v>
@@ -17803,7 +17842,7 @@
         <v>-12.17391304</v>
       </c>
       <c r="V55" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W55">
         <v>0.002472</v>
@@ -17832,10 +17871,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>44940.41882295139</v>
@@ -17853,13 +17892,13 @@
         <v>2760</v>
       </c>
       <c r="H56" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I56" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J56" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K56">
         <v>81</v>
@@ -17883,7 +17922,7 @@
         <v>-12.88461538</v>
       </c>
       <c r="V56" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W56">
         <v>-0.027335</v>
@@ -17912,10 +17951,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C57" s="2">
         <v>44940.41915699074</v>
@@ -17933,13 +17972,13 @@
         <v>2800</v>
       </c>
       <c r="H57" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I57" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J57" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="K57">
         <v>117</v>
@@ -17963,7 +18002,7 @@
         <v>-12.475</v>
       </c>
       <c r="V57" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W57">
         <v>0.01024</v>
@@ -17992,10 +18031,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2">
         <v>44940.41950591435</v>
@@ -18013,13 +18052,13 @@
         <v>2822</v>
       </c>
       <c r="H58" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I58" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J58" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K58">
         <v>108</v>
@@ -18043,7 +18082,7 @@
         <v>-12.18181818</v>
       </c>
       <c r="V58" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W58">
         <v>0.013326</v>
@@ -18072,10 +18111,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2">
         <v>44940.41979554398</v>
@@ -18093,13 +18132,13 @@
         <v>2823</v>
       </c>
       <c r="H59" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I59" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J59" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K59">
         <v>112</v>
@@ -18123,7 +18162,7 @@
         <v>-12</v>
       </c>
       <c r="V59" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W59">
         <v>0.181818</v>
@@ -18152,10 +18191,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2">
         <v>44940.42013127315</v>
@@ -18173,13 +18212,13 @@
         <v>2887</v>
       </c>
       <c r="H60" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I60" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J60" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K60">
         <v>165</v>
@@ -18203,7 +18242,7 @@
         <v>-10.640625</v>
       </c>
       <c r="V60" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W60">
         <v>0.02124</v>
@@ -18232,10 +18271,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
         <v>44940.42047820602</v>
@@ -18253,13 +18292,13 @@
         <v>2910</v>
       </c>
       <c r="H61" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I61" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J61" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K61">
         <v>173</v>
@@ -18283,7 +18322,7 @@
         <v>-11.69565217</v>
       </c>
       <c r="V61" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W61">
         <v>-0.045871</v>
@@ -18312,10 +18351,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
         <v>44940.42077486111</v>
@@ -18333,13 +18372,13 @@
         <v>2911</v>
       </c>
       <c r="H62" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I62" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J62" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K62">
         <v>166</v>
@@ -18363,7 +18402,7 @@
         <v>-13</v>
       </c>
       <c r="V62" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W62">
         <v>-1.304348</v>
@@ -18392,10 +18431,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>44940.42110949074</v>
@@ -18413,13 +18452,13 @@
         <v>2976</v>
       </c>
       <c r="H63" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I63" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="J63" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="K63">
         <v>94</v>
@@ -18443,7 +18482,7 @@
         <v>-12.10769231</v>
       </c>
       <c r="V63" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W63">
         <v>0.013728</v>
@@ -18472,10 +18511,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
         <v>44940.42145140046</v>
@@ -18493,13 +18532,13 @@
         <v>2999</v>
       </c>
       <c r="H64" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I64" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J64" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K64">
         <v>115</v>
@@ -18523,7 +18562,7 @@
         <v>-13.04347826</v>
       </c>
       <c r="V64" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W64">
         <v>-0.040686</v>
@@ -18552,10 +18591,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C65" s="2">
         <v>44940.42174225694</v>
@@ -18573,13 +18612,13 @@
         <v>3000</v>
       </c>
       <c r="H65" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I65" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J65" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K65">
         <v>152</v>
@@ -18603,7 +18642,7 @@
         <v>-10</v>
       </c>
       <c r="V65" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W65">
         <v>3.043478</v>
@@ -18632,10 +18671,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2">
         <v>44940.42208086805</v>
@@ -18653,13 +18692,13 @@
         <v>3064</v>
       </c>
       <c r="H66" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I66" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J66" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="K66">
         <v>200</v>
@@ -18683,7 +18722,7 @@
         <v>-11.8125</v>
       </c>
       <c r="V66" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W66">
         <v>-0.02832</v>
@@ -18712,10 +18751,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2">
         <v>44940.42242895834</v>
@@ -18733,13 +18772,13 @@
         <v>3086</v>
       </c>
       <c r="H67" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I67" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J67" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="K67">
         <v>126</v>
@@ -18763,7 +18802,7 @@
         <v>-12.18181818</v>
       </c>
       <c r="V67" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W67">
         <v>-0.016787</v>
@@ -18792,10 +18831,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2">
         <v>44940.42272012732</v>
@@ -18813,13 +18852,13 @@
         <v>3088</v>
       </c>
       <c r="H68" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I68" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J68" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="K68">
         <v>112</v>
@@ -18843,7 +18882,7 @@
         <v>-12.5</v>
       </c>
       <c r="V68" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W68">
         <v>-0.159091</v>
@@ -18872,10 +18911,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2">
         <v>44940.42305065972</v>
@@ -18893,13 +18932,13 @@
         <v>3128</v>
       </c>
       <c r="H69" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I69" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J69" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="K69">
         <v>168</v>
@@ -18923,7 +18962,7 @@
         <v>-10.65</v>
       </c>
       <c r="V69" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="W69">
         <v>0.04625</v>

--- a/www/flightdata/xlsx/eoss-334.xlsx
+++ b/www/flightdata/xlsx/eoss-334.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="500">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>KE0BMV-11</t>
   </si>
   <si>
@@ -1096,6 +1099,9 @@
   </si>
   <si>
     <t>low Re</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -2035,10 +2041,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE144"/>
+  <dimension ref="A1:AF144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -2132,13 +2138,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>44940.34004650463</v>
@@ -2156,13 +2165,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K2">
         <v>344</v>
@@ -2189,7 +2198,7 @@
         <v>1.5</v>
       </c>
       <c r="W2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Y2">
         <v>1.5</v>
@@ -2198,12 +2207,12 @@
         <v>8.820105999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2">
         <v>44940.34033475695</v>
@@ -2221,13 +2230,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2254,7 +2263,7 @@
         <v>13</v>
       </c>
       <c r="W3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X3">
         <v>11.5</v>
@@ -2275,12 +2284,12 @@
         <v>8.912556</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>44940.34067034722</v>
@@ -2298,13 +2307,13 @@
         <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K4">
         <v>130</v>
@@ -2331,7 +2340,7 @@
         <v>20.93846154</v>
       </c>
       <c r="W4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X4">
         <v>0.12213</v>
@@ -2358,12 +2367,12 @@
         <v>16.255015</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2">
         <v>44940.34101709491</v>
@@ -2381,13 +2390,13 @@
         <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K5">
         <v>136</v>
@@ -2414,7 +2423,7 @@
         <v>19.41666667</v>
       </c>
       <c r="W5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X5">
         <v>-0.06340800000000001</v>
@@ -2441,12 +2450,12 @@
         <v>17.899159</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>44940.34130826389</v>
@@ -2464,13 +2473,13 @@
         <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K6">
         <v>132</v>
@@ -2497,7 +2506,7 @@
         <v>22</v>
       </c>
       <c r="W6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X6">
         <v>2.583333</v>
@@ -2524,12 +2533,12 @@
         <v>17.967958</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2">
         <v>44940.34164278935</v>
@@ -2547,13 +2556,13 @@
         <v>132</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K7">
         <v>138</v>
@@ -2580,7 +2589,7 @@
         <v>16.92682927</v>
       </c>
       <c r="W7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X7">
         <v>-0.123736</v>
@@ -2607,12 +2616,12 @@
         <v>19.782634</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>44940.34199069445</v>
@@ -2630,13 +2639,13 @@
         <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K8">
         <v>120</v>
@@ -2663,7 +2672,7 @@
         <v>24.375</v>
       </c>
       <c r="W8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X8">
         <v>0.15517</v>
@@ -2690,12 +2699,12 @@
         <v>21.591719</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>44940.34228068287</v>
@@ -2713,13 +2722,13 @@
         <v>181</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K9">
         <v>118</v>
@@ -2746,7 +2755,7 @@
         <v>22</v>
       </c>
       <c r="W9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X9">
         <v>-2.375</v>
@@ -2773,12 +2782,12 @@
         <v>21.613938</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>44940.34261623843</v>
@@ -2796,13 +2805,13 @@
         <v>222</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K10">
         <v>135</v>
@@ -2829,7 +2838,7 @@
         <v>13.82926829</v>
       </c>
       <c r="W10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X10">
         <v>-0.199286</v>
@@ -2856,12 +2865,12 @@
         <v>22.068121</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>44940.3429653125</v>
@@ -2879,13 +2888,13 @@
         <v>245</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K11">
         <v>96</v>
@@ -2912,7 +2921,7 @@
         <v>18.73913043</v>
       </c>
       <c r="W11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X11">
         <v>0.213472</v>
@@ -2939,12 +2948,12 @@
         <v>22.280735</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>44940.3432546412</v>
@@ -2962,13 +2971,13 @@
         <v>271</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K12">
         <v>106</v>
@@ -2995,7 +3004,7 @@
         <v>22.42307692</v>
       </c>
       <c r="W12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X12">
         <v>0.14169</v>
@@ -3022,12 +3031,12 @@
         <v>22.423548</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2">
         <v>44940.34359054398</v>
@@ -3045,13 +3054,13 @@
         <v>311</v>
       </c>
       <c r="H13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K13">
         <v>106</v>
@@ -3078,7 +3087,7 @@
         <v>24.275</v>
       </c>
       <c r="W13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X13">
         <v>0.046298</v>
@@ -3105,12 +3114,12 @@
         <v>22.389879</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>44940.34393738426</v>
@@ -3128,13 +3137,13 @@
         <v>335</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K14">
         <v>82</v>
@@ -3161,7 +3170,7 @@
         <v>18.08333333</v>
       </c>
       <c r="W14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X14">
         <v>-0.257986</v>
@@ -3188,12 +3197,12 @@
         <v>22.297655</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2">
         <v>44940.34422796296</v>
@@ -3211,13 +3220,13 @@
         <v>337</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K15">
         <v>86</v>
@@ -3244,7 +3253,7 @@
         <v>21.5</v>
       </c>
       <c r="W15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X15">
         <v>1.708333</v>
@@ -3271,12 +3280,12 @@
         <v>22.286593</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>44940.34456484954</v>
@@ -3294,13 +3303,13 @@
         <v>401</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K16">
         <v>83</v>
@@ -3327,7 +3336,7 @@
         <v>20.703125</v>
       </c>
       <c r="W16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X16">
         <v>-0.012451</v>
@@ -3359,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>44940.34491047454</v>
@@ -3377,13 +3386,13 @@
         <v>425</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K17">
         <v>81</v>
@@ -3410,7 +3419,7 @@
         <v>23.79166667</v>
       </c>
       <c r="W17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X17">
         <v>0.128689</v>
@@ -3442,7 +3451,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>44940.3452025</v>
@@ -3460,13 +3469,13 @@
         <v>427</v>
       </c>
       <c r="H18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K18">
         <v>77</v>
@@ -3493,7 +3502,7 @@
         <v>28</v>
       </c>
       <c r="W18" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X18">
         <v>2.104167</v>
@@ -3525,7 +3534,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>44940.34553807871</v>
@@ -3543,13 +3552,13 @@
         <v>466</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K19">
         <v>78</v>
@@ -3576,7 +3585,7 @@
         <v>22.66666667</v>
       </c>
       <c r="W19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X19">
         <v>-0.136752</v>
@@ -3608,7 +3617,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2">
         <v>44940.34588461806</v>
@@ -3626,13 +3635,13 @@
         <v>515</v>
       </c>
       <c r="H20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K20">
         <v>85</v>
@@ -3659,7 +3668,7 @@
         <v>23.18367347</v>
       </c>
       <c r="W20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X20">
         <v>0.010551</v>
@@ -3691,7 +3700,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>44940.3461744213</v>
@@ -3709,13 +3718,13 @@
         <v>517</v>
       </c>
       <c r="H21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K21">
         <v>79</v>
@@ -3742,7 +3751,7 @@
         <v>23</v>
       </c>
       <c r="W21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X21">
         <v>-0.091837</v>
@@ -3774,7 +3783,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2">
         <v>44940.34651012732</v>
@@ -3792,13 +3801,13 @@
         <v>558</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K22">
         <v>84</v>
@@ -3825,7 +3834,7 @@
         <v>20.7804878</v>
       </c>
       <c r="W22" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X22">
         <v>-0.054134</v>
@@ -3857,7 +3866,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2">
         <v>44940.34685759259</v>
@@ -3875,13 +3884,13 @@
         <v>605</v>
       </c>
       <c r="H23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K23">
         <v>91</v>
@@ -3908,7 +3917,7 @@
         <v>20.06382979</v>
       </c>
       <c r="W23" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X23">
         <v>-0.015248</v>
@@ -3940,7 +3949,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>44940.34714877315</v>
@@ -3958,13 +3967,13 @@
         <v>607</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K24">
         <v>92</v>
@@ -3991,7 +4000,7 @@
         <v>19</v>
       </c>
       <c r="W24" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X24">
         <v>-0.531915</v>
@@ -4023,7 +4032,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>44940.34748677084</v>
@@ -4041,13 +4050,13 @@
         <v>647</v>
       </c>
       <c r="H25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K25">
         <v>86</v>
@@ -4074,7 +4083,7 @@
         <v>23.05</v>
       </c>
       <c r="W25" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X25">
         <v>0.10125</v>
@@ -4106,7 +4115,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2">
         <v>44940.34783131944</v>
@@ -4124,13 +4133,13 @@
         <v>671</v>
       </c>
       <c r="H26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K26">
         <v>98</v>
@@ -4157,7 +4166,7 @@
         <v>22.125</v>
       </c>
       <c r="W26" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X26">
         <v>-0.038542</v>
@@ -4189,7 +4198,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>44940.34812273148</v>
@@ -4207,13 +4216,13 @@
         <v>673</v>
       </c>
       <c r="H27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4240,7 +4249,7 @@
         <v>18.5</v>
       </c>
       <c r="W27" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X27">
         <v>-1.8125</v>
@@ -4272,7 +4281,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2">
         <v>44940.34845848379</v>
@@ -4290,13 +4299,13 @@
         <v>738</v>
       </c>
       <c r="H28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K28">
         <v>89</v>
@@ -4323,7 +4332,7 @@
         <v>18.44615385</v>
       </c>
       <c r="W28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X28">
         <v>-0.000828</v>
@@ -4355,7 +4364,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2">
         <v>44940.34880458334</v>
@@ -4373,13 +4382,13 @@
         <v>762</v>
       </c>
       <c r="H29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K29">
         <v>81</v>
@@ -4406,7 +4415,7 @@
         <v>19.95833333</v>
       </c>
       <c r="W29" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X29">
         <v>0.06300699999999999</v>
@@ -4438,7 +4447,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>44940.349095625</v>
@@ -4456,13 +4465,13 @@
         <v>763</v>
       </c>
       <c r="H30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K30">
         <v>85</v>
@@ -4489,7 +4498,7 @@
         <v>19</v>
       </c>
       <c r="W30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X30">
         <v>-0.958333</v>
@@ -4521,7 +4530,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2">
         <v>44940.3494306713</v>
@@ -4539,13 +4548,13 @@
         <v>828</v>
       </c>
       <c r="H31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K31">
         <v>75</v>
@@ -4572,7 +4581,7 @@
         <v>22.52307692</v>
       </c>
       <c r="W31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X31">
         <v>0.054201</v>
@@ -4604,7 +4613,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>44940.34977787037</v>
@@ -4622,13 +4631,13 @@
         <v>851</v>
       </c>
       <c r="H32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K32">
         <v>79</v>
@@ -4655,7 +4664,7 @@
         <v>16.2173913</v>
       </c>
       <c r="W32" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X32">
         <v>-0.27416</v>
@@ -4687,7 +4696,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>44940.35006822916</v>
@@ -4705,13 +4714,13 @@
         <v>853</v>
       </c>
       <c r="H33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K33">
         <v>77</v>
@@ -4738,7 +4747,7 @@
         <v>8</v>
       </c>
       <c r="W33" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X33">
         <v>-4.108696</v>
@@ -4770,7 +4779,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2">
         <v>44940.35040363426</v>
@@ -4788,13 +4797,13 @@
         <v>893</v>
       </c>
       <c r="H34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K34">
         <v>67</v>
@@ -4821,7 +4830,7 @@
         <v>14.725</v>
       </c>
       <c r="W34" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X34">
         <v>0.168125</v>
@@ -4853,7 +4862,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2">
         <v>44940.35075162037</v>
@@ -4871,13 +4880,13 @@
         <v>942</v>
       </c>
       <c r="H35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K35">
         <v>61</v>
@@ -4904,7 +4913,7 @@
         <v>21.02040816</v>
       </c>
       <c r="W35" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X35">
         <v>0.128478</v>
@@ -4936,7 +4945,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>44940.35104189815</v>
@@ -4954,13 +4963,13 @@
         <v>944</v>
       </c>
       <c r="H36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J36" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K36">
         <v>63</v>
@@ -4987,7 +4996,7 @@
         <v>26</v>
       </c>
       <c r="W36" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X36">
         <v>2.489796</v>
@@ -5019,7 +5028,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>44940.35137795139</v>
@@ -5037,13 +5046,13 @@
         <v>985</v>
       </c>
       <c r="H37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K37">
         <v>60</v>
@@ -5070,7 +5079,7 @@
         <v>24.65853659</v>
       </c>
       <c r="W37" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X37">
         <v>-0.032719</v>
@@ -5102,7 +5111,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2">
         <v>44940.35172524305</v>
@@ -5120,13 +5129,13 @@
         <v>1008</v>
       </c>
       <c r="H38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J38" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K38">
         <v>58</v>
@@ -5153,7 +5162,7 @@
         <v>23.95652174</v>
       </c>
       <c r="W38" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X38">
         <v>-0.030522</v>
@@ -5185,7 +5194,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2">
         <v>44940.35201546297</v>
@@ -5203,13 +5212,13 @@
         <v>1009</v>
       </c>
       <c r="H39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K39">
         <v>57</v>
@@ -5236,7 +5245,7 @@
         <v>29</v>
       </c>
       <c r="W39" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X39">
         <v>5.043478</v>
@@ -5268,7 +5277,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>44940.35235122685</v>
@@ -5286,13 +5295,13 @@
         <v>1075</v>
       </c>
       <c r="H40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K40">
         <v>56</v>
@@ -5319,7 +5328,7 @@
         <v>25.25757576</v>
       </c>
       <c r="W40" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X40">
         <v>-0.056703</v>
@@ -5351,7 +5360,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>44940.35269846065</v>
@@ -5369,13 +5378,13 @@
         <v>1098</v>
       </c>
       <c r="H41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K41">
         <v>58</v>
@@ -5402,7 +5411,7 @@
         <v>23.56521739</v>
       </c>
       <c r="W41" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X41">
         <v>-0.07358099999999999</v>
@@ -5434,7 +5443,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C42" s="2">
         <v>44940.35298905092</v>
@@ -5452,13 +5461,13 @@
         <v>1100</v>
       </c>
       <c r="H42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K42">
         <v>59</v>
@@ -5485,7 +5494,7 @@
         <v>30.5</v>
       </c>
       <c r="W42" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X42">
         <v>3.467391</v>
@@ -5517,7 +5526,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>44940.35332460648</v>
@@ -5535,13 +5544,13 @@
         <v>1141</v>
       </c>
       <c r="H43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J43" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K43">
         <v>59</v>
@@ -5568,7 +5577,7 @@
         <v>25.09756098</v>
       </c>
       <c r="W43" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X43">
         <v>-0.131767</v>
@@ -5600,7 +5609,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>44940.35367141203</v>
@@ -5618,13 +5627,13 @@
         <v>1190</v>
       </c>
       <c r="H44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K44">
         <v>65</v>
@@ -5651,7 +5660,7 @@
         <v>22.73469388</v>
       </c>
       <c r="W44" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X44">
         <v>-0.048222</v>
@@ -5683,7 +5692,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>44940.35396269676</v>
@@ -5701,13 +5710,13 @@
         <v>1191</v>
       </c>
       <c r="H45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K45">
         <v>66</v>
@@ -5734,7 +5743,7 @@
         <v>24</v>
       </c>
       <c r="W45" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X45">
         <v>1.265306</v>
@@ -5766,7 +5775,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2">
         <v>44940.35429768518</v>
@@ -5784,13 +5793,13 @@
         <v>1232</v>
       </c>
       <c r="H46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K46">
         <v>59</v>
@@ -5817,7 +5826,7 @@
         <v>24</v>
       </c>
       <c r="W46" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X46">
         <v>0</v>
@@ -5849,7 +5858,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>44940.35464509259</v>
@@ -5867,13 +5876,13 @@
         <v>1255</v>
       </c>
       <c r="H47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J47" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K47">
         <v>60</v>
@@ -5900,7 +5909,7 @@
         <v>26.91304348</v>
       </c>
       <c r="W47" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X47">
         <v>0.126654</v>
@@ -5932,7 +5941,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>44940.35493649306</v>
@@ -5950,13 +5959,13 @@
         <v>1257</v>
       </c>
       <c r="H48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K48">
         <v>61</v>
@@ -5983,7 +5992,7 @@
         <v>25.5</v>
       </c>
       <c r="W48" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X48">
         <v>-0.706522</v>
@@ -6015,7 +6024,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>44940.35527100694</v>
@@ -6033,13 +6042,13 @@
         <v>1323</v>
       </c>
       <c r="H49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J49" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K49">
         <v>49</v>
@@ -6066,7 +6075,7 @@
         <v>26.6969697</v>
       </c>
       <c r="W49" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X49">
         <v>0.018136</v>
@@ -6098,7 +6107,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>44940.35561853009</v>
@@ -6116,13 +6125,13 @@
         <v>1346</v>
       </c>
       <c r="H50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J50" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K50">
         <v>56</v>
@@ -6149,7 +6158,7 @@
         <v>27.30434783</v>
       </c>
       <c r="W50" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X50">
         <v>0.026408</v>
@@ -6181,7 +6190,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2">
         <v>44940.35590945602</v>
@@ -6199,13 +6208,13 @@
         <v>1348</v>
       </c>
       <c r="H51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I51" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J51" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K51">
         <v>57</v>
@@ -6232,7 +6241,7 @@
         <v>18.5</v>
       </c>
       <c r="W51" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X51">
         <v>-4.402174</v>
@@ -6264,7 +6273,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>44940.35624493055</v>
@@ -6282,13 +6291,13 @@
         <v>1414</v>
       </c>
       <c r="H52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I52" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J52" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K52">
         <v>53</v>
@@ -6315,7 +6324,7 @@
         <v>24.36363636</v>
       </c>
       <c r="W52" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X52">
         <v>0.08884300000000001</v>
@@ -6347,7 +6356,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>44940.3565925</v>
@@ -6365,13 +6374,13 @@
         <v>1437</v>
       </c>
       <c r="H53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I53" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K53">
         <v>56</v>
@@ -6398,7 +6407,7 @@
         <v>27.17391304</v>
       </c>
       <c r="W53" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X53">
         <v>0.122186</v>
@@ -6430,7 +6439,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>44940.35688671297</v>
@@ -6448,13 +6457,13 @@
         <v>1439</v>
       </c>
       <c r="H54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I54" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J54" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K54">
         <v>54</v>
@@ -6481,7 +6490,7 @@
         <v>21</v>
       </c>
       <c r="W54" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X54">
         <v>-3.086957</v>
@@ -6513,7 +6522,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C55" s="2">
         <v>44940.35721751158</v>
@@ -6531,13 +6540,13 @@
         <v>1479</v>
       </c>
       <c r="H55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J55" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K55">
         <v>58</v>
@@ -6564,7 +6573,7 @@
         <v>27.475</v>
       </c>
       <c r="W55" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X55">
         <v>0.161875</v>
@@ -6596,7 +6605,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>44940.3575658912</v>
@@ -6614,13 +6623,13 @@
         <v>1526</v>
       </c>
       <c r="H56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K56">
         <v>64</v>
@@ -6647,7 +6656,7 @@
         <v>26.38297872</v>
       </c>
       <c r="W56" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X56">
         <v>-0.023234</v>
@@ -6679,7 +6688,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C57" s="2">
         <v>44940.35785689815</v>
@@ -6697,13 +6706,13 @@
         <v>1528</v>
       </c>
       <c r="H57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K57">
         <v>65</v>
@@ -6730,7 +6739,7 @@
         <v>26.5</v>
       </c>
       <c r="W57" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X57">
         <v>0.058511</v>
@@ -6762,7 +6771,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2">
         <v>44940.35819158565</v>
@@ -6780,13 +6789,13 @@
         <v>1569</v>
       </c>
       <c r="H58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K58">
         <v>64</v>
@@ -6813,7 +6822,7 @@
         <v>24.87804878</v>
       </c>
       <c r="W58" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X58">
         <v>-0.03956</v>
@@ -6845,7 +6854,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>44940.35853839121</v>
@@ -6863,13 +6872,13 @@
         <v>1592</v>
       </c>
       <c r="H59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K59">
         <v>61</v>
@@ -6896,7 +6905,7 @@
         <v>24.69565217</v>
       </c>
       <c r="W59" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X59">
         <v>-0.00793</v>
@@ -6928,7 +6937,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2">
         <v>44940.35883177083</v>
@@ -6946,13 +6955,13 @@
         <v>1594</v>
       </c>
       <c r="H60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J60" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K60">
         <v>60</v>
@@ -6979,7 +6988,7 @@
         <v>22</v>
       </c>
       <c r="W60" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X60">
         <v>-1.347826</v>
@@ -7011,7 +7020,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2">
         <v>44940.35916414352</v>
@@ -7029,13 +7038,13 @@
         <v>1658</v>
       </c>
       <c r="H61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J61" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K61">
         <v>71</v>
@@ -7062,7 +7071,7 @@
         <v>23.328125</v>
       </c>
       <c r="W61" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X61">
         <v>0.020752</v>
@@ -7094,7 +7103,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>44940.35951258102</v>
@@ -7112,13 +7121,13 @@
         <v>1682</v>
       </c>
       <c r="H62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J62" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K62">
         <v>72</v>
@@ -7145,7 +7154,7 @@
         <v>24.75</v>
       </c>
       <c r="W62" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X62">
         <v>0.059245</v>
@@ -7177,7 +7186,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>44940.35980234954</v>
@@ -7195,13 +7204,13 @@
         <v>1684</v>
       </c>
       <c r="H63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J63" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K63">
         <v>75</v>
@@ -7228,7 +7237,7 @@
         <v>22.5</v>
       </c>
       <c r="W63" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X63">
         <v>-1.125</v>
@@ -7260,7 +7269,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>44940.36013804398</v>
@@ -7278,13 +7287,13 @@
         <v>1750</v>
       </c>
       <c r="H64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J64" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K64">
         <v>77</v>
@@ -7311,7 +7320,7 @@
         <v>26.98484848</v>
       </c>
       <c r="W64" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X64">
         <v>0.067952</v>
@@ -7338,12 +7347,12 @@
         <v>23.10038</v>
       </c>
     </row>
-    <row r="65" spans="1:31">
+    <row r="65" spans="1:32">
       <c r="A65" t="s">
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2">
         <v>44940.36048796296</v>
@@ -7361,13 +7370,13 @@
         <v>1774</v>
       </c>
       <c r="H65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K65">
         <v>72</v>
@@ -7394,7 +7403,7 @@
         <v>23.125</v>
       </c>
       <c r="W65" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X65">
         <v>-0.160827</v>
@@ -7421,12 +7430,12 @@
         <v>22.803445</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
+    <row r="66" spans="1:32">
       <c r="A66" t="s">
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2">
         <v>44940.36076875</v>
@@ -7444,13 +7453,13 @@
         <v>1775</v>
       </c>
       <c r="H66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K66">
         <v>71</v>
@@ -7477,7 +7486,7 @@
         <v>24</v>
       </c>
       <c r="W66" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X66">
         <v>0.875</v>
@@ -7504,12 +7513,12 @@
         <v>22.790573</v>
       </c>
     </row>
-    <row r="67" spans="1:31">
+    <row r="67" spans="1:32">
       <c r="A67" t="s">
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>44940.36110262731</v>
@@ -7527,13 +7536,13 @@
         <v>1815</v>
       </c>
       <c r="H67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K67">
         <v>58</v>
@@ -7560,7 +7569,7 @@
         <v>26.35</v>
       </c>
       <c r="W67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X67">
         <v>0.05875</v>
@@ -7587,12 +7596,12 @@
         <v>22.226537</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
+    <row r="68" spans="1:32">
       <c r="A68" t="s">
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2">
         <v>44940.36144950231</v>
@@ -7610,13 +7619,13 @@
         <v>1864</v>
       </c>
       <c r="H68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J68" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K68">
         <v>85</v>
@@ -7643,7 +7652,7 @@
         <v>24.48979592</v>
       </c>
       <c r="W68" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X68">
         <v>-0.037963</v>
@@ -7670,12 +7679,12 @@
         <v>21.599353</v>
       </c>
     </row>
-    <row r="69" spans="1:31">
+    <row r="69" spans="1:32">
       <c r="A69" t="s">
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2">
         <v>44940.36174215277</v>
@@ -7693,13 +7702,13 @@
         <v>1865</v>
       </c>
       <c r="H69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J69" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K69">
         <v>85</v>
@@ -7726,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="W69" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X69">
         <v>2.510204</v>
@@ -7753,12 +7762,12 @@
         <v>21.58556</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
+    <row r="70" spans="1:32">
       <c r="A70" t="s">
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2">
         <v>44940.3620759375</v>
@@ -7776,13 +7785,13 @@
         <v>1906</v>
       </c>
       <c r="H70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I70" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K70">
         <v>92</v>
@@ -7809,7 +7818,7 @@
         <v>21.90243902</v>
       </c>
       <c r="W70" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X70">
         <v>-0.124331</v>
@@ -7835,13 +7844,16 @@
       <c r="AE70">
         <v>21.137569</v>
       </c>
-    </row>
-    <row r="71" spans="1:31">
+      <c r="AF70" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32">
       <c r="A71" t="s">
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2">
         <v>44940.36242248843</v>
@@ -7859,13 +7871,13 @@
         <v>1930</v>
       </c>
       <c r="H71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I71" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J71" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K71">
         <v>87</v>
@@ -7892,7 +7904,7 @@
         <v>16.66666667</v>
       </c>
       <c r="W71" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X71">
         <v>-0.218157</v>
@@ -7919,12 +7931,12 @@
         <v>20.945661</v>
       </c>
     </row>
-    <row r="72" spans="1:31">
+    <row r="72" spans="1:32">
       <c r="A72" t="s">
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2">
         <v>44940.36271908565</v>
@@ -7942,13 +7954,13 @@
         <v>1932</v>
       </c>
       <c r="H72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I72" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J72" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K72">
         <v>86</v>
@@ -7975,7 +7987,7 @@
         <v>17</v>
       </c>
       <c r="W72" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X72">
         <v>0.166667</v>
@@ -8002,12 +8014,12 @@
         <v>20.92959</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:32">
       <c r="A73" t="s">
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2">
         <v>44940.36304903936</v>
@@ -8025,13 +8037,13 @@
         <v>1998</v>
       </c>
       <c r="H73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I73" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J73" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K73">
         <v>71</v>
@@ -8058,7 +8070,7 @@
         <v>16.8030303</v>
       </c>
       <c r="W73" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X73">
         <v>-0.002984</v>
@@ -8085,12 +8097,12 @@
         <v>20.428063</v>
       </c>
     </row>
-    <row r="74" spans="1:31">
+    <row r="74" spans="1:32">
       <c r="A74" t="s">
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2">
         <v>44940.36339696759</v>
@@ -8108,13 +8120,13 @@
         <v>2022</v>
       </c>
       <c r="H74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J74" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K74">
         <v>81</v>
@@ -8141,7 +8153,7 @@
         <v>17.91666667</v>
       </c>
       <c r="W74" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X74">
         <v>0.046402</v>
@@ -8168,12 +8180,12 @@
         <v>20.246278</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
+    <row r="75" spans="1:32">
       <c r="A75" t="s">
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2">
         <v>44940.36368710648</v>
@@ -8191,13 +8203,13 @@
         <v>2024</v>
       </c>
       <c r="H75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J75" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K75">
         <v>84</v>
@@ -8224,7 +8236,7 @@
         <v>16</v>
       </c>
       <c r="W75" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X75">
         <v>-0.958333</v>
@@ -8251,12 +8263,12 @@
         <v>20.233048</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:32">
       <c r="A76" t="s">
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2">
         <v>44940.36402215277</v>
@@ -8274,13 +8286,13 @@
         <v>2065</v>
       </c>
       <c r="H76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I76" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J76" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K76">
         <v>109</v>
@@ -8307,7 +8319,7 @@
         <v>23.12195122</v>
       </c>
       <c r="W76" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X76">
         <v>0.173706</v>
@@ -8334,12 +8346,12 @@
         <v>19.86037</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:32">
       <c r="A77" t="s">
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C77" s="2">
         <v>44940.36436971065</v>
@@ -8357,13 +8369,13 @@
         <v>2113</v>
       </c>
       <c r="H77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J77" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K77">
         <v>81</v>
@@ -8390,7 +8402,7 @@
         <v>20.79166667</v>
       </c>
       <c r="W77" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X77">
         <v>-0.048548</v>
@@ -8417,12 +8429,12 @@
         <v>19.508928</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:32">
       <c r="A78" t="s">
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2">
         <v>44940.36466076389</v>
@@ -8440,13 +8452,13 @@
         <v>2115</v>
       </c>
       <c r="H78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I78" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J78" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K78">
         <v>81</v>
@@ -8473,7 +8485,7 @@
         <v>20</v>
       </c>
       <c r="W78" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X78">
         <v>-0.395833</v>
@@ -8500,12 +8512,12 @@
         <v>19.495714</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:32">
       <c r="A79" t="s">
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C79" s="2">
         <v>44940.36499581019</v>
@@ -8523,13 +8535,13 @@
         <v>2156</v>
       </c>
       <c r="H79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I79" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J79" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K79">
         <v>90</v>
@@ -8556,7 +8568,7 @@
         <v>17.97560976</v>
       </c>
       <c r="W79" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X79">
         <v>-0.049375</v>
@@ -8583,12 +8595,12 @@
         <v>19.263987</v>
       </c>
     </row>
-    <row r="80" spans="1:31">
+    <row r="80" spans="1:32">
       <c r="A80" t="s">
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C80" s="2">
         <v>44940.36534358796</v>
@@ -8606,13 +8618,13 @@
         <v>2180</v>
       </c>
       <c r="H80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I80" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J80" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K80">
         <v>105</v>
@@ -8639,7 +8651,7 @@
         <v>20.5</v>
       </c>
       <c r="W80" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X80">
         <v>0.105183</v>
@@ -8671,7 +8683,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2">
         <v>44940.36563915509</v>
@@ -8689,13 +8701,13 @@
         <v>2182</v>
       </c>
       <c r="H81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I81" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J81" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K81">
         <v>99</v>
@@ -8722,7 +8734,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X81">
         <v>0.25</v>
@@ -8754,7 +8766,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2">
         <v>44940.36597112269</v>
@@ -8772,13 +8784,13 @@
         <v>2247</v>
       </c>
       <c r="H82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I82" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J82" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K82">
         <v>119</v>
@@ -8805,7 +8817,7 @@
         <v>24.24615385</v>
       </c>
       <c r="W82" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X82">
         <v>0.049941</v>
@@ -8837,7 +8849,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C83" s="2">
         <v>44940.3663169213</v>
@@ -8855,13 +8867,13 @@
         <v>2271</v>
       </c>
       <c r="H83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I83" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J83" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K83">
         <v>79</v>
@@ -8888,7 +8900,7 @@
         <v>19.70833333</v>
       </c>
       <c r="W83" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X83">
         <v>-0.189076</v>
@@ -8920,7 +8932,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84" s="2">
         <v>44940.36660665509</v>
@@ -8938,13 +8950,13 @@
         <v>2273</v>
       </c>
       <c r="H84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I84" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J84" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K84">
         <v>73</v>
@@ -8971,7 +8983,7 @@
         <v>16.5</v>
       </c>
       <c r="W84" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X84">
         <v>-1.604167</v>
@@ -9003,7 +9015,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2">
         <v>44940.36694467592</v>
@@ -9021,13 +9033,13 @@
         <v>2339</v>
       </c>
       <c r="H85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I85" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J85" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K85">
         <v>59</v>
@@ -9054,7 +9066,7 @@
         <v>19.36363636</v>
       </c>
       <c r="W85" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X85">
         <v>0.043388</v>
@@ -9086,7 +9098,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2">
         <v>44940.36729467593</v>
@@ -9104,13 +9116,13 @@
         <v>2362</v>
       </c>
       <c r="H86" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I86" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J86" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K86">
         <v>75</v>
@@ -9137,7 +9149,7 @@
         <v>15.86956522</v>
       </c>
       <c r="W86" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X86">
         <v>-0.151916</v>
@@ -9169,7 +9181,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C87" s="2">
         <v>44940.36757986111</v>
@@ -9187,13 +9199,13 @@
         <v>2364</v>
       </c>
       <c r="H87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I87" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K87">
         <v>71</v>
@@ -9220,7 +9232,7 @@
         <v>16.5</v>
       </c>
       <c r="W87" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X87">
         <v>0.315217</v>
@@ -9252,7 +9264,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2">
         <v>44940.36791641204</v>
@@ -9270,13 +9282,13 @@
         <v>2405</v>
       </c>
       <c r="H88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I88" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J88" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K88">
         <v>80</v>
@@ -9303,7 +9315,7 @@
         <v>15.56097561</v>
       </c>
       <c r="W88" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X88">
         <v>-0.022903</v>
@@ -9335,7 +9347,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C89" s="2">
         <v>44940.36826293982</v>
@@ -9353,13 +9365,13 @@
         <v>2453</v>
       </c>
       <c r="H89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I89" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J89" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K89">
         <v>77</v>
@@ -9386,7 +9398,7 @@
         <v>16.3125</v>
       </c>
       <c r="W89" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X89">
         <v>0.015657</v>
@@ -9418,7 +9430,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>44940.36855534722</v>
@@ -9436,13 +9448,13 @@
         <v>2455</v>
       </c>
       <c r="H90" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I90" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J90" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K90">
         <v>78</v>
@@ -9469,7 +9481,7 @@
         <v>16.5</v>
       </c>
       <c r="W90" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X90">
         <v>0.09375</v>
@@ -9501,7 +9513,7 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C91" s="2">
         <v>44940.36888913195</v>
@@ -9519,13 +9531,13 @@
         <v>2496</v>
       </c>
       <c r="H91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I91" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J91" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K91">
         <v>90</v>
@@ -9552,7 +9564,7 @@
         <v>16.58536585</v>
       </c>
       <c r="W91" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X91">
         <v>0.002082</v>
@@ -9584,7 +9596,7 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2">
         <v>44940.36923621528</v>
@@ -9602,13 +9614,13 @@
         <v>2520</v>
       </c>
       <c r="H92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I92" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J92" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K92">
         <v>102</v>
@@ -9635,7 +9647,7 @@
         <v>17.79166667</v>
       </c>
       <c r="W92" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X92">
         <v>0.050263</v>
@@ -9667,7 +9679,7 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C93" s="2">
         <v>44940.36952689815</v>
@@ -9685,13 +9697,13 @@
         <v>2521</v>
       </c>
       <c r="H93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I93" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J93" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K93">
         <v>106</v>
@@ -9718,7 +9730,7 @@
         <v>14</v>
       </c>
       <c r="W93" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X93">
         <v>-3.791667</v>
@@ -9750,7 +9762,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2">
         <v>44940.36986238426</v>
@@ -9768,13 +9780,13 @@
         <v>2586</v>
       </c>
       <c r="H94" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I94" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J94" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K94">
         <v>121</v>
@@ -9801,7 +9813,7 @@
         <v>20.95384615</v>
       </c>
       <c r="W94" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X94">
         <v>0.106982</v>
@@ -9833,7 +9845,7 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C95" s="2">
         <v>44940.37021008102</v>
@@ -9851,13 +9863,13 @@
         <v>2610</v>
       </c>
       <c r="H95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I95" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K95">
         <v>139</v>
@@ -9884,7 +9896,7 @@
         <v>20.54166667</v>
       </c>
       <c r="W95" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X95">
         <v>-0.017174</v>
@@ -9916,7 +9928,7 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2">
         <v>44940.37050086806</v>
@@ -9934,13 +9946,13 @@
         <v>2611</v>
       </c>
       <c r="H96" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I96" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J96" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K96">
         <v>140</v>
@@ -9967,7 +9979,7 @@
         <v>15</v>
       </c>
       <c r="W96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X96">
         <v>-5.541667</v>
@@ -9999,7 +10011,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2">
         <v>44940.37083533565</v>
@@ -10017,13 +10029,13 @@
         <v>2677</v>
       </c>
       <c r="H97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I97" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J97" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K97">
         <v>124</v>
@@ -10050,7 +10062,7 @@
         <v>21.1969697</v>
       </c>
       <c r="W97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X97">
         <v>0.093893</v>
@@ -10082,7 +10094,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C98" s="2">
         <v>44940.3711837963</v>
@@ -10100,13 +10112,13 @@
         <v>2700</v>
       </c>
       <c r="H98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I98" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J98" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K98">
         <v>127</v>
@@ -10133,7 +10145,7 @@
         <v>20.43478261</v>
       </c>
       <c r="W98" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X98">
         <v>-0.033139</v>
@@ -10165,7 +10177,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C99" s="2">
         <v>44940.371474375</v>
@@ -10183,13 +10195,13 @@
         <v>2702</v>
       </c>
       <c r="H99" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I99" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J99" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K99">
         <v>129</v>
@@ -10216,7 +10228,7 @@
         <v>16.5</v>
       </c>
       <c r="W99" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X99">
         <v>-1.967391</v>
@@ -10248,7 +10260,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C100" s="2">
         <v>44940.37180888889</v>
@@ -10266,13 +10278,13 @@
         <v>2744</v>
       </c>
       <c r="H100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I100" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J100" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K100">
         <v>122</v>
@@ -10299,7 +10311,7 @@
         <v>16.47619048</v>
       </c>
       <c r="W100" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X100">
         <v>-0.000567</v>
@@ -10331,7 +10343,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C101" s="2">
         <v>44940.37215681713</v>
@@ -10349,13 +10361,13 @@
         <v>2767</v>
       </c>
       <c r="H101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I101" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J101" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K101">
         <v>117</v>
@@ -10382,7 +10394,7 @@
         <v>17</v>
       </c>
       <c r="W101" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X101">
         <v>0.022774</v>
@@ -10414,7 +10426,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C102" s="2">
         <v>44940.37244690972</v>
@@ -10432,13 +10444,13 @@
         <v>2793</v>
       </c>
       <c r="H102" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I102" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J102" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K102">
         <v>120</v>
@@ -10465,7 +10477,7 @@
         <v>18.15384615</v>
       </c>
       <c r="W102" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X102">
         <v>0.044379</v>
@@ -10497,7 +10509,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C103" s="2">
         <v>44940.37278292824</v>
@@ -10515,13 +10527,13 @@
         <v>2834</v>
       </c>
       <c r="H103" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J103" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K103">
         <v>156</v>
@@ -10548,7 +10560,7 @@
         <v>17.31707317</v>
       </c>
       <c r="W103" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X103">
         <v>-0.020409</v>
@@ -10580,7 +10592,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C104" s="2">
         <v>44940.37312947917</v>
@@ -10598,13 +10610,13 @@
         <v>2858</v>
       </c>
       <c r="H104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I104" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J104" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K104">
         <v>120</v>
@@ -10631,7 +10643,7 @@
         <v>16.625</v>
       </c>
       <c r="W104" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X104">
         <v>-0.028836</v>
@@ -10663,7 +10675,7 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C105" s="2">
         <v>44940.37342081019</v>
@@ -10681,13 +10693,13 @@
         <v>2860</v>
       </c>
       <c r="H105" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I105" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J105" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K105">
         <v>113</v>
@@ -10714,7 +10726,7 @@
         <v>19</v>
       </c>
       <c r="W105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X105">
         <v>1.1875</v>
@@ -10746,7 +10758,7 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C106" s="2">
         <v>44940.37375604167</v>
@@ -10764,13 +10776,13 @@
         <v>2925</v>
       </c>
       <c r="H106" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J106" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K106">
         <v>169</v>
@@ -10797,7 +10809,7 @@
         <v>15.50769231</v>
       </c>
       <c r="W106" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X106">
         <v>-0.053728</v>
@@ -10829,7 +10841,7 @@
         <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C107" s="2">
         <v>44940.37410366898</v>
@@ -10847,13 +10859,13 @@
         <v>2949</v>
       </c>
       <c r="H107" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I107" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J107" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K107">
         <v>128</v>
@@ -10880,7 +10892,7 @@
         <v>17.125</v>
       </c>
       <c r="W107" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X107">
         <v>0.067388</v>
@@ -10912,7 +10924,7 @@
         <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C108" s="2">
         <v>44940.37439447916</v>
@@ -10930,13 +10942,13 @@
         <v>2950</v>
       </c>
       <c r="H108" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I108" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J108" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K108">
         <v>125</v>
@@ -10963,7 +10975,7 @@
         <v>15</v>
       </c>
       <c r="W108" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X108">
         <v>-2.125</v>
@@ -10995,7 +11007,7 @@
         <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C109" s="2">
         <v>44940.37472954861</v>
@@ -11013,13 +11025,13 @@
         <v>2991</v>
       </c>
       <c r="H109" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I109" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J109" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K109">
         <v>87</v>
@@ -11046,7 +11058,7 @@
         <v>16.24390244</v>
       </c>
       <c r="W109" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X109">
         <v>0.030339</v>
@@ -11078,7 +11090,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C110" s="2">
         <v>44940.3750762037</v>
@@ -11096,13 +11108,13 @@
         <v>3039</v>
       </c>
       <c r="H110" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I110" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J110" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K110">
         <v>155</v>
@@ -11129,7 +11141,7 @@
         <v>16.625</v>
       </c>
       <c r="W110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X110">
         <v>0.007939999999999999</v>
@@ -11161,7 +11173,7 @@
         <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C111" s="2">
         <v>44940.37536677083</v>
@@ -11179,13 +11191,13 @@
         <v>3040</v>
       </c>
       <c r="H111" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I111" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J111" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K111">
         <v>154</v>
@@ -11212,7 +11224,7 @@
         <v>17</v>
       </c>
       <c r="W111" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X111">
         <v>0.375</v>
@@ -11244,7 +11256,7 @@
         <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C112" s="2">
         <v>44940.37570267361</v>
@@ -11262,13 +11274,13 @@
         <v>3081</v>
       </c>
       <c r="H112" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I112" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J112" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K112">
         <v>185</v>
@@ -11295,7 +11307,7 @@
         <v>16.12195122</v>
       </c>
       <c r="W112" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X112">
         <v>-0.021416</v>
@@ -11327,7 +11339,7 @@
         <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C113" s="2">
         <v>44940.37605122685</v>
@@ -11345,13 +11357,13 @@
         <v>3105</v>
       </c>
       <c r="H113" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I113" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J113" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K113">
         <v>244</v>
@@ -11378,7 +11390,7 @@
         <v>14.125</v>
       </c>
       <c r="W113" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X113">
         <v>-0.083206</v>
@@ -11410,7 +11422,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C114" s="2">
         <v>44940.37634334491</v>
@@ -11428,13 +11440,13 @@
         <v>3107</v>
       </c>
       <c r="H114" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I114" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J114" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K114">
         <v>236</v>
@@ -11461,7 +11473,7 @@
         <v>6.5</v>
       </c>
       <c r="W114" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X114">
         <v>-3.8125</v>
@@ -11493,7 +11505,7 @@
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C115" s="2">
         <v>44940.37667689815</v>
@@ -11511,13 +11523,13 @@
         <v>3171</v>
       </c>
       <c r="H115" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I115" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J115" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K115">
         <v>216</v>
@@ -11544,7 +11556,7 @@
         <v>16.859375</v>
       </c>
       <c r="W115" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X115">
         <v>0.161865</v>
@@ -11576,7 +11588,7 @@
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C116" s="2">
         <v>44940.37702810185</v>
@@ -11594,13 +11606,13 @@
         <v>3195</v>
       </c>
       <c r="H116" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I116" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J116" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K116">
         <v>110</v>
@@ -11627,7 +11639,7 @@
         <v>17.58333333</v>
       </c>
       <c r="W116" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X116">
         <v>0.030165</v>
@@ -11659,7 +11671,7 @@
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C117" s="2">
         <v>44940.37731377315</v>
@@ -11677,13 +11689,13 @@
         <v>3196</v>
       </c>
       <c r="H117" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I117" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J117" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K117">
         <v>107</v>
@@ -11710,7 +11722,7 @@
         <v>17</v>
       </c>
       <c r="W117" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X117">
         <v>-0.583333</v>
@@ -11742,7 +11754,7 @@
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C118" s="2">
         <v>44940.37764974537</v>
@@ -11760,13 +11772,13 @@
         <v>3260</v>
       </c>
       <c r="H118" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I118" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J118" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K118">
         <v>184</v>
@@ -11793,7 +11805,7 @@
         <v>18.640625</v>
       </c>
       <c r="W118" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X118">
         <v>0.025635</v>
@@ -11825,7 +11837,7 @@
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C119" s="2">
         <v>44940.37799662037</v>
@@ -11843,13 +11855,13 @@
         <v>3284</v>
       </c>
       <c r="H119" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I119" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J119" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K119">
         <v>173</v>
@@ -11876,7 +11888,7 @@
         <v>17.04166667</v>
       </c>
       <c r="W119" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X119">
         <v>-0.066623</v>
@@ -11908,7 +11920,7 @@
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C120" s="2">
         <v>44940.37828671296</v>
@@ -11926,13 +11938,13 @@
         <v>3286</v>
       </c>
       <c r="H120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I120" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J120" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K120">
         <v>177</v>
@@ -11959,7 +11971,7 @@
         <v>15</v>
       </c>
       <c r="W120" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X120">
         <v>-1.020833</v>
@@ -11991,7 +12003,7 @@
         <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C121" s="2">
         <v>44940.37862175926</v>
@@ -12009,13 +12021,13 @@
         <v>3350</v>
       </c>
       <c r="H121" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I121" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J121" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K121">
         <v>198</v>
@@ -12042,7 +12054,7 @@
         <v>16.6875</v>
       </c>
       <c r="W121" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X121">
         <v>0.026367</v>
@@ -12074,7 +12086,7 @@
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C122" s="2">
         <v>44940.37897061343</v>
@@ -12092,13 +12104,13 @@
         <v>3372</v>
       </c>
       <c r="H122" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I122" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J122" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K122">
         <v>172</v>
@@ -12125,7 +12137,7 @@
         <v>16.68181818</v>
       </c>
       <c r="W122" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X122">
         <v>-0.000258</v>
@@ -12157,7 +12169,7 @@
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C123" s="2">
         <v>44940.37926053241</v>
@@ -12175,13 +12187,13 @@
         <v>3374</v>
       </c>
       <c r="H123" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I123" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J123" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K123">
         <v>166</v>
@@ -12208,7 +12220,7 @@
         <v>17</v>
       </c>
       <c r="W123" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X123">
         <v>0.159091</v>
@@ -12240,7 +12252,7 @@
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C124" s="2">
         <v>44940.37959600695</v>
@@ -12258,13 +12270,13 @@
         <v>3414</v>
       </c>
       <c r="H124" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I124" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J124" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K124">
         <v>182</v>
@@ -12291,7 +12303,7 @@
         <v>17.225</v>
       </c>
       <c r="W124" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X124">
         <v>0.005625</v>
@@ -12323,7 +12335,7 @@
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C125" s="2">
         <v>44940.37994346065</v>
@@ -12341,13 +12353,13 @@
         <v>3461</v>
       </c>
       <c r="H125" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I125" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J125" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K125">
         <v>177</v>
@@ -12374,7 +12386,7 @@
         <v>16.0212766</v>
       </c>
       <c r="W125" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X125">
         <v>-0.025611</v>
@@ -12406,7 +12418,7 @@
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C126" s="2">
         <v>44940.38023311343</v>
@@ -12424,13 +12436,13 @@
         <v>3463</v>
       </c>
       <c r="H126" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I126" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J126" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K126">
         <v>171</v>
@@ -12457,7 +12469,7 @@
         <v>15.5</v>
       </c>
       <c r="W126" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X126">
         <v>-0.260638</v>
@@ -12489,7 +12501,7 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C127" s="2">
         <v>44940.38056954861</v>
@@ -12507,13 +12519,13 @@
         <v>3504</v>
       </c>
       <c r="H127" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I127" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J127" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K127">
         <v>179</v>
@@ -12540,7 +12552,7 @@
         <v>17.36585366</v>
       </c>
       <c r="W127" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X127">
         <v>0.045509</v>
@@ -12572,7 +12584,7 @@
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C128" s="2">
         <v>44940.38091631945</v>
@@ -12590,13 +12602,13 @@
         <v>3527</v>
       </c>
       <c r="H128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I128" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J128" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K128">
         <v>176</v>
@@ -12623,7 +12635,7 @@
         <v>17.17391304</v>
       </c>
       <c r="W128" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X128">
         <v>-0.008345</v>
@@ -12655,7 +12667,7 @@
         <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C129" s="2">
         <v>44940.38120711806</v>
@@ -12673,13 +12685,13 @@
         <v>3529</v>
       </c>
       <c r="H129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I129" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J129" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K129">
         <v>173</v>
@@ -12706,7 +12718,7 @@
         <v>16</v>
       </c>
       <c r="W129" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X129">
         <v>-0.586957</v>
@@ -12738,7 +12750,7 @@
         <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C130" s="2">
         <v>44940.38155128472</v>
@@ -12756,13 +12768,13 @@
         <v>3594</v>
       </c>
       <c r="H130" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I130" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J130" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K130">
         <v>173</v>
@@ -12789,7 +12801,7 @@
         <v>17.66153846</v>
       </c>
       <c r="W130" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X130">
         <v>0.025562</v>
@@ -12821,7 +12833,7 @@
         <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C131" s="2">
         <v>44940.38189346065</v>
@@ -12839,13 +12851,13 @@
         <v>3617</v>
       </c>
       <c r="H131" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I131" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J131" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K131">
         <v>168</v>
@@ -12872,7 +12884,7 @@
         <v>16.91304348</v>
       </c>
       <c r="W131" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X131">
         <v>-0.032543</v>
@@ -12904,7 +12916,7 @@
         <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C132" s="2">
         <v>44940.38251856482</v>
@@ -12922,13 +12934,13 @@
         <v>3683</v>
       </c>
       <c r="H132" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I132" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J132" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K132">
         <v>174</v>
@@ -12955,7 +12967,7 @@
         <v>16.92424242</v>
       </c>
       <c r="W132" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X132">
         <v>0.00017</v>
@@ -12987,7 +12999,7 @@
         <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C133" s="2">
         <v>44940.382865625</v>
@@ -13005,13 +13017,13 @@
         <v>3706</v>
       </c>
       <c r="H133" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I133" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J133" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K133">
         <v>146</v>
@@ -13038,7 +13050,7 @@
         <v>17.7826087</v>
       </c>
       <c r="W133" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X133">
         <v>0.03732</v>
@@ -13070,7 +13082,7 @@
         <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C134" s="2">
         <v>44940.3831566088</v>
@@ -13088,13 +13100,13 @@
         <v>3708</v>
       </c>
       <c r="H134" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I134" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J134" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K134">
         <v>152</v>
@@ -13121,7 +13133,7 @@
         <v>15</v>
       </c>
       <c r="W134" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X134">
         <v>-1.391304</v>
@@ -13153,7 +13165,7 @@
         <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C135" s="2">
         <v>44940.38349574074</v>
@@ -13171,13 +13183,13 @@
         <v>3749</v>
       </c>
       <c r="H135" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I135" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J135" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K135">
         <v>182</v>
@@ -13204,7 +13216,7 @@
         <v>18.07317073</v>
       </c>
       <c r="W135" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X135">
         <v>0.07495499999999999</v>
@@ -13236,7 +13248,7 @@
         <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C136" s="2">
         <v>44940.38384002315</v>
@@ -13254,13 +13266,13 @@
         <v>3796</v>
       </c>
       <c r="H136" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I136" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J136" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K136">
         <v>183</v>
@@ -13287,7 +13299,7 @@
         <v>17.78723404</v>
       </c>
       <c r="W136" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X136">
         <v>-0.006084</v>
@@ -13319,7 +13331,7 @@
         <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C137" s="2">
         <v>44940.38413138889</v>
@@ -13337,13 +13349,13 @@
         <v>3798</v>
       </c>
       <c r="H137" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I137" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J137" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K137">
         <v>180</v>
@@ -13370,7 +13382,7 @@
         <v>19</v>
       </c>
       <c r="W137" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X137">
         <v>0.606383</v>
@@ -13402,7 +13414,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C138" s="2">
         <v>44940.38446775463</v>
@@ -13420,13 +13432,13 @@
         <v>3839</v>
       </c>
       <c r="H138" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I138" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J138" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K138">
         <v>182</v>
@@ -13453,7 +13465,7 @@
         <v>17.48780488</v>
       </c>
       <c r="W138" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X138">
         <v>-0.036883</v>
@@ -13485,7 +13497,7 @@
         <v>25</v>
       </c>
       <c r="B139" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C139" s="2">
         <v>44940.38481304398</v>
@@ -13503,13 +13515,13 @@
         <v>3862</v>
       </c>
       <c r="H139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I139" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J139" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K139">
         <v>179</v>
@@ -13536,7 +13548,7 @@
         <v>16.56521739</v>
       </c>
       <c r="W139" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X139">
         <v>-0.040112</v>
@@ -13568,7 +13580,7 @@
         <v>25</v>
       </c>
       <c r="B140" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C140" s="2">
         <v>44940.38510621528</v>
@@ -13586,13 +13598,13 @@
         <v>3864</v>
       </c>
       <c r="H140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I140" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J140" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K140">
         <v>182</v>
@@ -13619,7 +13631,7 @@
         <v>15</v>
       </c>
       <c r="W140" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X140">
         <v>-0.782609</v>
@@ -13651,7 +13663,7 @@
         <v>25</v>
       </c>
       <c r="B141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C141" s="2">
         <v>44940.38544024306</v>
@@ -13669,13 +13681,13 @@
         <v>3928</v>
       </c>
       <c r="H141" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I141" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J141" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K141">
         <v>179</v>
@@ -13702,7 +13714,7 @@
         <v>16.09375</v>
       </c>
       <c r="W141" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X141">
         <v>0.01709</v>
@@ -13734,7 +13746,7 @@
         <v>25</v>
       </c>
       <c r="B142" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C142" s="2">
         <v>44940.38578652778</v>
@@ -13752,13 +13764,13 @@
         <v>3951</v>
       </c>
       <c r="H142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I142" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J142" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K142">
         <v>177</v>
@@ -13785,7 +13797,7 @@
         <v>15.56521739</v>
       </c>
       <c r="W142" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X142">
         <v>-0.02298</v>
@@ -13817,7 +13829,7 @@
         <v>25</v>
       </c>
       <c r="B143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C143" s="2">
         <v>44940.38607760417</v>
@@ -13835,13 +13847,13 @@
         <v>3953</v>
       </c>
       <c r="H143" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I143" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J143" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K143">
         <v>177</v>
@@ -13868,7 +13880,7 @@
         <v>16.5</v>
       </c>
       <c r="W143" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X143">
         <v>0.467391</v>
@@ -13900,7 +13912,7 @@
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C144" s="2">
         <v>44940.386411875</v>
@@ -13918,13 +13930,13 @@
         <v>4017</v>
       </c>
       <c r="H144" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I144" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J144" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K144">
         <v>177</v>
@@ -13951,7 +13963,7 @@
         <v>16.515625</v>
       </c>
       <c r="W144" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X144">
         <v>0.000244</v>
@@ -13985,10 +13997,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE69"/>
+  <dimension ref="A1:AF69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -14082,13 +14094,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>44940.38676024305</v>
@@ -14106,13 +14121,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K2">
         <v>177</v>
@@ -14139,7 +14154,7 @@
         <v>-51.73913043</v>
       </c>
       <c r="W2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Y2">
         <v>-51.73913</v>
@@ -14148,12 +14163,12 @@
         <v>-51.73913</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2">
         <v>44940.38705238426</v>
@@ -14171,13 +14186,13 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K3">
         <v>165</v>
@@ -14204,7 +14219,7 @@
         <v>-92</v>
       </c>
       <c r="W3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X3">
         <v>-20.130435</v>
@@ -14225,12 +14240,12 @@
         <v>-92</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>44940.40132559028</v>
@@ -14248,13 +14263,13 @@
         <v>1270</v>
       </c>
       <c r="H4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -14281,7 +14296,7 @@
         <v>-41.10646688</v>
       </c>
       <c r="W4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X4">
         <v>0.040137</v>
@@ -14308,12 +14323,12 @@
         <v>-39.585893</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2">
         <v>44940.40167709491</v>
@@ -14331,13 +14346,13 @@
         <v>1293</v>
       </c>
       <c r="H5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K5">
         <v>66</v>
@@ -14364,7 +14379,7 @@
         <v>-20.56521739</v>
       </c>
       <c r="W5" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X5">
         <v>0.8930979999999999</v>
@@ -14391,12 +14406,12 @@
         <v>-24.829237</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>44940.40227767361</v>
@@ -14414,13 +14429,13 @@
         <v>1315</v>
       </c>
       <c r="H6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K6">
         <v>68</v>
@@ -14447,7 +14462,7 @@
         <v>-22.22727273</v>
       </c>
       <c r="W6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X6">
         <v>-0.075548</v>
@@ -14474,12 +14489,12 @@
         <v>-19.144189</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2">
         <v>44940.40261505787</v>
@@ -14497,13 +14512,13 @@
         <v>1380</v>
       </c>
       <c r="H7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K7">
         <v>70</v>
@@ -14530,7 +14545,7 @@
         <v>-20.2</v>
       </c>
       <c r="W7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X7">
         <v>0.031189</v>
@@ -14557,12 +14572,12 @@
         <v>-20.756574</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>44940.40297104167</v>
@@ -14580,13 +14595,13 @@
         <v>1404</v>
       </c>
       <c r="H8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K8">
         <v>66</v>
@@ -14613,7 +14628,7 @@
         <v>-16.20833333</v>
       </c>
       <c r="W8" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X8">
         <v>0.166319</v>
@@ -14640,12 +14655,12 @@
         <v>-21.820441</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>44940.40324975694</v>
@@ -14663,13 +14678,13 @@
         <v>1405</v>
       </c>
       <c r="H9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K9">
         <v>60</v>
@@ -14696,7 +14711,7 @@
         <v>-29</v>
       </c>
       <c r="W9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X9">
         <v>-12.791667</v>
@@ -14723,12 +14738,12 @@
         <v>-21.884167</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>44940.40358505787</v>
@@ -14746,13 +14761,13 @@
         <v>1446</v>
       </c>
       <c r="H10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K10">
         <v>67</v>
@@ -14779,7 +14794,7 @@
         <v>-21.87804878</v>
       </c>
       <c r="W10" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X10">
         <v>0.173706</v>
@@ -14806,12 +14821,12 @@
         <v>-22.565046</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>44940.40393440973</v>
@@ -14829,13 +14844,13 @@
         <v>1495</v>
       </c>
       <c r="H11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J11" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K11">
         <v>61</v>
@@ -14862,7 +14877,7 @@
         <v>-20.30612245</v>
       </c>
       <c r="W11" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X11">
         <v>0.03208</v>
@@ -14889,12 +14904,12 @@
         <v>-21.021563</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>44940.40422270833</v>
@@ -14912,13 +14927,13 @@
         <v>1496</v>
       </c>
       <c r="H12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J12" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K12">
         <v>65</v>
@@ -14945,7 +14960,7 @@
         <v>-19</v>
       </c>
       <c r="W12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X12">
         <v>1.306122</v>
@@ -14972,12 +14987,12 @@
         <v>-20.979887</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2">
         <v>44940.40455836806</v>
@@ -14995,13 +15010,13 @@
         <v>1537</v>
       </c>
       <c r="H13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J13" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K13">
         <v>64</v>
@@ -15028,7 +15043,7 @@
         <v>-19.70731707</v>
       </c>
       <c r="W13" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X13">
         <v>-0.017252</v>
@@ -15055,12 +15070,12 @@
         <v>-19.164354</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>44940.40490565972</v>
@@ -15078,13 +15093,13 @@
         <v>1560</v>
       </c>
       <c r="H14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J14" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K14">
         <v>65</v>
@@ -15111,7 +15126,7 @@
         <v>-19.26086957</v>
       </c>
       <c r="W14" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X14">
         <v>0.019411</v>
@@ -15138,12 +15153,12 @@
         <v>-18.290382</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2">
         <v>44940.40519541666</v>
@@ -15161,13 +15176,13 @@
         <v>1562</v>
       </c>
       <c r="H15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K15">
         <v>62</v>
@@ -15194,7 +15209,7 @@
         <v>-18.5</v>
       </c>
       <c r="W15" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X15">
         <v>0.380435</v>
@@ -15221,12 +15236,12 @@
         <v>-18.224917</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>44940.40553086805</v>
@@ -15244,13 +15259,13 @@
         <v>1626</v>
       </c>
       <c r="H16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J16" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K16">
         <v>61</v>
@@ -15277,7 +15292,7 @@
         <v>-18.71875</v>
       </c>
       <c r="W16" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X16">
         <v>-0.003418</v>
@@ -15309,7 +15324,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>44940.40587858796</v>
@@ -15327,13 +15342,13 @@
         <v>1650</v>
       </c>
       <c r="H17" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I17" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J17" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K17">
         <v>70</v>
@@ -15360,7 +15375,7 @@
         <v>-17.33333333</v>
       </c>
       <c r="W17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X17">
         <v>0.057726</v>
@@ -15392,7 +15407,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>44940.40616829861</v>
@@ -15410,13 +15425,13 @@
         <v>1651</v>
       </c>
       <c r="H18" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I18" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J18" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K18">
         <v>67</v>
@@ -15443,7 +15458,7 @@
         <v>-16</v>
       </c>
       <c r="W18" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X18">
         <v>1.333333</v>
@@ -15475,7 +15490,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>44940.40650520833</v>
@@ -15493,13 +15508,13 @@
         <v>1716</v>
       </c>
       <c r="H19" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J19" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K19">
         <v>83</v>
@@ -15526,7 +15541,7 @@
         <v>-16.44615385</v>
       </c>
       <c r="W19" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X19">
         <v>-0.006864</v>
@@ -15558,7 +15573,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2">
         <v>44940.4068628588</v>
@@ -15576,13 +15591,13 @@
         <v>1740</v>
       </c>
       <c r="H20" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I20" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J20" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K20">
         <v>79</v>
@@ -15609,7 +15624,7 @@
         <v>-15.75</v>
       </c>
       <c r="W20" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X20">
         <v>0.029006</v>
@@ -15641,7 +15656,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>44940.40714446759</v>
@@ -15659,13 +15674,13 @@
         <v>1741</v>
       </c>
       <c r="H21" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I21" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J21" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K21">
         <v>83</v>
@@ -15692,7 +15707,7 @@
         <v>-16</v>
       </c>
       <c r="W21" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X21">
         <v>-0.25</v>
@@ -15724,7 +15739,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2">
         <v>44940.40747799769</v>
@@ -15742,13 +15757,13 @@
         <v>1782</v>
       </c>
       <c r="H22" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I22" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J22" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K22">
         <v>88</v>
@@ -15775,7 +15790,7 @@
         <v>-14.63414634</v>
       </c>
       <c r="W22" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X22">
         <v>0.033314</v>
@@ -15807,7 +15822,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2">
         <v>44940.40782540509</v>
@@ -15825,13 +15840,13 @@
         <v>1829</v>
       </c>
       <c r="H23" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I23" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J23" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K23">
         <v>76</v>
@@ -15858,7 +15873,7 @@
         <v>-15.23404255</v>
       </c>
       <c r="W23" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X23">
         <v>-0.012764</v>
@@ -15890,7 +15905,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>44940.4081149537</v>
@@ -15908,13 +15923,13 @@
         <v>1831</v>
       </c>
       <c r="H24" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I24" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J24" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K24">
         <v>77</v>
@@ -15941,7 +15956,7 @@
         <v>-17.5</v>
       </c>
       <c r="W24" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X24">
         <v>-1.132979</v>
@@ -15973,7 +15988,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>44940.40845047454</v>
@@ -15991,13 +16006,13 @@
         <v>1871</v>
       </c>
       <c r="H25" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I25" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J25" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K25">
         <v>92</v>
@@ -16024,7 +16039,7 @@
         <v>-15.625</v>
       </c>
       <c r="W25" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X25">
         <v>0.046875</v>
@@ -16056,7 +16071,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2">
         <v>44940.4087983912</v>
@@ -16074,13 +16089,13 @@
         <v>1895</v>
       </c>
       <c r="H26" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I26" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J26" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K26">
         <v>82</v>
@@ -16107,7 +16122,7 @@
         <v>-16.375</v>
       </c>
       <c r="W26" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X26">
         <v>-0.03125</v>
@@ -16139,7 +16154,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>44940.40942376157</v>
@@ -16157,13 +16172,13 @@
         <v>1960</v>
       </c>
       <c r="H27" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I27" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K27">
         <v>91</v>
@@ -16190,7 +16205,7 @@
         <v>-14.61538462</v>
       </c>
       <c r="W27" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X27">
         <v>0.027071</v>
@@ -16222,7 +16237,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2">
         <v>44940.40977202546</v>
@@ -16240,13 +16255,13 @@
         <v>1982</v>
       </c>
       <c r="H28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I28" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J28" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K28">
         <v>75</v>
@@ -16273,7 +16288,7 @@
         <v>-14.09090909</v>
       </c>
       <c r="W28" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X28">
         <v>0.02384</v>
@@ -16305,7 +16320,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2">
         <v>44940.41006155092</v>
@@ -16323,13 +16338,13 @@
         <v>1985</v>
       </c>
       <c r="H29" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I29" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J29" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K29">
         <v>78</v>
@@ -16356,7 +16371,7 @@
         <v>-14.33333333</v>
       </c>
       <c r="W29" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X29">
         <v>-0.080808</v>
@@ -16388,7 +16403,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>44940.41039842593</v>
@@ -16406,13 +16421,13 @@
         <v>2049</v>
       </c>
       <c r="H30" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I30" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J30" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K30">
         <v>59</v>
@@ -16439,7 +16454,7 @@
         <v>-13.53125</v>
       </c>
       <c r="W30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X30">
         <v>0.012533</v>
@@ -16471,7 +16486,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2">
         <v>44940.41074732639</v>
@@ -16489,13 +16504,13 @@
         <v>2072</v>
       </c>
       <c r="H31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I31" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J31" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K31">
         <v>73</v>
@@ -16522,7 +16537,7 @@
         <v>-13.91304348</v>
       </c>
       <c r="W31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X31">
         <v>-0.0166</v>
@@ -16554,7 +16569,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>44940.41103886574</v>
@@ -16572,13 +16587,13 @@
         <v>2074</v>
       </c>
       <c r="H32" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I32" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J32" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K32">
         <v>69</v>
@@ -16605,7 +16620,7 @@
         <v>-11</v>
       </c>
       <c r="W32" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X32">
         <v>1.456522</v>
@@ -16637,7 +16652,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>44940.41137101852</v>
@@ -16655,13 +16670,13 @@
         <v>2139</v>
       </c>
       <c r="H33" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J33" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K33">
         <v>60</v>
@@ -16688,7 +16703,7 @@
         <v>-12.98461538</v>
       </c>
       <c r="W33" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X33">
         <v>-0.030533</v>
@@ -16720,7 +16735,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2">
         <v>44940.41171789352</v>
@@ -16738,13 +16753,13 @@
         <v>2162</v>
       </c>
       <c r="H34" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I34" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J34" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K34">
         <v>74</v>
@@ -16771,7 +16786,7 @@
         <v>-13.34782609</v>
       </c>
       <c r="W34" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X34">
         <v>-0.015792</v>
@@ -16803,7 +16818,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2">
         <v>44940.41200840277</v>
@@ -16821,13 +16836,13 @@
         <v>2164</v>
       </c>
       <c r="H35" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I35" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K35">
         <v>69</v>
@@ -16854,7 +16869,7 @@
         <v>-13</v>
       </c>
       <c r="W35" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X35">
         <v>0.173913</v>
@@ -16886,7 +16901,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>44940.41234394676</v>
@@ -16904,13 +16919,13 @@
         <v>2204</v>
       </c>
       <c r="H36" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I36" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J36" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K36">
         <v>56</v>
@@ -16937,7 +16952,7 @@
         <v>-13.125</v>
       </c>
       <c r="W36" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X36">
         <v>-0.003125</v>
@@ -16969,7 +16984,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>44940.41269121528</v>
@@ -16987,13 +17002,13 @@
         <v>2252</v>
       </c>
       <c r="H37" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I37" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J37" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K37">
         <v>65</v>
@@ -17020,7 +17035,7 @@
         <v>-13.9375</v>
       </c>
       <c r="W37" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X37">
         <v>-0.016927</v>
@@ -17052,7 +17067,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2">
         <v>44940.41298534722</v>
@@ -17070,13 +17085,13 @@
         <v>2254</v>
       </c>
       <c r="H38" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I38" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J38" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K38">
         <v>66</v>
@@ -17103,7 +17118,7 @@
         <v>-14</v>
       </c>
       <c r="W38" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X38">
         <v>-0.03125</v>
@@ -17135,7 +17150,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2">
         <v>44940.41332467592</v>
@@ -17153,13 +17168,13 @@
         <v>2294</v>
       </c>
       <c r="H39" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I39" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J39" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K39">
         <v>80</v>
@@ -17186,7 +17201,7 @@
         <v>-13.25</v>
       </c>
       <c r="W39" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X39">
         <v>0.01875</v>
@@ -17218,7 +17233,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>44940.41366487269</v>
@@ -17236,13 +17251,13 @@
         <v>2317</v>
       </c>
       <c r="H40" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I40" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J40" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K40">
         <v>83</v>
@@ -17269,7 +17284,7 @@
         <v>-12.86956522</v>
       </c>
       <c r="W40" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X40">
         <v>0.016541</v>
@@ -17301,7 +17316,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>44940.41395497685</v>
@@ -17319,13 +17334,13 @@
         <v>2319</v>
       </c>
       <c r="H41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I41" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J41" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K41">
         <v>78</v>
@@ -17352,7 +17367,7 @@
         <v>-13</v>
       </c>
       <c r="W41" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X41">
         <v>-0.065217</v>
@@ -17384,7 +17399,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C42" s="2">
         <v>44940.41429173611</v>
@@ -17402,13 +17417,13 @@
         <v>2382</v>
       </c>
       <c r="H42" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I42" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J42" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K42">
         <v>106</v>
@@ -17435,7 +17450,7 @@
         <v>-13.49206349</v>
       </c>
       <c r="W42" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X42">
         <v>-0.007811</v>
@@ -17467,7 +17482,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>44940.41463856481</v>
@@ -17485,13 +17500,13 @@
         <v>2405</v>
       </c>
       <c r="H43" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I43" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J43" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K43">
         <v>110</v>
@@ -17518,7 +17533,7 @@
         <v>-12.69565217</v>
       </c>
       <c r="W43" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X43">
         <v>0.034627</v>
@@ -17550,7 +17565,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>44940.41492850694</v>
@@ -17568,13 +17583,13 @@
         <v>2407</v>
       </c>
       <c r="H44" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I44" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J44" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K44">
         <v>108</v>
@@ -17601,7 +17616,7 @@
         <v>-12</v>
       </c>
       <c r="W44" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X44">
         <v>0.347826</v>
@@ -17633,7 +17648,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>44940.41526369213</v>
@@ -17651,13 +17666,13 @@
         <v>2470</v>
       </c>
       <c r="H45" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I45" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J45" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K45">
         <v>94</v>
@@ -17684,7 +17699,7 @@
         <v>-13.17460317</v>
       </c>
       <c r="W45" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X45">
         <v>-0.018644</v>
@@ -17716,7 +17731,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2">
         <v>44940.41561819444</v>
@@ -17734,13 +17749,13 @@
         <v>2494</v>
       </c>
       <c r="H46" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I46" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J46" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K46">
         <v>110</v>
@@ -17767,7 +17782,7 @@
         <v>-13.25</v>
       </c>
       <c r="W46" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X46">
         <v>-0.003142</v>
@@ -17799,7 +17814,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>44940.41590708333</v>
@@ -17817,13 +17832,13 @@
         <v>2495</v>
       </c>
       <c r="H47" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I47" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J47" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K47">
         <v>106</v>
@@ -17850,7 +17865,7 @@
         <v>-15</v>
       </c>
       <c r="W47" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X47">
         <v>-1.75</v>
@@ -17882,7 +17897,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>44940.41623784722</v>
@@ -17900,13 +17915,13 @@
         <v>2560</v>
       </c>
       <c r="H48" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I48" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J48" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K48">
         <v>108</v>
@@ -17933,7 +17948,7 @@
         <v>-13.78461538</v>
       </c>
       <c r="W48" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X48">
         <v>0.018698</v>
@@ -17965,7 +17980,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>44940.41658493056</v>
@@ -17983,13 +17998,13 @@
         <v>2582</v>
       </c>
       <c r="H49" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I49" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J49" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K49">
         <v>75</v>
@@ -18016,7 +18031,7 @@
         <v>-13.68181818</v>
       </c>
       <c r="W49" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X49">
         <v>0.004673</v>
@@ -18048,7 +18063,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>44940.41687560186</v>
@@ -18066,13 +18081,13 @@
         <v>2584</v>
       </c>
       <c r="H50" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I50" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J50" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K50">
         <v>79</v>
@@ -18099,7 +18114,7 @@
         <v>-14.5</v>
       </c>
       <c r="W50" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X50">
         <v>-0.409091</v>
@@ -18131,7 +18146,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2">
         <v>44940.41721150463</v>
@@ -18149,13 +18164,13 @@
         <v>2624</v>
       </c>
       <c r="H51" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I51" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J51" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K51">
         <v>81</v>
@@ -18182,7 +18197,7 @@
         <v>-13.05</v>
       </c>
       <c r="W51" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X51">
         <v>0.03625</v>
@@ -18214,7 +18229,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>44940.41755880787</v>
@@ -18232,13 +18247,13 @@
         <v>2670</v>
       </c>
       <c r="H52" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I52" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J52" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K52">
         <v>83</v>
@@ -18265,7 +18280,7 @@
         <v>-12.41304348</v>
       </c>
       <c r="W52" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X52">
         <v>0.013847</v>
@@ -18297,7 +18312,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>44940.41785347222</v>
@@ -18315,13 +18330,13 @@
         <v>2672</v>
       </c>
       <c r="H53" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I53" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J53" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K53">
         <v>83</v>
@@ -18348,7 +18363,7 @@
         <v>-12.5</v>
       </c>
       <c r="W53" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X53">
         <v>-0.043478</v>
@@ -18380,7 +18395,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>44940.41818424768</v>
@@ -18398,13 +18413,13 @@
         <v>2711</v>
       </c>
       <c r="H54" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I54" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J54" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K54">
         <v>99</v>
@@ -18431,7 +18446,7 @@
         <v>-12.23076923</v>
       </c>
       <c r="W54" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X54">
         <v>0.006903</v>
@@ -18463,7 +18478,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C55" s="2">
         <v>44940.41853172454</v>
@@ -18481,13 +18496,13 @@
         <v>2734</v>
       </c>
       <c r="H55" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I55" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J55" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K55">
         <v>83</v>
@@ -18514,7 +18529,7 @@
         <v>-12.17391304</v>
       </c>
       <c r="W55" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X55">
         <v>0.002472</v>
@@ -18546,7 +18561,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>44940.41882295139</v>
@@ -18564,13 +18579,13 @@
         <v>2760</v>
       </c>
       <c r="H56" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I56" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J56" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K56">
         <v>81</v>
@@ -18597,7 +18612,7 @@
         <v>-12.88461538</v>
       </c>
       <c r="W56" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X56">
         <v>-0.027335</v>
@@ -18629,7 +18644,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C57" s="2">
         <v>44940.41915699074</v>
@@ -18647,13 +18662,13 @@
         <v>2800</v>
       </c>
       <c r="H57" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I57" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J57" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K57">
         <v>117</v>
@@ -18680,7 +18695,7 @@
         <v>-12.475</v>
       </c>
       <c r="W57" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X57">
         <v>0.01024</v>
@@ -18712,7 +18727,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2">
         <v>44940.41950591435</v>
@@ -18730,13 +18745,13 @@
         <v>2822</v>
       </c>
       <c r="H58" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I58" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J58" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K58">
         <v>108</v>
@@ -18763,7 +18778,7 @@
         <v>-12.18181818</v>
       </c>
       <c r="W58" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X58">
         <v>0.013326</v>
@@ -18795,7 +18810,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>44940.41979554398</v>
@@ -18813,13 +18828,13 @@
         <v>2823</v>
       </c>
       <c r="H59" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I59" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J59" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K59">
         <v>112</v>
@@ -18846,7 +18861,7 @@
         <v>-12</v>
       </c>
       <c r="W59" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X59">
         <v>0.181818</v>
@@ -18878,7 +18893,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2">
         <v>44940.42013127315</v>
@@ -18896,13 +18911,13 @@
         <v>2887</v>
       </c>
       <c r="H60" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I60" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J60" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K60">
         <v>165</v>
@@ -18929,7 +18944,7 @@
         <v>-10.640625</v>
       </c>
       <c r="W60" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X60">
         <v>0.02124</v>
@@ -18961,7 +18976,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2">
         <v>44940.42047820602</v>
@@ -18979,13 +18994,13 @@
         <v>2910</v>
       </c>
       <c r="H61" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I61" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J61" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K61">
         <v>173</v>
@@ -19012,7 +19027,7 @@
         <v>-11.69565217</v>
       </c>
       <c r="W61" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X61">
         <v>-0.045871</v>
@@ -19044,7 +19059,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>44940.42077486111</v>
@@ -19062,13 +19077,13 @@
         <v>2911</v>
       </c>
       <c r="H62" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I62" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J62" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K62">
         <v>166</v>
@@ -19095,7 +19110,7 @@
         <v>-13</v>
       </c>
       <c r="W62" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X62">
         <v>-1.304348</v>
@@ -19127,7 +19142,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>44940.42110949074</v>
@@ -19145,13 +19160,13 @@
         <v>2976</v>
       </c>
       <c r="H63" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I63" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J63" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K63">
         <v>94</v>
@@ -19178,7 +19193,7 @@
         <v>-12.10769231</v>
       </c>
       <c r="W63" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X63">
         <v>0.013728</v>
@@ -19210,7 +19225,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>44940.42145140046</v>
@@ -19228,13 +19243,13 @@
         <v>2999</v>
       </c>
       <c r="H64" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I64" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J64" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K64">
         <v>115</v>
@@ -19261,7 +19276,7 @@
         <v>-13.04347826</v>
       </c>
       <c r="W64" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X64">
         <v>-0.040686</v>
@@ -19293,7 +19308,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2">
         <v>44940.42174225694</v>
@@ -19311,13 +19326,13 @@
         <v>3000</v>
       </c>
       <c r="H65" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I65" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J65" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K65">
         <v>152</v>
@@ -19344,7 +19359,7 @@
         <v>-10</v>
       </c>
       <c r="W65" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X65">
         <v>3.043478</v>
@@ -19376,7 +19391,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2">
         <v>44940.42208086805</v>
@@ -19394,13 +19409,13 @@
         <v>3064</v>
       </c>
       <c r="H66" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I66" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J66" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K66">
         <v>200</v>
@@ -19427,7 +19442,7 @@
         <v>-11.8125</v>
       </c>
       <c r="W66" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X66">
         <v>-0.02832</v>
@@ -19459,7 +19474,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>44940.42242895834</v>
@@ -19477,13 +19492,13 @@
         <v>3086</v>
       </c>
       <c r="H67" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I67" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J67" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K67">
         <v>126</v>
@@ -19510,7 +19525,7 @@
         <v>-12.18181818</v>
       </c>
       <c r="W67" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X67">
         <v>-0.016787</v>
@@ -19542,7 +19557,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2">
         <v>44940.42272012732</v>
@@ -19560,13 +19575,13 @@
         <v>3088</v>
       </c>
       <c r="H68" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I68" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J68" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K68">
         <v>112</v>
@@ -19593,7 +19608,7 @@
         <v>-12.5</v>
       </c>
       <c r="W68" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X68">
         <v>-0.159091</v>
@@ -19625,7 +19640,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2">
         <v>44940.42305065972</v>
@@ -19643,13 +19658,13 @@
         <v>3128</v>
       </c>
       <c r="H69" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I69" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J69" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K69">
         <v>168</v>
@@ -19676,7 +19691,7 @@
         <v>-10.65</v>
       </c>
       <c r="W69" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X69">
         <v>0.04625</v>

--- a/www/flightdata/xlsx/eoss-334.xlsx
+++ b/www/flightdata/xlsx/eoss-334.xlsx
@@ -2088,7 +2088,7 @@
         <v>26277.11</v>
       </c>
       <c r="I2">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>

--- a/www/flightdata/xlsx/eoss-334.xlsx
+++ b/www/flightdata/xlsx/eoss-334.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="533">
   <si>
     <t>flight</t>
   </si>
@@ -57,6 +57,21 @@
     <t>range_distance_traveled_km</t>
   </si>
   <si>
+    <t>parachute.description</t>
+  </si>
+  <si>
+    <t>parachute.size_ft</t>
+  </si>
+  <si>
+    <t>parachute.size_m</t>
+  </si>
+  <si>
+    <t>parachute.weight_lb</t>
+  </si>
+  <si>
+    <t>parachute.weight_kg</t>
+  </si>
+  <si>
     <t>weights.client_lb</t>
   </si>
   <si>
@@ -99,6 +114,15 @@
     <t>weights.necklift_kg</t>
   </si>
   <si>
+    <t>detected_burst.detected</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_ft</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_m</t>
+  </si>
+  <si>
     <t>launch_location.latitude</t>
   </si>
   <si>
@@ -148,6 +172,12 @@
   </si>
   <si>
     <t>1hrs 59mins 52secs</t>
+  </si>
+  <si>
+    <t>Rocketman</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>flightid</t>
@@ -1946,10 +1976,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2061,25 +2091,49 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>86211</v>
@@ -2091,7 +2145,7 @@
         <v>212</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>7192</v>
@@ -2102,76 +2156,100 @@
       <c r="M2">
         <v>121.6</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2">
+        <v>3.05</v>
+      </c>
+      <c r="Q2">
+        <v>2.25</v>
+      </c>
+      <c r="R2">
+        <v>1.02</v>
+      </c>
+      <c r="S2">
         <v>7.46</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>3.38</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>3.23</v>
       </c>
-      <c r="Q2">
+      <c r="V2">
         <v>1.47</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>2.25</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>1.02</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>12.93</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>5.86</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>3.31</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <v>1.5</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>16.24</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>7.37</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>17.81</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>8.08</v>
       </c>
-      <c r="AB2">
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
         <v>39.6081666667</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <v>-104.042</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
         <v>5215</v>
       </c>
-      <c r="AE2">
+      <c r="AM2">
         <v>1589.53</v>
       </c>
-      <c r="AF2">
+      <c r="AN2">
         <v>39.7735</v>
       </c>
-      <c r="AG2">
+      <c r="AO2">
         <v>-102.6361666667</v>
       </c>
-      <c r="AH2">
+      <c r="AP2">
         <v>75.56</v>
       </c>
-      <c r="AI2">
+      <c r="AQ2">
         <v>121.6</v>
       </c>
-      <c r="AJ2">
+      <c r="AR2">
         <v>5519</v>
       </c>
-      <c r="AK2">
+      <c r="AS2">
         <v>1682.19</v>
       </c>
     </row>
@@ -2187,156 +2265,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>44940.33969886574</v>
@@ -2357,16 +2435,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="L2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M2">
         <v>296</v>
@@ -2402,7 +2480,7 @@
         <v>0.01848485</v>
       </c>
       <c r="AE2" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AG2">
         <v>0.060606</v>
@@ -2419,10 +2497,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C3" s="2">
         <v>44940.34004650463</v>
@@ -2443,16 +2521,16 @@
         <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M3">
         <v>344</v>
@@ -2488,7 +2566,7 @@
         <v>0.45708333</v>
       </c>
       <c r="AE3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF3">
         <v>0.059975</v>
@@ -2529,10 +2607,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>44940.34033475695</v>
@@ -2553,16 +2631,16 @@
         <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2598,7 +2676,7 @@
         <v>3.97</v>
       </c>
       <c r="AE4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -2651,10 +2729,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2">
         <v>44940.34067034722</v>
@@ -2675,16 +2753,16 @@
         <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M5">
         <v>130</v>
@@ -2720,7 +2798,7 @@
         <v>6.382</v>
       </c>
       <c r="AE5" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF5">
         <v>0.12213</v>
@@ -2773,10 +2851,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>44940.34101709491</v>
@@ -2797,16 +2875,16 @@
         <v>114</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M6">
         <v>136</v>
@@ -2842,7 +2920,7 @@
         <v>5.91833333</v>
       </c>
       <c r="AE6" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF6">
         <v>-0.06340800000000001</v>
@@ -2895,10 +2973,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2">
         <v>44940.34130826389</v>
@@ -2919,16 +2997,16 @@
         <v>115</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L7" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M7">
         <v>132</v>
@@ -2964,7 +3042,7 @@
         <v>6.7</v>
       </c>
       <c r="AE7" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF7">
         <v>2.583333</v>
@@ -3017,10 +3095,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>44940.34164278935</v>
@@ -3041,16 +3119,16 @@
         <v>156</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M8">
         <v>138</v>
@@ -3086,7 +3164,7 @@
         <v>5.15926829</v>
       </c>
       <c r="AE8" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF8">
         <v>-0.123736</v>
@@ -3139,10 +3217,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>44940.34199069445</v>
@@ -3163,16 +3241,16 @@
         <v>204</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L9" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="M9">
         <v>120</v>
@@ -3208,7 +3286,7 @@
         <v>7.42958333</v>
       </c>
       <c r="AE9" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF9">
         <v>0.15517</v>
@@ -3261,10 +3339,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>44940.34228068287</v>
@@ -3285,16 +3363,16 @@
         <v>205</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L10" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M10">
         <v>118</v>
@@ -3330,7 +3408,7 @@
         <v>6.71</v>
       </c>
       <c r="AE10" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF10">
         <v>-2.375</v>
@@ -3383,10 +3461,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>44940.34261623843</v>
@@ -3407,16 +3485,16 @@
         <v>246</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="M11">
         <v>135</v>
@@ -3452,7 +3530,7 @@
         <v>4.21512195</v>
       </c>
       <c r="AE11" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF11">
         <v>-0.199286</v>
@@ -3505,10 +3583,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>44940.3429653125</v>
@@ -3529,16 +3607,16 @@
         <v>269</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M12">
         <v>96</v>
@@ -3574,7 +3652,7 @@
         <v>5.71173913</v>
       </c>
       <c r="AE12" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF12">
         <v>0.213472</v>
@@ -3627,10 +3705,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2">
         <v>44940.3432546412</v>
@@ -3651,16 +3729,16 @@
         <v>295</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L13" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="M13">
         <v>106</v>
@@ -3696,7 +3774,7 @@
         <v>6.83423077</v>
       </c>
       <c r="AE13" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF13">
         <v>0.14169</v>
@@ -3749,10 +3827,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>44940.34359054398</v>
@@ -3773,16 +3851,16 @@
         <v>335</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M14">
         <v>106</v>
@@ -3818,7 +3896,7 @@
         <v>7.399</v>
       </c>
       <c r="AE14" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF14">
         <v>0.046298</v>
@@ -3871,10 +3949,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2">
         <v>44940.34393738426</v>
@@ -3895,16 +3973,16 @@
         <v>359</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L15" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M15">
         <v>82</v>
@@ -3940,7 +4018,7 @@
         <v>5.51208333</v>
       </c>
       <c r="AE15" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF15">
         <v>-0.257986</v>
@@ -3993,10 +4071,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>44940.34422796296</v>
@@ -4017,16 +4095,16 @@
         <v>361</v>
       </c>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L16" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M16">
         <v>86</v>
@@ -4062,7 +4140,7 @@
         <v>6.55</v>
       </c>
       <c r="AE16" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF16">
         <v>1.708333</v>
@@ -4115,10 +4193,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>44940.34456484954</v>
@@ -4139,16 +4217,16 @@
         <v>425</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L17" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M17">
         <v>83</v>
@@ -4184,7 +4262,7 @@
         <v>6.3103125</v>
       </c>
       <c r="AE17" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF17">
         <v>-0.012451</v>
@@ -4237,10 +4315,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2">
         <v>44940.34491047454</v>
@@ -4261,16 +4339,16 @@
         <v>449</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L18" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M18">
         <v>81</v>
@@ -4306,7 +4384,7 @@
         <v>7.25208333</v>
       </c>
       <c r="AE18" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF18">
         <v>0.128689</v>
@@ -4359,10 +4437,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2">
         <v>44940.3452025</v>
@@ -4383,16 +4461,16 @@
         <v>451</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="M19">
         <v>77</v>
@@ -4428,7 +4506,7 @@
         <v>8.529999999999999</v>
       </c>
       <c r="AE19" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF19">
         <v>2.104167</v>
@@ -4481,10 +4559,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>44940.34553807871</v>
@@ -4505,16 +4583,16 @@
         <v>490</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M20">
         <v>78</v>
@@ -4550,7 +4628,7 @@
         <v>6.90897436</v>
       </c>
       <c r="AE20" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF20">
         <v>-0.136752</v>
@@ -4603,10 +4681,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>44940.34588461806</v>
@@ -4627,16 +4705,16 @@
         <v>539</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L21" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M21">
         <v>85</v>
@@ -4672,7 +4750,7 @@
         <v>7.06632653</v>
       </c>
       <c r="AE21" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF21">
         <v>0.010551</v>
@@ -4725,10 +4803,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>44940.3461744213</v>
@@ -4749,16 +4827,16 @@
         <v>541</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L22" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="M22">
         <v>79</v>
@@ -4794,7 +4872,7 @@
         <v>7.01</v>
       </c>
       <c r="AE22" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF22">
         <v>-0.091837</v>
@@ -4847,10 +4925,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2">
         <v>44940.34651012732</v>
@@ -4871,16 +4949,16 @@
         <v>582</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L23" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M23">
         <v>84</v>
@@ -4916,7 +4994,7 @@
         <v>6.33390244</v>
       </c>
       <c r="AE23" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF23">
         <v>-0.054134</v>
@@ -4969,10 +5047,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2">
         <v>44940.34685759259</v>
@@ -4993,16 +5071,16 @@
         <v>629</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L24" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M24">
         <v>91</v>
@@ -5038,7 +5116,7 @@
         <v>6.11553191</v>
       </c>
       <c r="AE24" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF24">
         <v>-0.015248</v>
@@ -5091,10 +5169,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>44940.34714877315</v>
@@ -5115,16 +5193,16 @@
         <v>631</v>
       </c>
       <c r="I25" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M25">
         <v>92</v>
@@ -5160,7 +5238,7 @@
         <v>5.79</v>
       </c>
       <c r="AE25" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF25">
         <v>-0.531915</v>
@@ -5213,10 +5291,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>44940.34748677084</v>
@@ -5237,16 +5315,16 @@
         <v>671</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L26" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="M26">
         <v>86</v>
@@ -5282,7 +5360,7 @@
         <v>7.0255</v>
       </c>
       <c r="AE26" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF26">
         <v>0.10125</v>
@@ -5335,10 +5413,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2">
         <v>44940.34783131944</v>
@@ -5359,16 +5437,16 @@
         <v>695</v>
       </c>
       <c r="I27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L27" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="M27">
         <v>98</v>
@@ -5404,7 +5482,7 @@
         <v>6.74375</v>
       </c>
       <c r="AE27" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF27">
         <v>-0.038542</v>
@@ -5457,10 +5535,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2">
         <v>44940.34812273148</v>
@@ -5481,16 +5559,16 @@
         <v>697</v>
       </c>
       <c r="I28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L28" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -5526,7 +5604,7 @@
         <v>5.64</v>
       </c>
       <c r="AE28" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF28">
         <v>-1.8125</v>
@@ -5579,10 +5657,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>44940.34845848379</v>
@@ -5603,16 +5681,16 @@
         <v>762</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M29">
         <v>89</v>
@@ -5648,7 +5726,7 @@
         <v>5.62246154</v>
       </c>
       <c r="AE29" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF29">
         <v>-0.000828</v>
@@ -5701,10 +5779,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2">
         <v>44940.34880458334</v>
@@ -5725,16 +5803,16 @@
         <v>786</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L30" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M30">
         <v>81</v>
@@ -5770,7 +5848,7 @@
         <v>6.08333333</v>
       </c>
       <c r="AE30" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF30">
         <v>0.06300699999999999</v>
@@ -5823,10 +5901,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2">
         <v>44940.349095625</v>
@@ -5847,16 +5925,16 @@
         <v>787</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="M31">
         <v>85</v>
@@ -5892,7 +5970,7 @@
         <v>5.79</v>
       </c>
       <c r="AE31" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF31">
         <v>-0.958333</v>
@@ -5945,10 +6023,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2">
         <v>44940.3494306713</v>
@@ -5969,16 +6047,16 @@
         <v>852</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M32">
         <v>75</v>
@@ -6014,7 +6092,7 @@
         <v>6.86492308</v>
       </c>
       <c r="AE32" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF32">
         <v>0.054201</v>
@@ -6067,10 +6145,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>44940.34977787037</v>
@@ -6091,16 +6169,16 @@
         <v>875</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M33">
         <v>79</v>
@@ -6136,7 +6214,7 @@
         <v>4.94304348</v>
       </c>
       <c r="AE33" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF33">
         <v>-0.27416</v>
@@ -6189,10 +6267,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C34" s="2">
         <v>44940.35006822916</v>
@@ -6213,16 +6291,16 @@
         <v>877</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M34">
         <v>77</v>
@@ -6258,7 +6336,7 @@
         <v>2.44</v>
       </c>
       <c r="AE34" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF34">
         <v>-4.108696</v>
@@ -6311,10 +6389,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>44940.35040363426</v>
@@ -6335,16 +6413,16 @@
         <v>917</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L35" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M35">
         <v>67</v>
@@ -6380,7 +6458,7 @@
         <v>4.48825</v>
       </c>
       <c r="AE35" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF35">
         <v>0.168125</v>
@@ -6433,10 +6511,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2">
         <v>44940.35075162037</v>
@@ -6457,16 +6535,16 @@
         <v>966</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L36" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="M36">
         <v>61</v>
@@ -6502,7 +6580,7 @@
         <v>6.40693878</v>
       </c>
       <c r="AE36" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF36">
         <v>0.128478</v>
@@ -6555,10 +6633,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>44940.35104189815</v>
@@ -6579,16 +6657,16 @@
         <v>968</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M37">
         <v>63</v>
@@ -6624,7 +6702,7 @@
         <v>7.925</v>
       </c>
       <c r="AE37" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF37">
         <v>2.489796</v>
@@ -6677,10 +6755,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C38" s="2">
         <v>44940.35137795139</v>
@@ -6701,16 +6779,16 @@
         <v>1009</v>
       </c>
       <c r="I38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M38">
         <v>60</v>
@@ -6746,7 +6824,7 @@
         <v>7.51585366</v>
       </c>
       <c r="AE38" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF38">
         <v>-0.032719</v>
@@ -6799,10 +6877,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2">
         <v>44940.35172524305</v>
@@ -6823,16 +6901,16 @@
         <v>1032</v>
       </c>
       <c r="I39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M39">
         <v>58</v>
@@ -6868,7 +6946,7 @@
         <v>7.30217391</v>
       </c>
       <c r="AE39" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF39">
         <v>-0.030522</v>
@@ -6921,10 +6999,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>44940.35201546297</v>
@@ -6945,16 +7023,16 @@
         <v>1033</v>
       </c>
       <c r="I40" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M40">
         <v>57</v>
@@ -6990,7 +7068,7 @@
         <v>8.84</v>
       </c>
       <c r="AE40" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF40">
         <v>5.043478</v>
@@ -7043,10 +7121,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>44940.35235122685</v>
@@ -7067,16 +7145,16 @@
         <v>1099</v>
       </c>
       <c r="I41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L41" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M41">
         <v>56</v>
@@ -7112,7 +7190,7 @@
         <v>7.69848485</v>
       </c>
       <c r="AE41" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF41">
         <v>-0.056703</v>
@@ -7165,10 +7243,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2">
         <v>44940.35269846065</v>
@@ -7189,16 +7267,16 @@
         <v>1122</v>
       </c>
       <c r="I42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L42" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M42">
         <v>58</v>
@@ -7234,7 +7312,7 @@
         <v>7.1826087</v>
       </c>
       <c r="AE42" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF42">
         <v>-0.07358099999999999</v>
@@ -7287,10 +7365,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>44940.35298905092</v>
@@ -7311,16 +7389,16 @@
         <v>1124</v>
       </c>
       <c r="I43" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L43" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M43">
         <v>59</v>
@@ -7356,7 +7434,7 @@
         <v>9.295</v>
       </c>
       <c r="AE43" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF43">
         <v>3.467391</v>
@@ -7409,10 +7487,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2">
         <v>44940.35332460648</v>
@@ -7433,16 +7511,16 @@
         <v>1165</v>
       </c>
       <c r="I44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L44" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M44">
         <v>59</v>
@@ -7478,7 +7556,7 @@
         <v>7.6497561</v>
       </c>
       <c r="AE44" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF44">
         <v>-0.131767</v>
@@ -7531,10 +7609,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
         <v>44940.35367141203</v>
@@ -7555,16 +7633,16 @@
         <v>1214</v>
       </c>
       <c r="I45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L45" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M45">
         <v>65</v>
@@ -7600,7 +7678,7 @@
         <v>6.92959184</v>
       </c>
       <c r="AE45" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF45">
         <v>-0.048222</v>
@@ -7653,10 +7731,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2">
         <v>44940.35396269676</v>
@@ -7677,16 +7755,16 @@
         <v>1215</v>
       </c>
       <c r="I46" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L46" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="M46">
         <v>66</v>
@@ -7722,7 +7800,7 @@
         <v>7.32</v>
       </c>
       <c r="AE46" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF46">
         <v>1.265306</v>
@@ -7775,10 +7853,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>44940.35429768518</v>
@@ -7799,16 +7877,16 @@
         <v>1256</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L47" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="M47">
         <v>59</v>
@@ -7844,7 +7922,7 @@
         <v>7.31512195</v>
       </c>
       <c r="AE47" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF47">
         <v>0</v>
@@ -7897,10 +7975,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2">
         <v>44940.35464509259</v>
@@ -7921,16 +7999,16 @@
         <v>1279</v>
       </c>
       <c r="I48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L48" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M48">
         <v>60</v>
@@ -7966,7 +8044,7 @@
         <v>8.20304348</v>
       </c>
       <c r="AE48" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF48">
         <v>0.126654</v>
@@ -8019,10 +8097,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2">
         <v>44940.35493649306</v>
@@ -8043,16 +8121,16 @@
         <v>1281</v>
       </c>
       <c r="I49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L49" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M49">
         <v>61</v>
@@ -8088,7 +8166,7 @@
         <v>7.775</v>
       </c>
       <c r="AE49" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF49">
         <v>-0.706522</v>
@@ -8141,10 +8219,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2">
         <v>44940.35527100694</v>
@@ -8165,16 +8243,16 @@
         <v>1347</v>
       </c>
       <c r="I50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L50" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M50">
         <v>49</v>
@@ -8210,7 +8288,7 @@
         <v>8.13712121</v>
       </c>
       <c r="AE50" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF50">
         <v>0.018136</v>
@@ -8263,10 +8341,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>44940.35561853009</v>
@@ -8287,16 +8365,16 @@
         <v>1370</v>
       </c>
       <c r="I51" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="L51" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M51">
         <v>56</v>
@@ -8332,7 +8410,7 @@
         <v>8.3226087</v>
       </c>
       <c r="AE51" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF51">
         <v>0.026408</v>
@@ -8385,10 +8463,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>44940.35590945602</v>
@@ -8409,16 +8487,16 @@
         <v>1372</v>
       </c>
       <c r="I52" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="L52" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M52">
         <v>57</v>
@@ -8454,7 +8532,7 @@
         <v>5.64</v>
       </c>
       <c r="AE52" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF52">
         <v>-4.402174</v>
@@ -8507,10 +8585,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2">
         <v>44940.35624493055</v>
@@ -8531,16 +8609,16 @@
         <v>1438</v>
       </c>
       <c r="I53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L53" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M53">
         <v>53</v>
@@ -8576,7 +8654,7 @@
         <v>7.42590909</v>
       </c>
       <c r="AE53" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF53">
         <v>0.08884300000000001</v>
@@ -8629,10 +8707,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2">
         <v>44940.3565925</v>
@@ -8653,16 +8731,16 @@
         <v>1461</v>
       </c>
       <c r="I54" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L54" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M54">
         <v>56</v>
@@ -8698,7 +8776,7 @@
         <v>8.282608700000001</v>
       </c>
       <c r="AE54" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF54">
         <v>0.122186</v>
@@ -8751,10 +8829,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C55" s="2">
         <v>44940.35688671297</v>
@@ -8775,16 +8853,16 @@
         <v>1463</v>
       </c>
       <c r="I55" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L55" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M55">
         <v>54</v>
@@ -8820,7 +8898,7 @@
         <v>6.405</v>
       </c>
       <c r="AE55" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF55">
         <v>-3.086957</v>
@@ -8873,10 +8951,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2">
         <v>44940.35721751158</v>
@@ -8897,16 +8975,16 @@
         <v>1503</v>
       </c>
       <c r="I56" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L56" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M56">
         <v>58</v>
@@ -8942,7 +9020,7 @@
         <v>8.37425</v>
       </c>
       <c r="AE56" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF56">
         <v>0.161875</v>
@@ -8995,10 +9073,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>44940.3575658912</v>
@@ -9019,16 +9097,16 @@
         <v>1550</v>
       </c>
       <c r="I57" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L57" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M57">
         <v>64</v>
@@ -9064,7 +9142,7 @@
         <v>8.04148936</v>
       </c>
       <c r="AE57" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF57">
         <v>-0.023234</v>
@@ -9117,10 +9195,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>44940.35785689815</v>
@@ -9141,16 +9219,16 @@
         <v>1552</v>
       </c>
       <c r="I58" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M58">
         <v>65</v>
@@ -9186,7 +9264,7 @@
         <v>8.08</v>
       </c>
       <c r="AE58" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF58">
         <v>0.058511</v>
@@ -9239,10 +9317,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2">
         <v>44940.35819158565</v>
@@ -9263,16 +9341,16 @@
         <v>1593</v>
       </c>
       <c r="I59" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M59">
         <v>64</v>
@@ -9308,7 +9386,7 @@
         <v>7.58268293</v>
       </c>
       <c r="AE59" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF59">
         <v>-0.03956</v>
@@ -9361,10 +9439,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2">
         <v>44940.35853839121</v>
@@ -9385,16 +9463,16 @@
         <v>1616</v>
       </c>
       <c r="I60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L60" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="M60">
         <v>61</v>
@@ -9430,7 +9508,7 @@
         <v>7.5273913</v>
       </c>
       <c r="AE60" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF60">
         <v>-0.00793</v>
@@ -9483,10 +9561,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>44940.35883177083</v>
@@ -9507,16 +9585,16 @@
         <v>1618</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L61" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="M61">
         <v>60</v>
@@ -9552,7 +9630,7 @@
         <v>6.705</v>
       </c>
       <c r="AE61" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF61">
         <v>-1.347826</v>
@@ -9605,10 +9683,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C62" s="2">
         <v>44940.35916414352</v>
@@ -9629,16 +9707,16 @@
         <v>1682</v>
       </c>
       <c r="I62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L62" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M62">
         <v>71</v>
@@ -9674,7 +9752,7 @@
         <v>7.11046875</v>
       </c>
       <c r="AE62" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF62">
         <v>0.020752</v>
@@ -9727,10 +9805,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>44940.35951258102</v>
@@ -9751,16 +9829,16 @@
         <v>1706</v>
       </c>
       <c r="I63" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L63" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="M63">
         <v>72</v>
@@ -9796,7 +9874,7 @@
         <v>7.54375</v>
       </c>
       <c r="AE63" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF63">
         <v>0.059245</v>
@@ -9849,10 +9927,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C64" s="2">
         <v>44940.35980234954</v>
@@ -9873,16 +9951,16 @@
         <v>1708</v>
       </c>
       <c r="I64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L64" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="M64">
         <v>75</v>
@@ -9918,7 +9996,7 @@
         <v>6.855</v>
       </c>
       <c r="AE64" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF64">
         <v>-1.125</v>
@@ -9971,10 +10049,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>44940.36013804398</v>
@@ -9995,16 +10073,16 @@
         <v>1774</v>
       </c>
       <c r="I65" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L65" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M65">
         <v>77</v>
@@ -10040,7 +10118,7 @@
         <v>8.225</v>
       </c>
       <c r="AE65" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF65">
         <v>0.067952</v>
@@ -10093,10 +10171,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C66" s="2">
         <v>44940.36048796296</v>
@@ -10117,16 +10195,16 @@
         <v>1798</v>
       </c>
       <c r="I66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L66" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="M66">
         <v>72</v>
@@ -10162,7 +10240,7 @@
         <v>7.04875</v>
       </c>
       <c r="AE66" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF66">
         <v>-0.160827</v>
@@ -10215,10 +10293,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>44940.36076875</v>
@@ -10239,16 +10317,16 @@
         <v>1799</v>
       </c>
       <c r="I67" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="L67" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="M67">
         <v>71</v>
@@ -10284,7 +10362,7 @@
         <v>7.31</v>
       </c>
       <c r="AE67" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF67">
         <v>0.875</v>
@@ -10337,10 +10415,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C68" s="2">
         <v>44940.36110262731</v>
@@ -10361,16 +10439,16 @@
         <v>1839</v>
       </c>
       <c r="I68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L68" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M68">
         <v>58</v>
@@ -10406,7 +10484,7 @@
         <v>8.031499999999999</v>
       </c>
       <c r="AE68" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF68">
         <v>0.05875</v>
@@ -10459,10 +10537,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>44940.36144950231</v>
@@ -10483,16 +10561,16 @@
         <v>1888</v>
       </c>
       <c r="I69" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="L69" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M69">
         <v>85</v>
@@ -10528,7 +10606,7 @@
         <v>7.4644898</v>
       </c>
       <c r="AE69" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF69">
         <v>-0.037963</v>
@@ -10581,10 +10659,10 @@
     </row>
     <row r="70" spans="1:47">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C70" s="2">
         <v>44940.36174215277</v>
@@ -10605,16 +10683,16 @@
         <v>1889</v>
       </c>
       <c r="I70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="L70" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M70">
         <v>85</v>
@@ -10650,7 +10728,7 @@
         <v>8.23</v>
       </c>
       <c r="AE70" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF70">
         <v>2.510204</v>
@@ -10703,10 +10781,10 @@
     </row>
     <row r="71" spans="1:47">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C71" s="2">
         <v>44940.3620759375</v>
@@ -10727,16 +10805,16 @@
         <v>1930</v>
       </c>
       <c r="I71" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L71" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="M71">
         <v>92</v>
@@ -10772,7 +10850,7 @@
         <v>6.67585366</v>
       </c>
       <c r="AE71" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF71">
         <v>-0.124331</v>
@@ -10825,10 +10903,10 @@
     </row>
     <row r="72" spans="1:47">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C72" s="2">
         <v>44940.36242248843</v>
@@ -10849,16 +10927,16 @@
         <v>1954</v>
       </c>
       <c r="I72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L72" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M72">
         <v>87</v>
@@ -10894,7 +10972,7 @@
         <v>5.08</v>
       </c>
       <c r="AE72" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF72">
         <v>-0.218157</v>
@@ -10947,10 +11025,10 @@
     </row>
     <row r="73" spans="1:47">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2">
         <v>44940.36271908565</v>
@@ -10971,16 +11049,16 @@
         <v>1956</v>
       </c>
       <c r="I73" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L73" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M73">
         <v>86</v>
@@ -11016,7 +11094,7 @@
         <v>5.18</v>
       </c>
       <c r="AE73" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF73">
         <v>0.166667</v>
@@ -11069,10 +11147,10 @@
     </row>
     <row r="74" spans="1:47">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C74" s="2">
         <v>44940.36304903936</v>
@@ -11093,16 +11171,16 @@
         <v>2022</v>
       </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L74" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="M74">
         <v>71</v>
@@ -11138,7 +11216,7 @@
         <v>5.12166667</v>
       </c>
       <c r="AE74" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF74">
         <v>-0.002984</v>
@@ -11191,10 +11269,10 @@
     </row>
     <row r="75" spans="1:47">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C75" s="2">
         <v>44940.36339696759</v>
@@ -11215,16 +11293,16 @@
         <v>2046</v>
       </c>
       <c r="I75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L75" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M75">
         <v>81</v>
@@ -11260,7 +11338,7 @@
         <v>5.46083333</v>
       </c>
       <c r="AE75" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF75">
         <v>0.046402</v>
@@ -11313,10 +11391,10 @@
     </row>
     <row r="76" spans="1:47">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C76" s="2">
         <v>44940.36368710648</v>
@@ -11337,16 +11415,16 @@
         <v>2048</v>
       </c>
       <c r="I76" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L76" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M76">
         <v>84</v>
@@ -11382,7 +11460,7 @@
         <v>4.88</v>
       </c>
       <c r="AE76" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF76">
         <v>-0.958333</v>
@@ -11435,10 +11513,10 @@
     </row>
     <row r="77" spans="1:47">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C77" s="2">
         <v>44940.36402215277</v>
@@ -11459,16 +11537,16 @@
         <v>2089</v>
       </c>
       <c r="I77" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L77" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M77">
         <v>109</v>
@@ -11504,7 +11582,7 @@
         <v>7.04756098</v>
       </c>
       <c r="AE77" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF77">
         <v>0.173706</v>
@@ -11557,10 +11635,10 @@
     </row>
     <row r="78" spans="1:47">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C78" s="2">
         <v>44940.36436971065</v>
@@ -11581,16 +11659,16 @@
         <v>2137</v>
       </c>
       <c r="I78" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L78" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="M78">
         <v>81</v>
@@ -11626,7 +11704,7 @@
         <v>6.33729167</v>
       </c>
       <c r="AE78" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF78">
         <v>-0.048548</v>
@@ -11679,10 +11757,10 @@
     </row>
     <row r="79" spans="1:47">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2">
         <v>44940.36466076389</v>
@@ -11703,16 +11781,16 @@
         <v>2139</v>
       </c>
       <c r="I79" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L79" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="M79">
         <v>81</v>
@@ -11748,7 +11826,7 @@
         <v>6.095</v>
       </c>
       <c r="AE79" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF79">
         <v>-0.395833</v>
@@ -11801,10 +11879,10 @@
     </row>
     <row r="80" spans="1:47">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C80" s="2">
         <v>44940.36499581019</v>
@@ -11825,16 +11903,16 @@
         <v>2180</v>
       </c>
       <c r="I80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L80" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="M80">
         <v>90</v>
@@ -11870,7 +11948,7 @@
         <v>5.47902439</v>
       </c>
       <c r="AE80" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF80">
         <v>-0.049375</v>
@@ -11923,10 +12001,10 @@
     </row>
     <row r="81" spans="1:48">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C81" s="2">
         <v>44940.36534358796</v>
@@ -11947,16 +12025,16 @@
         <v>2204</v>
       </c>
       <c r="I81" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L81" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="M81">
         <v>105</v>
@@ -11992,7 +12070,7 @@
         <v>6.24833333</v>
       </c>
       <c r="AE81" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF81">
         <v>0.105183</v>
@@ -12045,10 +12123,10 @@
     </row>
     <row r="82" spans="1:48">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2">
         <v>44940.36563915509</v>
@@ -12069,16 +12147,16 @@
         <v>2206</v>
       </c>
       <c r="I82" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L82" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M82">
         <v>99</v>
@@ -12114,7 +12192,7 @@
         <v>6.4</v>
       </c>
       <c r="AE82" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AF82">
         <v>0.25</v>
@@ -12167,10 +12245,10 @@
     </row>
     <row r="83" spans="1:48">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2">
         <v>44940.36597112269</v>
@@ -12191,16 +12269,16 @@
         <v>2271</v>
       </c>
       <c r="I83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L83" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="M83">
         <v>119</v>
@@ -12236,7 +12314,7 @@
         <v>7.39015385</v>
       </c>
       <c r="AE83" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF83">
         <v>0.049941</v>
@@ -12287,15 +12365,15 @@
         <v>5.709989</v>
       </c>
       <c r="AV83" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:48">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2">
         <v>44940.3663169213</v>
@@ -12316,16 +12394,16 @@
         <v>2295</v>
       </c>
       <c r="I84" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L84" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="M84">
         <v>79</v>
@@ -12361,7 +12439,7 @@
         <v>6.00708333</v>
       </c>
       <c r="AE84" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF84">
         <v>-0.189076</v>
@@ -12414,10 +12492,10 @@
     </row>
     <row r="85" spans="1:48">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C85" s="2">
         <v>44940.36660665509</v>
@@ -12438,16 +12516,16 @@
         <v>2297</v>
       </c>
       <c r="I85" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L85" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M85">
         <v>73</v>
@@ -12483,7 +12561,7 @@
         <v>5.03</v>
       </c>
       <c r="AE85" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF85">
         <v>-1.604167</v>
@@ -12536,10 +12614,10 @@
     </row>
     <row r="86" spans="1:48">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C86" s="2">
         <v>44940.36694467592</v>
@@ -12560,16 +12638,16 @@
         <v>2363</v>
       </c>
       <c r="I86" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L86" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M86">
         <v>59</v>
@@ -12605,7 +12683,7 @@
         <v>5.90212121</v>
       </c>
       <c r="AE86" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF86">
         <v>0.043388</v>
@@ -12658,10 +12736,10 @@
     </row>
     <row r="87" spans="1:48">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C87" s="2">
         <v>44940.36729467593</v>
@@ -12682,16 +12760,16 @@
         <v>2386</v>
       </c>
       <c r="I87" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L87" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="M87">
         <v>75</v>
@@ -12727,7 +12805,7 @@
         <v>4.83695652</v>
       </c>
       <c r="AE87" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF87">
         <v>-0.151916</v>
@@ -12780,10 +12858,10 @@
     </row>
     <row r="88" spans="1:48">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C88" s="2">
         <v>44940.36757986111</v>
@@ -12804,16 +12882,16 @@
         <v>2388</v>
       </c>
       <c r="I88" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L88" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M88">
         <v>71</v>
@@ -12849,7 +12927,7 @@
         <v>5.03</v>
       </c>
       <c r="AE88" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF88">
         <v>0.315217</v>
@@ -12902,10 +12980,10 @@
     </row>
     <row r="89" spans="1:48">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C89" s="2">
         <v>44940.36791641204</v>
@@ -12926,16 +13004,16 @@
         <v>2429</v>
       </c>
       <c r="I89" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L89" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M89">
         <v>80</v>
@@ -12971,7 +13049,7 @@
         <v>4.74292683</v>
       </c>
       <c r="AE89" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF89">
         <v>-0.022903</v>
@@ -13024,10 +13102,10 @@
     </row>
     <row r="90" spans="1:48">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C90" s="2">
         <v>44940.36826293982</v>
@@ -13048,16 +13126,16 @@
         <v>2477</v>
       </c>
       <c r="I90" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L90" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M90">
         <v>77</v>
@@ -13093,7 +13171,7 @@
         <v>4.97208333</v>
       </c>
       <c r="AE90" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF90">
         <v>0.015657</v>
@@ -13146,10 +13224,10 @@
     </row>
     <row r="91" spans="1:48">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2">
         <v>44940.36855534722</v>
@@ -13170,16 +13248,16 @@
         <v>2479</v>
       </c>
       <c r="I91" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L91" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="M91">
         <v>78</v>
@@ -13215,7 +13293,7 @@
         <v>5.03</v>
       </c>
       <c r="AE91" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF91">
         <v>0.09375</v>
@@ -13268,10 +13346,10 @@
     </row>
     <row r="92" spans="1:48">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C92" s="2">
         <v>44940.36888913195</v>
@@ -13292,16 +13370,16 @@
         <v>2520</v>
       </c>
       <c r="I92" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L92" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="M92">
         <v>90</v>
@@ -13337,7 +13415,7 @@
         <v>5.05512195</v>
       </c>
       <c r="AE92" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF92">
         <v>0.002082</v>
@@ -13390,10 +13468,10 @@
     </row>
     <row r="93" spans="1:48">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C93" s="2">
         <v>44940.36923621528</v>
@@ -13414,16 +13492,16 @@
         <v>2544</v>
       </c>
       <c r="I93" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="L93" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="M93">
         <v>102</v>
@@ -13459,7 +13537,7 @@
         <v>5.42291667</v>
       </c>
       <c r="AE93" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF93">
         <v>0.050263</v>
@@ -13512,10 +13590,10 @@
     </row>
     <row r="94" spans="1:48">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C94" s="2">
         <v>44940.36952689815</v>
@@ -13536,16 +13614,16 @@
         <v>2545</v>
       </c>
       <c r="I94" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L94" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M94">
         <v>106</v>
@@ -13581,7 +13659,7 @@
         <v>4.27</v>
       </c>
       <c r="AE94" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF94">
         <v>-3.791667</v>
@@ -13634,10 +13712,10 @@
     </row>
     <row r="95" spans="1:48">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C95" s="2">
         <v>44940.36986238426</v>
@@ -13658,16 +13736,16 @@
         <v>2610</v>
       </c>
       <c r="I95" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L95" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M95">
         <v>121</v>
@@ -13703,7 +13781,7 @@
         <v>6.38661538</v>
       </c>
       <c r="AE95" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF95">
         <v>0.106982</v>
@@ -13756,10 +13834,10 @@
     </row>
     <row r="96" spans="1:48">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C96" s="2">
         <v>44940.37021008102</v>
@@ -13780,16 +13858,16 @@
         <v>2634</v>
       </c>
       <c r="I96" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L96" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M96">
         <v>139</v>
@@ -13825,7 +13903,7 @@
         <v>6.26125</v>
       </c>
       <c r="AE96" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF96">
         <v>-0.017174</v>
@@ -13878,10 +13956,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2">
         <v>44940.37050086806</v>
@@ -13902,16 +13980,16 @@
         <v>2635</v>
       </c>
       <c r="I97" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L97" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="M97">
         <v>140</v>
@@ -13947,7 +14025,7 @@
         <v>4.57</v>
       </c>
       <c r="AE97" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF97">
         <v>-5.541667</v>
@@ -14000,10 +14078,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C98" s="2">
         <v>44940.37083533565</v>
@@ -14024,16 +14102,16 @@
         <v>2701</v>
       </c>
       <c r="I98" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L98" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M98">
         <v>124</v>
@@ -14069,7 +14147,7 @@
         <v>6.46090909</v>
       </c>
       <c r="AE98" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF98">
         <v>0.093893</v>
@@ -14122,10 +14200,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2">
         <v>44940.3711837963</v>
@@ -14146,16 +14224,16 @@
         <v>2724</v>
       </c>
       <c r="I99" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L99" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="M99">
         <v>127</v>
@@ -14191,7 +14269,7 @@
         <v>6.22826087</v>
       </c>
       <c r="AE99" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF99">
         <v>-0.033139</v>
@@ -14244,10 +14322,10 @@
     </row>
     <row r="100" spans="1:47">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C100" s="2">
         <v>44940.371474375</v>
@@ -14268,16 +14346,16 @@
         <v>2726</v>
       </c>
       <c r="I100" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L100" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M100">
         <v>129</v>
@@ -14313,7 +14391,7 @@
         <v>5.03</v>
       </c>
       <c r="AE100" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF100">
         <v>-1.967391</v>
@@ -14366,10 +14444,10 @@
     </row>
     <row r="101" spans="1:47">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C101" s="2">
         <v>44940.37180888889</v>
@@ -14390,16 +14468,16 @@
         <v>2768</v>
       </c>
       <c r="I101" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L101" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M101">
         <v>122</v>
@@ -14435,7 +14513,7 @@
         <v>5.02190476</v>
       </c>
       <c r="AE101" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF101">
         <v>-0.000567</v>
@@ -14488,10 +14566,10 @@
     </row>
     <row r="102" spans="1:47">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C102" s="2">
         <v>44940.37215681713</v>
@@ -14512,16 +14590,16 @@
         <v>2791</v>
       </c>
       <c r="I102" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L102" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="M102">
         <v>117</v>
@@ -14557,7 +14635,7 @@
         <v>5.18173913</v>
       </c>
       <c r="AE102" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF102">
         <v>0.022774</v>
@@ -14610,10 +14688,10 @@
     </row>
     <row r="103" spans="1:47">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C103" s="2">
         <v>44940.37244690972</v>
@@ -14634,16 +14712,16 @@
         <v>2817</v>
       </c>
       <c r="I103" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="L103" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="M103">
         <v>120</v>
@@ -14679,7 +14757,7 @@
         <v>5.53346154</v>
       </c>
       <c r="AE103" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF103">
         <v>0.044379</v>
@@ -14732,10 +14810,10 @@
     </row>
     <row r="104" spans="1:47">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C104" s="2">
         <v>44940.37278292824</v>
@@ -14756,16 +14834,16 @@
         <v>2858</v>
       </c>
       <c r="I104" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J104" t="b">
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L104" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="M104">
         <v>156</v>
@@ -14801,7 +14879,7 @@
         <v>5.27804878</v>
       </c>
       <c r="AE104" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF104">
         <v>-0.020409</v>
@@ -14854,10 +14932,10 @@
     </row>
     <row r="105" spans="1:47">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C105" s="2">
         <v>44940.37312947917</v>
@@ -14878,16 +14956,16 @@
         <v>2882</v>
       </c>
       <c r="I105" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L105" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="M105">
         <v>120</v>
@@ -14923,7 +15001,7 @@
         <v>5.0675</v>
       </c>
       <c r="AE105" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF105">
         <v>-0.028836</v>
@@ -14976,10 +15054,10 @@
     </row>
     <row r="106" spans="1:47">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C106" s="2">
         <v>44940.37342081019</v>
@@ -15000,16 +15078,16 @@
         <v>2884</v>
       </c>
       <c r="I106" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J106" t="b">
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L106" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M106">
         <v>113</v>
@@ -15045,7 +15123,7 @@
         <v>5.79</v>
       </c>
       <c r="AE106" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF106">
         <v>1.1875</v>
@@ -15098,10 +15176,10 @@
     </row>
     <row r="107" spans="1:47">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C107" s="2">
         <v>44940.37375604167</v>
@@ -15122,16 +15200,16 @@
         <v>2949</v>
       </c>
       <c r="I107" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="L107" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="M107">
         <v>169</v>
@@ -15167,7 +15245,7 @@
         <v>4.72676923</v>
       </c>
       <c r="AE107" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF107">
         <v>-0.053728</v>
@@ -15220,10 +15298,10 @@
     </row>
     <row r="108" spans="1:47">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C108" s="2">
         <v>44940.37410366898</v>
@@ -15244,16 +15322,16 @@
         <v>2973</v>
       </c>
       <c r="I108" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J108" t="b">
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="L108" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M108">
         <v>128</v>
@@ -15289,7 +15367,7 @@
         <v>5.21958333</v>
       </c>
       <c r="AE108" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF108">
         <v>0.067388</v>
@@ -15342,10 +15420,10 @@
     </row>
     <row r="109" spans="1:47">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C109" s="2">
         <v>44940.37439447916</v>
@@ -15366,16 +15444,16 @@
         <v>2974</v>
       </c>
       <c r="I109" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J109" t="b">
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L109" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="M109">
         <v>125</v>
@@ -15411,7 +15489,7 @@
         <v>4.58</v>
       </c>
       <c r="AE109" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF109">
         <v>-2.125</v>
@@ -15464,10 +15542,10 @@
     </row>
     <row r="110" spans="1:47">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C110" s="2">
         <v>44940.37472954861</v>
@@ -15488,16 +15566,16 @@
         <v>3015</v>
       </c>
       <c r="I110" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J110" t="b">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="L110" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="M110">
         <v>87</v>
@@ -15533,7 +15611,7 @@
         <v>4.95097561</v>
       </c>
       <c r="AE110" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF110">
         <v>0.030339</v>
@@ -15586,10 +15664,10 @@
     </row>
     <row r="111" spans="1:47">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C111" s="2">
         <v>44940.3750762037</v>
@@ -15610,16 +15688,16 @@
         <v>3063</v>
       </c>
       <c r="I111" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J111" t="b">
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="L111" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="M111">
         <v>155</v>
@@ -15655,7 +15733,7 @@
         <v>5.06729167</v>
       </c>
       <c r="AE111" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF111">
         <v>0.007939999999999999</v>
@@ -15708,10 +15786,10 @@
     </row>
     <row r="112" spans="1:47">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C112" s="2">
         <v>44940.37536677083</v>
@@ -15732,16 +15810,16 @@
         <v>3064</v>
       </c>
       <c r="I112" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J112" t="b">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L112" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="M112">
         <v>154</v>
@@ -15777,7 +15855,7 @@
         <v>5.18</v>
       </c>
       <c r="AE112" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF112">
         <v>0.375</v>
@@ -15830,10 +15908,10 @@
     </row>
     <row r="113" spans="1:47">
       <c r="A113" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C113" s="2">
         <v>44940.37570267361</v>
@@ -15854,16 +15932,16 @@
         <v>3105</v>
       </c>
       <c r="I113" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
       </c>
       <c r="K113" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L113" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M113">
         <v>185</v>
@@ -15899,7 +15977,7 @@
         <v>4.91414634</v>
       </c>
       <c r="AE113" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF113">
         <v>-0.021416</v>
@@ -15952,10 +16030,10 @@
     </row>
     <row r="114" spans="1:47">
       <c r="A114" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C114" s="2">
         <v>44940.37605122685</v>
@@ -15976,16 +16054,16 @@
         <v>3129</v>
       </c>
       <c r="I114" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J114" t="b">
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="L114" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="M114">
         <v>244</v>
@@ -16021,7 +16099,7 @@
         <v>4.305</v>
       </c>
       <c r="AE114" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF114">
         <v>-0.083206</v>
@@ -16074,10 +16152,10 @@
     </row>
     <row r="115" spans="1:47">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C115" s="2">
         <v>44940.37634334491</v>
@@ -16098,16 +16176,16 @@
         <v>3131</v>
       </c>
       <c r="I115" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J115" t="b">
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="L115" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="M115">
         <v>236</v>
@@ -16143,7 +16221,7 @@
         <v>1.985</v>
       </c>
       <c r="AE115" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF115">
         <v>-3.8125</v>
@@ -16196,10 +16274,10 @@
     </row>
     <row r="116" spans="1:47">
       <c r="A116" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C116" s="2">
         <v>44940.37667689815</v>
@@ -16220,16 +16298,16 @@
         <v>3195</v>
       </c>
       <c r="I116" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="L116" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="M116">
         <v>216</v>
@@ -16265,7 +16343,7 @@
         <v>5.13875</v>
       </c>
       <c r="AE116" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF116">
         <v>0.161865</v>
@@ -16318,10 +16396,10 @@
     </row>
     <row r="117" spans="1:47">
       <c r="A117" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B117" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C117" s="2">
         <v>44940.37702810185</v>
@@ -16342,16 +16420,16 @@
         <v>3219</v>
       </c>
       <c r="I117" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J117" t="b">
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L117" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="M117">
         <v>110</v>
@@ -16387,7 +16465,7 @@
         <v>5.35916667</v>
       </c>
       <c r="AE117" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF117">
         <v>0.030165</v>
@@ -16440,10 +16518,10 @@
     </row>
     <row r="118" spans="1:47">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B118" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C118" s="2">
         <v>44940.37731377315</v>
@@ -16464,16 +16542,16 @@
         <v>3220</v>
       </c>
       <c r="I118" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J118" t="b">
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L118" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="M118">
         <v>107</v>
@@ -16509,7 +16587,7 @@
         <v>5.18</v>
       </c>
       <c r="AE118" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF118">
         <v>-0.583333</v>
@@ -16562,10 +16640,10 @@
     </row>
     <row r="119" spans="1:47">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C119" s="2">
         <v>44940.37764974537</v>
@@ -16586,16 +16664,16 @@
         <v>3284</v>
       </c>
       <c r="I119" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J119" t="b">
         <v>1</v>
       </c>
       <c r="K119" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="L119" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M119">
         <v>184</v>
@@ -16631,7 +16709,7 @@
         <v>5.68171875</v>
       </c>
       <c r="AE119" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF119">
         <v>0.025635</v>
@@ -16684,10 +16762,10 @@
     </row>
     <row r="120" spans="1:47">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C120" s="2">
         <v>44940.37799662037</v>
@@ -16708,16 +16786,16 @@
         <v>3308</v>
       </c>
       <c r="I120" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J120" t="b">
         <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L120" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="M120">
         <v>173</v>
@@ -16753,7 +16831,7 @@
         <v>5.19416667</v>
       </c>
       <c r="AE120" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF120">
         <v>-0.066623</v>
@@ -16806,10 +16884,10 @@
     </row>
     <row r="121" spans="1:47">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B121" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C121" s="2">
         <v>44940.37828671296</v>
@@ -16830,16 +16908,16 @@
         <v>3310</v>
       </c>
       <c r="I121" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J121" t="b">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="L121" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="M121">
         <v>177</v>
@@ -16875,7 +16953,7 @@
         <v>4.575</v>
       </c>
       <c r="AE121" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF121">
         <v>-1.020833</v>
@@ -16928,10 +17006,10 @@
     </row>
     <row r="122" spans="1:47">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B122" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C122" s="2">
         <v>44940.37862175926</v>
@@ -16952,16 +17030,16 @@
         <v>3374</v>
       </c>
       <c r="I122" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J122" t="b">
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="L122" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="M122">
         <v>198</v>
@@ -16997,7 +17075,7 @@
         <v>5.08625</v>
       </c>
       <c r="AE122" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF122">
         <v>0.026367</v>
@@ -17050,10 +17128,10 @@
     </row>
     <row r="123" spans="1:47">
       <c r="A123" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C123" s="2">
         <v>44940.37897061343</v>
@@ -17074,16 +17152,16 @@
         <v>3396</v>
       </c>
       <c r="I123" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
       </c>
       <c r="K123" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="L123" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M123">
         <v>172</v>
@@ -17119,7 +17197,7 @@
         <v>5.08454545</v>
       </c>
       <c r="AE123" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF123">
         <v>-0.000258</v>
@@ -17172,10 +17250,10 @@
     </row>
     <row r="124" spans="1:47">
       <c r="A124" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B124" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C124" s="2">
         <v>44940.37926053241</v>
@@ -17196,16 +17274,16 @@
         <v>3398</v>
       </c>
       <c r="I124" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J124" t="b">
         <v>1</v>
       </c>
       <c r="K124" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="L124" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="M124">
         <v>166</v>
@@ -17241,7 +17319,7 @@
         <v>5.185</v>
       </c>
       <c r="AE124" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF124">
         <v>0.159091</v>
@@ -17294,10 +17372,10 @@
     </row>
     <row r="125" spans="1:47">
       <c r="A125" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B125" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C125" s="2">
         <v>44940.37959600695</v>
@@ -17318,16 +17396,16 @@
         <v>3438</v>
       </c>
       <c r="I125" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="L125" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="M125">
         <v>182</v>
@@ -17363,7 +17441,7 @@
         <v>5.25025</v>
       </c>
       <c r="AE125" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF125">
         <v>0.005625</v>
@@ -17416,10 +17494,10 @@
     </row>
     <row r="126" spans="1:47">
       <c r="A126" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C126" s="2">
         <v>44940.37994346065</v>
@@ -17440,16 +17518,16 @@
         <v>3485</v>
       </c>
       <c r="I126" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J126" t="b">
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="L126" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="M126">
         <v>177</v>
@@ -17485,7 +17563,7 @@
         <v>4.88319149</v>
       </c>
       <c r="AE126" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF126">
         <v>-0.025611</v>
@@ -17538,10 +17616,10 @@
     </row>
     <row r="127" spans="1:47">
       <c r="A127" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B127" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C127" s="2">
         <v>44940.38023311343</v>
@@ -17562,16 +17640,16 @@
         <v>3487</v>
       </c>
       <c r="I127" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J127" t="b">
         <v>1</v>
       </c>
       <c r="K127" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L127" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="M127">
         <v>171</v>
@@ -17607,7 +17685,7 @@
         <v>4.725</v>
       </c>
       <c r="AE127" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF127">
         <v>-0.260638</v>
@@ -17660,10 +17738,10 @@
     </row>
     <row r="128" spans="1:47">
       <c r="A128" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B128" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C128" s="2">
         <v>44940.38056954861</v>
@@ -17684,16 +17762,16 @@
         <v>3528</v>
       </c>
       <c r="I128" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
       </c>
       <c r="K128" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="L128" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="M128">
         <v>179</v>
@@ -17729,7 +17807,7 @@
         <v>5.29317073</v>
       </c>
       <c r="AE128" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF128">
         <v>0.045509</v>
@@ -17782,10 +17860,10 @@
     </row>
     <row r="129" spans="1:47">
       <c r="A129" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C129" s="2">
         <v>44940.38091631945</v>
@@ -17806,16 +17884,16 @@
         <v>3551</v>
       </c>
       <c r="I129" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J129" t="b">
         <v>1</v>
       </c>
       <c r="K129" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="L129" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="M129">
         <v>176</v>
@@ -17851,7 +17929,7 @@
         <v>5.23434783</v>
       </c>
       <c r="AE129" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF129">
         <v>-0.008345</v>
@@ -17904,10 +17982,10 @@
     </row>
     <row r="130" spans="1:47">
       <c r="A130" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B130" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C130" s="2">
         <v>44940.38120711806</v>
@@ -17928,16 +18006,16 @@
         <v>3553</v>
       </c>
       <c r="I130" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J130" t="b">
         <v>1</v>
       </c>
       <c r="K130" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L130" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="M130">
         <v>173</v>
@@ -17973,7 +18051,7 @@
         <v>4.88</v>
       </c>
       <c r="AE130" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF130">
         <v>-0.586957</v>
@@ -18026,10 +18104,10 @@
     </row>
     <row r="131" spans="1:47">
       <c r="A131" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B131" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C131" s="2">
         <v>44940.38155128472</v>
@@ -18050,16 +18128,16 @@
         <v>3618</v>
       </c>
       <c r="I131" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J131" t="b">
         <v>1</v>
       </c>
       <c r="K131" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="L131" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M131">
         <v>173</v>
@@ -18095,7 +18173,7 @@
         <v>5.38323077</v>
       </c>
       <c r="AE131" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF131">
         <v>0.025562</v>
@@ -18148,10 +18226,10 @@
     </row>
     <row r="132" spans="1:47">
       <c r="A132" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B132" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C132" s="2">
         <v>44940.38189346065</v>
@@ -18172,16 +18250,16 @@
         <v>3641</v>
       </c>
       <c r="I132" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J132" t="b">
         <v>1</v>
       </c>
       <c r="K132" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="L132" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M132">
         <v>168</v>
@@ -18217,7 +18295,7 @@
         <v>5.15478261</v>
       </c>
       <c r="AE132" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF132">
         <v>-0.032543</v>
@@ -18270,10 +18348,10 @@
     </row>
     <row r="133" spans="1:47">
       <c r="A133" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B133" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C133" s="2">
         <v>44940.38251856482</v>
@@ -18294,16 +18372,16 @@
         <v>3707</v>
       </c>
       <c r="I133" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J133" t="b">
         <v>1</v>
       </c>
       <c r="K133" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="L133" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="M133">
         <v>174</v>
@@ -18339,7 +18417,7 @@
         <v>5.15848485</v>
       </c>
       <c r="AE133" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF133">
         <v>0.00017</v>
@@ -18392,10 +18470,10 @@
     </row>
     <row r="134" spans="1:47">
       <c r="A134" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B134" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C134" s="2">
         <v>44940.382865625</v>
@@ -18416,16 +18494,16 @@
         <v>3730</v>
       </c>
       <c r="I134" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J134" t="b">
         <v>1</v>
       </c>
       <c r="K134" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="L134" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="M134">
         <v>146</v>
@@ -18461,7 +18539,7 @@
         <v>5.42043478</v>
       </c>
       <c r="AE134" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF134">
         <v>0.03732</v>
@@ -18514,10 +18592,10 @@
     </row>
     <row r="135" spans="1:47">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B135" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C135" s="2">
         <v>44940.3831566088</v>
@@ -18538,16 +18616,16 @@
         <v>3732</v>
       </c>
       <c r="I135" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J135" t="b">
         <v>1</v>
       </c>
       <c r="K135" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="L135" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="M135">
         <v>152</v>
@@ -18583,7 +18661,7 @@
         <v>4.57</v>
       </c>
       <c r="AE135" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF135">
         <v>-1.391304</v>
@@ -18636,10 +18714,10 @@
     </row>
     <row r="136" spans="1:47">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B136" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C136" s="2">
         <v>44940.38349574074</v>
@@ -18660,16 +18738,16 @@
         <v>3773</v>
       </c>
       <c r="I136" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
       </c>
       <c r="K136" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="L136" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="M136">
         <v>182</v>
@@ -18705,7 +18783,7 @@
         <v>5.50878049</v>
       </c>
       <c r="AE136" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF136">
         <v>0.07495499999999999</v>
@@ -18758,10 +18836,10 @@
     </row>
     <row r="137" spans="1:47">
       <c r="A137" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B137" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C137" s="2">
         <v>44940.38384002315</v>
@@ -18782,16 +18860,16 @@
         <v>3820</v>
       </c>
       <c r="I137" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J137" t="b">
         <v>1</v>
       </c>
       <c r="K137" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="L137" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="M137">
         <v>183</v>
@@ -18827,7 +18905,7 @@
         <v>5.42148936</v>
       </c>
       <c r="AE137" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF137">
         <v>-0.006084</v>
@@ -18880,10 +18958,10 @@
     </row>
     <row r="138" spans="1:47">
       <c r="A138" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B138" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C138" s="2">
         <v>44940.38413138889</v>
@@ -18904,16 +18982,16 @@
         <v>3822</v>
       </c>
       <c r="I138" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J138" t="b">
         <v>1</v>
       </c>
       <c r="K138" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L138" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="M138">
         <v>180</v>
@@ -18949,7 +19027,7 @@
         <v>5.79</v>
       </c>
       <c r="AE138" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF138">
         <v>0.606383</v>
@@ -19002,10 +19080,10 @@
     </row>
     <row r="139" spans="1:47">
       <c r="A139" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B139" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C139" s="2">
         <v>44940.38446775463</v>
@@ -19026,16 +19104,16 @@
         <v>3863</v>
       </c>
       <c r="I139" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J139" t="b">
         <v>1</v>
       </c>
       <c r="K139" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L139" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="M139">
         <v>182</v>
@@ -19071,7 +19149,7 @@
         <v>5.3304878</v>
       </c>
       <c r="AE139" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF139">
         <v>-0.036883</v>
@@ -19124,10 +19202,10 @@
     </row>
     <row r="140" spans="1:47">
       <c r="A140" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B140" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C140" s="2">
         <v>44940.38481304398</v>
@@ -19148,16 +19226,16 @@
         <v>3886</v>
       </c>
       <c r="I140" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J140" t="b">
         <v>1</v>
       </c>
       <c r="K140" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L140" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="M140">
         <v>179</v>
@@ -19193,7 +19271,7 @@
         <v>5.04869565</v>
       </c>
       <c r="AE140" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF140">
         <v>-0.040112</v>
@@ -19246,10 +19324,10 @@
     </row>
     <row r="141" spans="1:47">
       <c r="A141" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B141" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C141" s="2">
         <v>44940.38510621528</v>
@@ -19270,16 +19348,16 @@
         <v>3888</v>
       </c>
       <c r="I141" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J141" t="b">
         <v>1</v>
       </c>
       <c r="K141" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L141" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="M141">
         <v>182</v>
@@ -19315,7 +19393,7 @@
         <v>4.575</v>
       </c>
       <c r="AE141" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF141">
         <v>-0.782609</v>
@@ -19368,10 +19446,10 @@
     </row>
     <row r="142" spans="1:47">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B142" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C142" s="2">
         <v>44940.38544024306</v>
@@ -19392,16 +19470,16 @@
         <v>3952</v>
       </c>
       <c r="I142" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J142" t="b">
         <v>1</v>
       </c>
       <c r="K142" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="L142" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="M142">
         <v>179</v>
@@ -19437,7 +19515,7 @@
         <v>4.9053125</v>
       </c>
       <c r="AE142" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF142">
         <v>0.01709</v>
@@ -19490,10 +19568,10 @@
     </row>
     <row r="143" spans="1:47">
       <c r="A143" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B143" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C143" s="2">
         <v>44940.38578652778</v>
@@ -19514,16 +19592,16 @@
         <v>3975</v>
       </c>
       <c r="I143" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J143" t="b">
         <v>1</v>
       </c>
       <c r="K143" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L143" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="M143">
         <v>177</v>
@@ -19559,7 +19637,7 @@
         <v>4.74434783</v>
       </c>
       <c r="AE143" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF143">
         <v>-0.02298</v>
@@ -19612,10 +19690,10 @@
     </row>
     <row r="144" spans="1:47">
       <c r="A144" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B144" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C144" s="2">
         <v>44940.38607760417</v>
@@ -19636,16 +19714,16 @@
         <v>3977</v>
       </c>
       <c r="I144" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J144" t="b">
         <v>1</v>
       </c>
       <c r="K144" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L144" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="M144">
         <v>177</v>
@@ -19681,7 +19759,7 @@
         <v>5.03</v>
       </c>
       <c r="AE144" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF144">
         <v>0.467391</v>
@@ -19734,10 +19812,10 @@
     </row>
     <row r="145" spans="1:47">
       <c r="A145" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B145" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C145" s="2">
         <v>44940.386411875</v>
@@ -19758,16 +19836,16 @@
         <v>4041</v>
       </c>
       <c r="I145" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J145" t="b">
         <v>1</v>
       </c>
       <c r="K145" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="L145" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="M145">
         <v>177</v>
@@ -19803,7 +19881,7 @@
         <v>5.03390625</v>
       </c>
       <c r="AE145" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AF145">
         <v>0.000244</v>
@@ -19866,156 +19944,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>44940.38676024305</v>
@@ -20036,16 +20114,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L2" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M2">
         <v>177</v>
@@ -20081,7 +20159,7 @@
         <v>-15.77</v>
       </c>
       <c r="AE2" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AG2">
         <v>-51.73913</v>
@@ -20098,10 +20176,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C3" s="2">
         <v>44940.38705238426</v>
@@ -20122,16 +20200,16 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="L3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="M3">
         <v>165</v>
@@ -20167,7 +20245,7 @@
         <v>-28.04</v>
       </c>
       <c r="AE3" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF3">
         <v>-20.130435</v>
@@ -20208,10 +20286,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>44940.40132559028</v>
@@ -20232,16 +20310,16 @@
         <v>1270</v>
       </c>
       <c r="I4" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="L4" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -20277,7 +20355,7 @@
         <v>-12.52925079</v>
       </c>
       <c r="AE4" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF4">
         <v>0.040137</v>
@@ -20330,10 +20408,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2">
         <v>44940.40167709491</v>
@@ -20354,16 +20432,16 @@
         <v>1293</v>
       </c>
       <c r="I5" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="L5" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="M5">
         <v>66</v>
@@ -20399,7 +20477,7 @@
         <v>-6.26826087</v>
       </c>
       <c r="AE5" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF5">
         <v>0.8930979999999999</v>
@@ -20452,10 +20530,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>44940.40227767361</v>
@@ -20476,16 +20554,16 @@
         <v>1315</v>
       </c>
       <c r="I6" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="L6" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="M6">
         <v>68</v>
@@ -20521,7 +20599,7 @@
         <v>-6.775</v>
       </c>
       <c r="AE6" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF6">
         <v>-0.075548</v>
@@ -20574,10 +20652,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2">
         <v>44940.40261505787</v>
@@ -20598,16 +20676,16 @@
         <v>1380</v>
       </c>
       <c r="I7" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="L7" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="M7">
         <v>70</v>
@@ -20643,7 +20721,7 @@
         <v>-6.15692308</v>
       </c>
       <c r="AE7" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF7">
         <v>0.031189</v>
@@ -20696,10 +20774,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>44940.40297104167</v>
@@ -20720,16 +20798,16 @@
         <v>1404</v>
       </c>
       <c r="I8" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L8" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="M8">
         <v>66</v>
@@ -20765,7 +20843,7 @@
         <v>-4.94041667</v>
       </c>
       <c r="AE8" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF8">
         <v>0.166319</v>
@@ -20818,10 +20896,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>44940.40324975694</v>
@@ -20842,16 +20920,16 @@
         <v>1405</v>
       </c>
       <c r="I9" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="L9" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="M9">
         <v>60</v>
@@ -20887,7 +20965,7 @@
         <v>-8.84</v>
       </c>
       <c r="AE9" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF9">
         <v>-12.791667</v>
@@ -20940,10 +21018,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>44940.40358505787</v>
@@ -20964,16 +21042,16 @@
         <v>1446</v>
       </c>
       <c r="I10" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L10" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="M10">
         <v>67</v>
@@ -21009,7 +21087,7 @@
         <v>-6.66829268</v>
       </c>
       <c r="AE10" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF10">
         <v>0.173706</v>
@@ -21062,10 +21140,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>44940.40393440973</v>
@@ -21086,16 +21164,16 @@
         <v>1495</v>
       </c>
       <c r="I11" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="L11" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="M11">
         <v>61</v>
@@ -21131,7 +21209,7 @@
         <v>-6.18938776</v>
       </c>
       <c r="AE11" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF11">
         <v>0.03208</v>
@@ -21184,10 +21262,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>44940.40422270833</v>
@@ -21208,16 +21286,16 @@
         <v>1496</v>
       </c>
       <c r="I12" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="L12" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="M12">
         <v>65</v>
@@ -21253,7 +21331,7 @@
         <v>-5.79</v>
       </c>
       <c r="AE12" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF12">
         <v>1.306122</v>
@@ -21306,10 +21384,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2">
         <v>44940.40455836806</v>
@@ -21330,16 +21408,16 @@
         <v>1537</v>
       </c>
       <c r="I13" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="L13" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="M13">
         <v>64</v>
@@ -21375,7 +21453,7 @@
         <v>-6.00682927</v>
       </c>
       <c r="AE13" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF13">
         <v>-0.017252</v>
@@ -21428,10 +21506,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>44940.40490565972</v>
@@ -21452,16 +21530,16 @@
         <v>1560</v>
       </c>
       <c r="I14" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="L14" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="M14">
         <v>65</v>
@@ -21497,7 +21575,7 @@
         <v>-5.87086957</v>
       </c>
       <c r="AE14" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF14">
         <v>0.019411</v>
@@ -21550,10 +21628,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2">
         <v>44940.40519541666</v>
@@ -21574,16 +21652,16 @@
         <v>1562</v>
       </c>
       <c r="I15" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="L15" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="M15">
         <v>62</v>
@@ -21619,7 +21697,7 @@
         <v>-5.635</v>
       </c>
       <c r="AE15" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF15">
         <v>0.380435</v>
@@ -21672,10 +21750,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>44940.40553086805</v>
@@ -21696,16 +21774,16 @@
         <v>1626</v>
       </c>
       <c r="I16" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="L16" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="M16">
         <v>61</v>
@@ -21741,7 +21819,7 @@
         <v>-5.70546875</v>
       </c>
       <c r="AE16" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF16">
         <v>-0.003418</v>
@@ -21794,10 +21872,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>44940.40587858796</v>
@@ -21818,16 +21896,16 @@
         <v>1650</v>
       </c>
       <c r="I17" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="L17" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="M17">
         <v>70</v>
@@ -21863,7 +21941,7 @@
         <v>-5.28333333</v>
       </c>
       <c r="AE17" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF17">
         <v>0.057726</v>
@@ -21916,10 +21994,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2">
         <v>44940.40616829861</v>
@@ -21940,16 +22018,16 @@
         <v>1651</v>
       </c>
       <c r="I18" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="L18" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M18">
         <v>67</v>
@@ -21985,7 +22063,7 @@
         <v>-4.88</v>
       </c>
       <c r="AE18" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF18">
         <v>1.333333</v>
@@ -22038,10 +22116,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2">
         <v>44940.40650520833</v>
@@ -22062,16 +22140,16 @@
         <v>1716</v>
       </c>
       <c r="I19" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="L19" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M19">
         <v>83</v>
@@ -22107,7 +22185,7 @@
         <v>-5.01276923</v>
       </c>
       <c r="AE19" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF19">
         <v>-0.006864</v>
@@ -22160,10 +22238,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>44940.4068628588</v>
@@ -22184,16 +22262,16 @@
         <v>1740</v>
       </c>
       <c r="I20" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="L20" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="M20">
         <v>79</v>
@@ -22229,7 +22307,7 @@
         <v>-4.80041667</v>
       </c>
       <c r="AE20" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF20">
         <v>0.029006</v>
@@ -22282,10 +22360,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>44940.40714446759</v>
@@ -22306,16 +22384,16 @@
         <v>1741</v>
       </c>
       <c r="I21" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="L21" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="M21">
         <v>83</v>
@@ -22351,7 +22429,7 @@
         <v>-4.88</v>
       </c>
       <c r="AE21" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF21">
         <v>-0.25</v>
@@ -22404,10 +22482,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>44940.40747799769</v>
@@ -22428,16 +22506,16 @@
         <v>1782</v>
       </c>
       <c r="I22" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="L22" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="M22">
         <v>88</v>
@@ -22473,7 +22551,7 @@
         <v>-4.4604878</v>
       </c>
       <c r="AE22" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF22">
         <v>0.033314</v>
@@ -22526,10 +22604,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2">
         <v>44940.40782540509</v>
@@ -22550,16 +22628,16 @@
         <v>1829</v>
       </c>
       <c r="I23" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="L23" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="M23">
         <v>76</v>
@@ -22595,7 +22673,7 @@
         <v>-4.64340426</v>
       </c>
       <c r="AE23" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF23">
         <v>-0.012764</v>
@@ -22648,10 +22726,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2">
         <v>44940.4081149537</v>
@@ -22672,16 +22750,16 @@
         <v>1831</v>
       </c>
       <c r="I24" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="L24" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="M24">
         <v>77</v>
@@ -22717,7 +22795,7 @@
         <v>-5.335</v>
       </c>
       <c r="AE24" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF24">
         <v>-1.132979</v>
@@ -22770,10 +22848,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>44940.40845047454</v>
@@ -22794,16 +22872,16 @@
         <v>1871</v>
       </c>
       <c r="I25" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="L25" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="M25">
         <v>92</v>
@@ -22839,7 +22917,7 @@
         <v>-4.7625</v>
       </c>
       <c r="AE25" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF25">
         <v>0.046875</v>
@@ -22892,10 +22970,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>44940.4087983912</v>
@@ -22916,16 +22994,16 @@
         <v>1895</v>
       </c>
       <c r="I26" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="L26" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="M26">
         <v>82</v>
@@ -22961,7 +23039,7 @@
         <v>-4.99083333</v>
       </c>
       <c r="AE26" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF26">
         <v>-0.03125</v>
@@ -23014,10 +23092,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2">
         <v>44940.40942376157</v>
@@ -23038,16 +23116,16 @@
         <v>1960</v>
       </c>
       <c r="I27" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="L27" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="M27">
         <v>91</v>
@@ -23083,7 +23161,7 @@
         <v>-4.45476923</v>
       </c>
       <c r="AE27" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF27">
         <v>0.027071</v>
@@ -23136,10 +23214,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2">
         <v>44940.40977202546</v>
@@ -23160,16 +23238,16 @@
         <v>1982</v>
       </c>
       <c r="I28" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="L28" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="M28">
         <v>75</v>
@@ -23205,7 +23283,7 @@
         <v>-4.295</v>
       </c>
       <c r="AE28" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF28">
         <v>0.02384</v>
@@ -23258,10 +23336,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>44940.41006155092</v>
@@ -23282,16 +23360,16 @@
         <v>1985</v>
       </c>
       <c r="I29" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="L29" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="M29">
         <v>78</v>
@@ -23327,7 +23405,7 @@
         <v>-4.37</v>
       </c>
       <c r="AE29" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF29">
         <v>-0.080808</v>
@@ -23380,10 +23458,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2">
         <v>44940.41039842593</v>
@@ -23404,16 +23482,16 @@
         <v>2049</v>
       </c>
       <c r="I30" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="L30" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M30">
         <v>59</v>
@@ -23449,7 +23527,7 @@
         <v>-4.12421875</v>
       </c>
       <c r="AE30" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF30">
         <v>0.012533</v>
@@ -23502,10 +23580,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2">
         <v>44940.41074732639</v>
@@ -23526,16 +23604,16 @@
         <v>2072</v>
       </c>
       <c r="I31" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="L31" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="M31">
         <v>73</v>
@@ -23571,7 +23649,7 @@
         <v>-4.24086957</v>
       </c>
       <c r="AE31" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF31">
         <v>-0.0166</v>
@@ -23624,10 +23702,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2">
         <v>44940.41103886574</v>
@@ -23648,16 +23726,16 @@
         <v>2074</v>
       </c>
       <c r="I32" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="L32" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="M32">
         <v>69</v>
@@ -23693,7 +23771,7 @@
         <v>-3.35</v>
       </c>
       <c r="AE32" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF32">
         <v>1.456522</v>
@@ -23746,10 +23824,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>44940.41137101852</v>
@@ -23770,16 +23848,16 @@
         <v>2139</v>
       </c>
       <c r="I33" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="L33" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M33">
         <v>60</v>
@@ -23815,7 +23893,7 @@
         <v>-3.95784615</v>
       </c>
       <c r="AE33" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF33">
         <v>-0.030533</v>
@@ -23868,10 +23946,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C34" s="2">
         <v>44940.41171789352</v>
@@ -23892,16 +23970,16 @@
         <v>2162</v>
       </c>
       <c r="I34" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="L34" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="M34">
         <v>74</v>
@@ -23937,7 +24015,7 @@
         <v>-4.06826087</v>
       </c>
       <c r="AE34" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF34">
         <v>-0.015792</v>
@@ -23990,10 +24068,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>44940.41200840277</v>
@@ -24014,16 +24092,16 @@
         <v>2164</v>
       </c>
       <c r="I35" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="L35" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="M35">
         <v>69</v>
@@ -24059,7 +24137,7 @@
         <v>-3.96</v>
       </c>
       <c r="AE35" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF35">
         <v>0.173913</v>
@@ -24112,10 +24190,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2">
         <v>44940.41234394676</v>
@@ -24136,16 +24214,16 @@
         <v>2204</v>
       </c>
       <c r="I36" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="L36" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="M36">
         <v>56</v>
@@ -24181,7 +24259,7 @@
         <v>-4.0005</v>
       </c>
       <c r="AE36" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF36">
         <v>-0.003125</v>
@@ -24234,10 +24312,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>44940.41269121528</v>
@@ -24258,16 +24336,16 @@
         <v>2252</v>
       </c>
       <c r="I37" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="L37" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="M37">
         <v>65</v>
@@ -24303,7 +24381,7 @@
         <v>-4.24833333</v>
       </c>
       <c r="AE37" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF37">
         <v>-0.016927</v>
@@ -24356,10 +24434,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C38" s="2">
         <v>44940.41298534722</v>
@@ -24380,16 +24458,16 @@
         <v>2254</v>
       </c>
       <c r="I38" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="L38" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="M38">
         <v>66</v>
@@ -24425,7 +24503,7 @@
         <v>-4.265</v>
       </c>
       <c r="AE38" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF38">
         <v>-0.03125</v>
@@ -24478,10 +24556,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2">
         <v>44940.41332467592</v>
@@ -24502,16 +24580,16 @@
         <v>2294</v>
       </c>
       <c r="I39" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="L39" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="M39">
         <v>80</v>
@@ -24547,7 +24625,7 @@
         <v>-4.0385</v>
       </c>
       <c r="AE39" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF39">
         <v>0.01875</v>
@@ -24600,10 +24678,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>44940.41366487269</v>
@@ -24624,16 +24702,16 @@
         <v>2317</v>
       </c>
       <c r="I40" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="L40" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="M40">
         <v>83</v>
@@ -24669,7 +24747,7 @@
         <v>-3.9226087</v>
       </c>
       <c r="AE40" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF40">
         <v>0.016541</v>
@@ -24722,10 +24800,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>44940.41395497685</v>
@@ -24746,16 +24824,16 @@
         <v>2319</v>
       </c>
       <c r="I41" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="L41" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="M41">
         <v>78</v>
@@ -24791,7 +24869,7 @@
         <v>-3.965</v>
       </c>
       <c r="AE41" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF41">
         <v>-0.065217</v>
@@ -24844,10 +24922,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2">
         <v>44940.41429173611</v>
@@ -24868,16 +24946,16 @@
         <v>2382</v>
       </c>
       <c r="I42" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="L42" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="M42">
         <v>106</v>
@@ -24913,7 +24991,7 @@
         <v>-4.11238095</v>
       </c>
       <c r="AE42" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF42">
         <v>-0.007811</v>
@@ -24966,10 +25044,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>44940.41463856481</v>
@@ -24990,16 +25068,16 @@
         <v>2405</v>
       </c>
       <c r="I43" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="L43" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="M43">
         <v>110</v>
@@ -25035,7 +25113,7 @@
         <v>-3.86956522</v>
       </c>
       <c r="AE43" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF43">
         <v>0.034627</v>
@@ -25088,10 +25166,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2">
         <v>44940.41492850694</v>
@@ -25112,16 +25190,16 @@
         <v>2407</v>
       </c>
       <c r="I44" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L44" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="M44">
         <v>108</v>
@@ -25157,7 +25235,7 @@
         <v>-3.66</v>
       </c>
       <c r="AE44" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF44">
         <v>0.347826</v>
@@ -25210,10 +25288,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
         <v>44940.41526369213</v>
@@ -25234,16 +25312,16 @@
         <v>2470</v>
       </c>
       <c r="I45" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="L45" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="M45">
         <v>94</v>
@@ -25279,7 +25357,7 @@
         <v>-4.01555556</v>
       </c>
       <c r="AE45" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF45">
         <v>-0.018644</v>
@@ -25332,10 +25410,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2">
         <v>44940.41561819444</v>
@@ -25356,16 +25434,16 @@
         <v>2494</v>
       </c>
       <c r="I46" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="L46" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="M46">
         <v>110</v>
@@ -25401,7 +25479,7 @@
         <v>-4.03875</v>
       </c>
       <c r="AE46" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF46">
         <v>-0.003142</v>
@@ -25454,10 +25532,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>44940.41590708333</v>
@@ -25478,16 +25556,16 @@
         <v>2495</v>
       </c>
       <c r="I47" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="L47" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M47">
         <v>106</v>
@@ -25523,7 +25601,7 @@
         <v>-4.57</v>
       </c>
       <c r="AE47" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF47">
         <v>-1.75</v>
@@ -25576,10 +25654,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2">
         <v>44940.41623784722</v>
@@ -25600,16 +25678,16 @@
         <v>2560</v>
       </c>
       <c r="I48" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="L48" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="M48">
         <v>108</v>
@@ -25645,7 +25723,7 @@
         <v>-4.20153846</v>
       </c>
       <c r="AE48" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF48">
         <v>0.018698</v>
@@ -25698,10 +25776,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2">
         <v>44940.41658493056</v>
@@ -25722,16 +25800,16 @@
         <v>2582</v>
       </c>
       <c r="I49" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="L49" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M49">
         <v>75</v>
@@ -25767,7 +25845,7 @@
         <v>-4.17</v>
       </c>
       <c r="AE49" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF49">
         <v>0.004673</v>
@@ -25820,10 +25898,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2">
         <v>44940.41687560186</v>
@@ -25844,16 +25922,16 @@
         <v>2584</v>
       </c>
       <c r="I50" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="L50" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="M50">
         <v>79</v>
@@ -25889,7 +25967,7 @@
         <v>-4.42</v>
       </c>
       <c r="AE50" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF50">
         <v>-0.409091</v>
@@ -25942,10 +26020,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>44940.41721150463</v>
@@ -25966,16 +26044,16 @@
         <v>2624</v>
       </c>
       <c r="I51" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="L51" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="M51">
         <v>81</v>
@@ -26011,7 +26089,7 @@
         <v>-3.97775</v>
       </c>
       <c r="AE51" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF51">
         <v>0.03625</v>
@@ -26064,10 +26142,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>44940.41755880787</v>
@@ -26088,16 +26166,16 @@
         <v>2670</v>
       </c>
       <c r="I52" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="M52">
         <v>83</v>
@@ -26133,7 +26211,7 @@
         <v>-3.78347826</v>
       </c>
       <c r="AE52" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF52">
         <v>0.013847</v>
@@ -26186,10 +26264,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2">
         <v>44940.41785347222</v>
@@ -26210,16 +26288,16 @@
         <v>2672</v>
       </c>
       <c r="I53" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="L53" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="M53">
         <v>83</v>
@@ -26255,7 +26333,7 @@
         <v>-3.81</v>
       </c>
       <c r="AE53" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF53">
         <v>-0.043478</v>
@@ -26308,10 +26386,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2">
         <v>44940.41818424768</v>
@@ -26332,16 +26410,16 @@
         <v>2711</v>
       </c>
       <c r="I54" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="L54" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="M54">
         <v>99</v>
@@ -26377,7 +26455,7 @@
         <v>-3.72794872</v>
       </c>
       <c r="AE54" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF54">
         <v>0.006903</v>
@@ -26430,10 +26508,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C55" s="2">
         <v>44940.41853172454</v>
@@ -26454,16 +26532,16 @@
         <v>2734</v>
       </c>
       <c r="I55" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="L55" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="M55">
         <v>83</v>
@@ -26499,7 +26577,7 @@
         <v>-3.71043478</v>
       </c>
       <c r="AE55" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF55">
         <v>0.002472</v>
@@ -26552,10 +26630,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2">
         <v>44940.41882295139</v>
@@ -26576,16 +26654,16 @@
         <v>2760</v>
       </c>
       <c r="I56" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="L56" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="M56">
         <v>81</v>
@@ -26621,7 +26699,7 @@
         <v>-3.92730769</v>
       </c>
       <c r="AE56" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF56">
         <v>-0.027335</v>
@@ -26674,10 +26752,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>44940.41915699074</v>
@@ -26698,16 +26776,16 @@
         <v>2800</v>
       </c>
       <c r="I57" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="L57" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="M57">
         <v>117</v>
@@ -26743,7 +26821,7 @@
         <v>-3.8025</v>
       </c>
       <c r="AE57" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF57">
         <v>0.01024</v>
@@ -26796,10 +26874,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>44940.41950591435</v>
@@ -26820,16 +26898,16 @@
         <v>2822</v>
       </c>
       <c r="I58" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="L58" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M58">
         <v>108</v>
@@ -26865,7 +26943,7 @@
         <v>-3.71272727</v>
       </c>
       <c r="AE58" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF58">
         <v>0.013326</v>
@@ -26918,10 +26996,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2">
         <v>44940.41979554398</v>
@@ -26942,16 +27020,16 @@
         <v>2823</v>
       </c>
       <c r="I59" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="L59" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="M59">
         <v>112</v>
@@ -26987,7 +27065,7 @@
         <v>-3.66</v>
       </c>
       <c r="AE59" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF59">
         <v>0.181818</v>
@@ -27040,10 +27118,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2">
         <v>44940.42013127315</v>
@@ -27064,16 +27142,16 @@
         <v>2887</v>
       </c>
       <c r="I60" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="L60" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="M60">
         <v>165</v>
@@ -27109,7 +27187,7 @@
         <v>-3.24328125</v>
       </c>
       <c r="AE60" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF60">
         <v>0.02124</v>
@@ -27162,10 +27240,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>44940.42047820602</v>
@@ -27186,16 +27264,16 @@
         <v>2910</v>
       </c>
       <c r="I61" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="L61" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="M61">
         <v>173</v>
@@ -27231,7 +27309,7 @@
         <v>-3.56478261</v>
       </c>
       <c r="AE61" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF61">
         <v>-0.045871</v>
@@ -27284,10 +27362,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C62" s="2">
         <v>44940.42077486111</v>
@@ -27308,16 +27386,16 @@
         <v>2911</v>
       </c>
       <c r="I62" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="L62" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="M62">
         <v>166</v>
@@ -27353,7 +27431,7 @@
         <v>-3.96</v>
       </c>
       <c r="AE62" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF62">
         <v>-1.304348</v>
@@ -27406,10 +27484,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>44940.42110949074</v>
@@ -27430,16 +27508,16 @@
         <v>2976</v>
       </c>
       <c r="I63" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="L63" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="M63">
         <v>94</v>
@@ -27475,7 +27553,7 @@
         <v>-3.69046154</v>
       </c>
       <c r="AE63" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF63">
         <v>0.013728</v>
@@ -27528,10 +27606,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C64" s="2">
         <v>44940.42145140046</v>
@@ -27552,16 +27630,16 @@
         <v>2999</v>
       </c>
       <c r="I64" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="L64" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="M64">
         <v>115</v>
@@ -27597,7 +27675,7 @@
         <v>-3.97565217</v>
       </c>
       <c r="AE64" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF64">
         <v>-0.040686</v>
@@ -27650,10 +27728,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>44940.42174225694</v>
@@ -27674,16 +27752,16 @@
         <v>3000</v>
       </c>
       <c r="I65" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="L65" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M65">
         <v>152</v>
@@ -27719,7 +27797,7 @@
         <v>-3.05</v>
       </c>
       <c r="AE65" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF65">
         <v>3.043478</v>
@@ -27772,10 +27850,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C66" s="2">
         <v>44940.42208086805</v>
@@ -27796,16 +27874,16 @@
         <v>3064</v>
       </c>
       <c r="I66" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="L66" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="M66">
         <v>200</v>
@@ -27841,7 +27919,7 @@
         <v>-3.60046875</v>
       </c>
       <c r="AE66" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF66">
         <v>-0.02832</v>
@@ -27894,10 +27972,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>44940.42242895834</v>
@@ -27918,16 +27996,16 @@
         <v>3086</v>
       </c>
       <c r="I67" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="L67" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="M67">
         <v>126</v>
@@ -27963,7 +28041,7 @@
         <v>-3.71272727</v>
       </c>
       <c r="AE67" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF67">
         <v>-0.016787</v>
@@ -28016,10 +28094,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C68" s="2">
         <v>44940.42272012732</v>
@@ -28040,16 +28118,16 @@
         <v>3088</v>
       </c>
       <c r="I68" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="L68" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="M68">
         <v>112</v>
@@ -28085,7 +28163,7 @@
         <v>-3.81</v>
       </c>
       <c r="AE68" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF68">
         <v>-0.159091</v>
@@ -28138,10 +28216,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>44940.42305065972</v>
@@ -28162,16 +28240,16 @@
         <v>3128</v>
       </c>
       <c r="I69" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="L69" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="M69">
         <v>168</v>
@@ -28207,7 +28285,7 @@
         <v>-3.24625</v>
       </c>
       <c r="AE69" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="AF69">
         <v>0.04625</v>
